--- a/research/traditional_assets/database/data/malaysia/malaysia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_telecom_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_hexcap" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,29 +589,23 @@
           <t>Telecom. Equipment</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0133</v>
-      </c>
-      <c r="E2">
-        <v>-0.178</v>
-      </c>
       <c r="G2">
-        <v>-0.3541661406388082</v>
+        <v>-0.02314159481834169</v>
       </c>
       <c r="H2">
-        <v>-0.3652316626688549</v>
+        <v>-0.02384935443743834</v>
       </c>
       <c r="I2">
-        <v>-0.370199037746731</v>
+        <v>-0.04927166658255091</v>
       </c>
       <c r="J2">
-        <v>-0.339587621516245</v>
+        <v>-0.04311270825973205</v>
       </c>
       <c r="K2">
-        <v>-42.39</v>
+        <v>-10.08</v>
       </c>
       <c r="L2">
-        <v>-0.2675798510289105</v>
+        <v>-0.04323767854844936</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +629,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>42.133</v>
+        <v>23.998</v>
       </c>
       <c r="V2">
-        <v>0.3853040695016004</v>
-      </c>
-      <c r="W2">
-        <v>-0.1155963302752294</v>
+        <v>0.2773052923503582</v>
       </c>
       <c r="X2">
-        <v>0.1332091797841263</v>
-      </c>
-      <c r="Y2">
-        <v>-0.2488055100593557</v>
+        <v>0.1201704838036672</v>
       </c>
       <c r="Z2">
-        <v>1.738249630565069</v>
-      </c>
-      <c r="AA2">
-        <v>-0.3899796900034319</v>
+        <v>6.784822014878913</v>
       </c>
       <c r="AB2">
-        <v>0.1327744986895758</v>
-      </c>
-      <c r="AC2">
-        <v>-0.5220791422794295</v>
+        <v>0.1130993674867273</v>
       </c>
       <c r="AD2">
-        <v>4.657</v>
+        <v>8.475</v>
       </c>
       <c r="AE2">
-        <v>0.004657799185611588</v>
+        <v>0.003518151950459178</v>
       </c>
       <c r="AF2">
-        <v>4.661657799185612</v>
+        <v>8.478518151950459</v>
       </c>
       <c r="AG2">
-        <v>-37.47134220081439</v>
+        <v>-15.51948184804954</v>
       </c>
       <c r="AH2">
-        <v>0.04088755386222365</v>
+        <v>0.08923016604396938</v>
       </c>
       <c r="AI2">
-        <v>0.0440811793989816</v>
+        <v>0.07794294586829169</v>
       </c>
       <c r="AJ2">
-        <v>-0.5213138829818126</v>
+        <v>-0.2185211013927716</v>
       </c>
       <c r="AK2">
-        <v>-0.5889992574048625</v>
+        <v>-0.1830548124303072</v>
       </c>
       <c r="AL2">
-        <v>0.352</v>
+        <v>0.701</v>
       </c>
       <c r="AM2">
-        <v>-0.106</v>
+        <v>-1.294</v>
       </c>
       <c r="AN2">
-        <v>-0.08264272151337154</v>
+        <v>12.21181556195965</v>
       </c>
       <c r="AO2">
-        <v>-166.6221590909091</v>
+        <v>-16.39087018544936</v>
       </c>
       <c r="AP2">
-        <v>0.6649632162839061</v>
+        <v>-22.36236577528751</v>
       </c>
       <c r="AQ2">
-        <v>553.3113207547171</v>
+        <v>8.879443585780525</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +694,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Opcom Holdings Berhad (KLSE:OPCOM)</t>
+          <t>Hextar Capital Berhad (KLSE:HEXCAP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,29 +702,23 @@
           <t>Telecom. Equipment</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0133</v>
-      </c>
-      <c r="E3">
-        <v>-0.178</v>
-      </c>
       <c r="G3">
-        <v>0.0904494382022472</v>
+        <v>0.1076591154261057</v>
       </c>
       <c r="H3">
-        <v>0.0904494382022472</v>
+        <v>0.1076591154261057</v>
       </c>
       <c r="I3">
-        <v>-0.01073033707865169</v>
+        <v>0.02448759439050701</v>
       </c>
       <c r="J3">
-        <v>-0.006293928807478046</v>
+        <v>0.01224379719525351</v>
       </c>
       <c r="K3">
-        <v>0.22</v>
+        <v>1.17</v>
       </c>
       <c r="L3">
-        <v>0.01235955056179775</v>
+        <v>0.01262135922330097</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +742,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.3</v>
+        <v>12.5</v>
       </c>
       <c r="V3">
-        <v>0.4123931623931624</v>
+        <v>0.2446183953033268</v>
       </c>
       <c r="W3">
-        <v>0.007586206896551724</v>
+        <v>0.03323863636363636</v>
       </c>
       <c r="X3">
-        <v>0.1328085933479788</v>
+        <v>0.1153214466736765</v>
       </c>
       <c r="Y3">
-        <v>-0.1252223864514271</v>
+        <v>-0.08208281031004015</v>
       </c>
       <c r="Z3">
-        <v>1.220348279171809</v>
+        <v>5.82945541441328</v>
       </c>
       <c r="AA3">
-        <v>-0.007680785189435708</v>
+        <v>0.07137466985284868</v>
       </c>
       <c r="AB3">
-        <v>0.1328053040591282</v>
+        <v>0.1130137857778996</v>
       </c>
       <c r="AC3">
-        <v>-0.1404860892485639</v>
+        <v>-0.0416391159250509</v>
       </c>
       <c r="AD3">
-        <v>0.002</v>
+        <v>1.83</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.002</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>-19.298</v>
+        <v>-10.67</v>
       </c>
       <c r="AH3">
-        <v>4.273321652920816e-05</v>
+        <v>0.03457396561496316</v>
       </c>
       <c r="AI3">
-        <v>5.347307630607989e-05</v>
+        <v>0.04082087887575285</v>
       </c>
       <c r="AJ3">
-        <v>-0.7016944222238385</v>
+        <v>-0.2639129359386594</v>
       </c>
       <c r="AK3">
-        <v>-1.066070047508563</v>
+        <v>-0.3300340241261986</v>
       </c>
       <c r="AL3">
-        <v>0.005</v>
+        <v>0.297</v>
       </c>
       <c r="AM3">
-        <v>-0.322</v>
+        <v>-1.563</v>
       </c>
       <c r="AN3">
-        <v>0.01219512195121951</v>
+        <v>0.1833667334669339</v>
       </c>
       <c r="AO3">
-        <v>-38.2</v>
+        <v>7.643097643097644</v>
       </c>
       <c r="AP3">
-        <v>-117.6707317073171</v>
+        <v>-1.069138276553106</v>
       </c>
       <c r="AQ3">
-        <v>0.593167701863354</v>
+        <v>-1.45233525271913</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +819,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMTrack Berhad (KLSE:SMTRACK)</t>
+          <t>Mlabs Systems Berhad (KLSE:MLAB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,22 +828,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-1.259615384615385</v>
+        <v>-0.3876767676767677</v>
       </c>
       <c r="H4">
-        <v>-1.259615384615385</v>
+        <v>-0.496969696969697</v>
       </c>
       <c r="I4">
-        <v>-1.269230769230769</v>
+        <v>-0.6862027536141599</v>
       </c>
       <c r="J4">
-        <v>-1.269230769230769</v>
+        <v>-0.6862027536141599</v>
       </c>
       <c r="K4">
-        <v>-1.26</v>
+        <v>-1.79</v>
       </c>
       <c r="L4">
-        <v>-1.211538461538461</v>
+        <v>-0.3616161616161616</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,67 +867,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.033</v>
+        <v>8.5</v>
       </c>
       <c r="V4">
-        <v>0.002462686567164179</v>
+        <v>1.793248945147679</v>
       </c>
       <c r="W4">
-        <v>-0.1155963302752294</v>
+        <v>-0.06347517730496455</v>
       </c>
       <c r="X4">
-        <v>0.1328055401765884</v>
+        <v>0.1197260835855945</v>
       </c>
       <c r="Y4">
-        <v>-0.2484018704518178</v>
+        <v>-0.1832012608905591</v>
       </c>
       <c r="Z4">
-        <v>0.1068200493015612</v>
+        <v>0.2681688724550702</v>
       </c>
       <c r="AA4">
-        <v>-0.1355792933442892</v>
+        <v>-0.1840182187122736</v>
       </c>
       <c r="AB4">
-        <v>0.1328055401765884</v>
+        <v>0.1181308816414565</v>
       </c>
       <c r="AC4">
-        <v>-0.2683848335208777</v>
+        <v>-0.30214910035373</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.003518151950459178</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.5385181519504592</v>
       </c>
       <c r="AG4">
-        <v>-0.033</v>
+        <v>-7.961481848049541</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.102020706654475</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.01999063752923871</v>
       </c>
       <c r="AJ4">
-        <v>-0.002468766364928556</v>
+        <v>2.471372561937561</v>
       </c>
       <c r="AK4">
-        <v>-0.002329356956306911</v>
+        <v>-0.4317853410149102</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.097</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>-0.2068832173240526</v>
+      </c>
+      <c r="AO4">
+        <v>-89.47368421052632</v>
       </c>
       <c r="AP4">
-        <v>0.02519083969465649</v>
+        <v>3.078685942787912</v>
+      </c>
+      <c r="AQ4">
+        <v>35.05154639175257</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +944,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mlabs Systems Berhad (KLSE:MLAB)</t>
+          <t>SMTrack Berhad (KLSE:SMTRACK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,22 +953,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-0.7216049382716049</v>
+        <v>-0.6575342465753424</v>
       </c>
       <c r="H5">
-        <v>-0.794238683127572</v>
+        <v>-0.6575342465753424</v>
       </c>
       <c r="I5">
-        <v>-0.8098624608718359</v>
+        <v>-0.5388127853881278</v>
       </c>
       <c r="J5">
-        <v>-0.8098624608718359</v>
+        <v>-0.5388127853881278</v>
       </c>
       <c r="K5">
-        <v>-2.92</v>
+        <v>-2.79</v>
       </c>
       <c r="L5">
-        <v>-0.6008230452674896</v>
+        <v>-0.636986301369863</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,73 +992,52 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.7</v>
+        <v>0.138</v>
       </c>
       <c r="V5">
-        <v>1.633587786259542</v>
-      </c>
-      <c r="W5">
-        <v>-0.08588235294117647</v>
+        <v>0.01037593984962406</v>
       </c>
       <c r="X5">
-        <v>0.1432730201530481</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2291553730942246</v>
-      </c>
-      <c r="Z5">
-        <v>0.4815381732641486</v>
-      </c>
-      <c r="AA5">
-        <v>-0.3899796900034319</v>
+        <v>0.1297251612620347</v>
       </c>
       <c r="AB5">
-        <v>0.1320994522759976</v>
-      </c>
-      <c r="AC5">
-        <v>-0.5220791422794295</v>
+        <v>0.113184949195555</v>
       </c>
       <c r="AD5">
-        <v>0.955</v>
+        <v>3.86</v>
       </c>
       <c r="AE5">
-        <v>0.004657799185611588</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.9596577991856116</v>
+        <v>3.86</v>
       </c>
       <c r="AG5">
-        <v>-9.740342200814387</v>
+        <v>3.722</v>
       </c>
       <c r="AH5">
-        <v>0.1277898174387762</v>
+        <v>0.2249417249417249</v>
       </c>
       <c r="AI5">
-        <v>0.03291046163142606</v>
+        <v>0.1841603053435114</v>
       </c>
       <c r="AJ5">
-        <v>3.053071296968709</v>
+        <v>0.2186582070262014</v>
       </c>
       <c r="AK5">
-        <v>-0.5276556210724612</v>
+        <v>0.1787532417635193</v>
       </c>
       <c r="AL5">
-        <v>0.092</v>
+        <v>0.202</v>
       </c>
       <c r="AM5">
-        <v>-0.016</v>
-      </c>
-      <c r="AN5">
-        <v>-0.263448275862069</v>
+        <v>0.202</v>
       </c>
       <c r="AO5">
-        <v>-42.82608695652174</v>
-      </c>
-      <c r="AP5">
-        <v>2.686990951948796</v>
+        <v>-11.68316831683168</v>
       </c>
       <c r="AQ5">
-        <v>246.25</v>
+        <v>-11.68316831683168</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1048,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UCrest Berhad (KLSE:UCREST)</t>
+          <t>Green Packet Berhad (KLSE:GPACKET)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,26 +1056,23 @@
           <t>Telecom. Equipment</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.137</v>
-      </c>
       <c r="G6">
-        <v>-5.563380281690141</v>
+        <v>-0.08067124332570556</v>
       </c>
       <c r="H6">
-        <v>-5.563380281690141</v>
+        <v>-0.07780320366132723</v>
       </c>
       <c r="I6">
-        <v>-5.704225352112676</v>
+        <v>-0.06102212051868803</v>
       </c>
       <c r="J6">
-        <v>-5.704225352112676</v>
+        <v>-0.06102212051868803</v>
       </c>
       <c r="K6">
-        <v>-8.029999999999999</v>
+        <v>-6.67</v>
       </c>
       <c r="L6">
-        <v>-5.654929577464789</v>
+        <v>-0.05087719298245614</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1136,201 +1096,8830 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.53</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>0.1994350282485876</v>
+        <v>0.164367816091954</v>
+      </c>
+      <c r="X6">
+        <v>0.12061488402174</v>
+      </c>
+      <c r="AB6">
+        <v>0.1125984007054824</v>
+      </c>
+      <c r="AD6">
+        <v>2.25</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2.25</v>
+      </c>
+      <c r="AG6">
+        <v>-0.6099999999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.1145038167938931</v>
+      </c>
+      <c r="AI6">
+        <v>0.1401869158878505</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.03633114949374627</v>
+      </c>
+      <c r="AK6">
+        <v>-0.04624715693707353</v>
+      </c>
+      <c r="AL6">
+        <v>0.164</v>
+      </c>
+      <c r="AM6">
+        <v>0.164</v>
+      </c>
+      <c r="AN6">
+        <v>-0.335820895522388</v>
+      </c>
+      <c r="AO6">
+        <v>-48.78048780487805</v>
+      </c>
+      <c r="AP6">
+        <v>0.09104477611940297</v>
+      </c>
+      <c r="AQ6">
+        <v>-48.78048780487805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hextar Capital Berhad (KLSE:HEXCAP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:HEXCAP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>7.64309764309764</v>
+      </c>
+      <c r="F2">
+        <v>4.68094648160472</v>
+      </c>
+      <c r="G2">
+        <v>0.183366733466934</v>
+      </c>
+      <c r="H2">
+        <v>0.9546492985971941</v>
+      </c>
+      <c r="I2">
+        <v>0.0345739656149632</v>
+      </c>
+      <c r="J2">
+        <v>0.18</v>
+      </c>
+      <c r="K2">
+        <v>51.1</v>
+      </c>
+      <c r="L2">
+        <v>44.62440719946</v>
+      </c>
+      <c r="M2">
+        <v>40.43</v>
+      </c>
+      <c r="N2">
+        <v>41.65180719946</v>
+      </c>
+      <c r="O2">
+        <v>1.83</v>
+      </c>
+      <c r="P2">
+        <v>9.5274</v>
+      </c>
+      <c r="Q2">
+        <v>0.1130137857779</v>
+      </c>
+      <c r="R2">
+        <v>0.110054911206531</v>
+      </c>
+      <c r="S2">
+        <v>0.048575823059757</v>
+      </c>
+      <c r="T2">
+        <v>0.038684</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.115321446673677</v>
+      </c>
+      <c r="X2">
+        <v>0.125721696593331</v>
+      </c>
+      <c r="Y2">
+        <v>1.20443606780733</v>
+      </c>
+      <c r="Z2">
+        <v>1.36813443815912</v>
+      </c>
+      <c r="AA2">
+        <v>1.83</v>
+      </c>
+      <c r="AB2">
+        <v>0.06391555665757501</v>
+      </c>
+      <c r="AC2">
+        <v>7.643097643097642</v>
+      </c>
+      <c r="AD2">
+        <v>1.83</v>
+      </c>
+      <c r="AE2">
+        <v>0.297</v>
+      </c>
+      <c r="AF2">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>9.98</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>51.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.06353300828410362</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.24</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>5.405999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.297</v>
+      </c>
+      <c r="AS2">
+        <v>1.83</v>
+      </c>
+      <c r="AT2">
+        <v>12.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1132939289365921</v>
+      </c>
+      <c r="C2">
+        <v>52.81802487793542</v>
+      </c>
+      <c r="D2">
+        <v>40.31802487793542</v>
+      </c>
+      <c r="E2">
+        <v>-1.83</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>12.5</v>
+      </c>
+      <c r="H2">
+        <v>51.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.98</v>
+      </c>
+      <c r="K2">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L2">
+        <v>2.27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.27</v>
+      </c>
+      <c r="O2">
+        <v>0.5447999999999998</v>
+      </c>
+      <c r="P2">
+        <v>1.7252</v>
+      </c>
+      <c r="Q2">
+        <v>9.4352</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1132939289365921</v>
+      </c>
+      <c r="T2">
+        <v>1.172523243405601</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.033972</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1130668635071443</v>
+      </c>
+      <c r="C3">
+        <v>52.37943673834892</v>
+      </c>
+      <c r="D3">
+        <v>40.40873673834892</v>
+      </c>
+      <c r="E3">
+        <v>-1.3007</v>
+      </c>
+      <c r="F3">
+        <v>0.5293</v>
+      </c>
+      <c r="G3">
+        <v>12.5</v>
+      </c>
+      <c r="H3">
+        <v>51.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.98</v>
+      </c>
+      <c r="K3">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L3">
+        <v>2.27</v>
+      </c>
+      <c r="M3">
+        <v>0.02365971</v>
+      </c>
+      <c r="N3">
+        <v>2.24634029</v>
+      </c>
+      <c r="O3">
+        <v>0.5391216695999999</v>
+      </c>
+      <c r="P3">
+        <v>1.7072186204</v>
+      </c>
+      <c r="Q3">
+        <v>9.4172186204</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.113865801522368</v>
+      </c>
+      <c r="T3">
+        <v>1.181524431940836</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.033972</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>95.94369499879751</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1128397980776965</v>
+      </c>
+      <c r="C4">
+        <v>51.94125770595862</v>
+      </c>
+      <c r="D4">
+        <v>40.49985770595862</v>
+      </c>
+      <c r="E4">
+        <v>-0.7714000000000001</v>
+      </c>
+      <c r="F4">
+        <v>1.0586</v>
+      </c>
+      <c r="G4">
+        <v>12.5</v>
+      </c>
+      <c r="H4">
+        <v>51.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.98</v>
+      </c>
+      <c r="K4">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L4">
+        <v>2.27</v>
+      </c>
+      <c r="M4">
+        <v>0.04731942</v>
+      </c>
+      <c r="N4">
+        <v>2.22268058</v>
+      </c>
+      <c r="O4">
+        <v>0.5334433391999999</v>
+      </c>
+      <c r="P4">
+        <v>1.6892372408</v>
+      </c>
+      <c r="Q4">
+        <v>9.399237240800002</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1144493449772413</v>
+      </c>
+      <c r="T4">
+        <v>1.19070931820128</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.033972</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>47.97184749939876</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1126127326482487</v>
+      </c>
+      <c r="C5">
+        <v>51.50349055460737</v>
+      </c>
+      <c r="D5">
+        <v>40.59139055460737</v>
+      </c>
+      <c r="E5">
+        <v>-0.2421000000000002</v>
+      </c>
+      <c r="F5">
+        <v>1.5879</v>
+      </c>
+      <c r="G5">
+        <v>12.5</v>
+      </c>
+      <c r="H5">
+        <v>51.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.98</v>
+      </c>
+      <c r="K5">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L5">
+        <v>2.27</v>
+      </c>
+      <c r="M5">
+        <v>0.07097913</v>
+      </c>
+      <c r="N5">
+        <v>2.19902087</v>
+      </c>
+      <c r="O5">
+        <v>0.5277650087999999</v>
+      </c>
+      <c r="P5">
+        <v>1.6712558612</v>
+      </c>
+      <c r="Q5">
+        <v>9.3812558612</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1150449202559265</v>
+      </c>
+      <c r="T5">
+        <v>1.200083583559878</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.033972</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>31.98123166626584</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1123856672188008</v>
+      </c>
+      <c r="C6">
+        <v>51.06613808327128</v>
+      </c>
+      <c r="D6">
+        <v>40.68333808327127</v>
+      </c>
+      <c r="E6">
+        <v>0.2871999999999999</v>
+      </c>
+      <c r="F6">
+        <v>2.1172</v>
+      </c>
+      <c r="G6">
+        <v>12.5</v>
+      </c>
+      <c r="H6">
+        <v>51.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.98</v>
+      </c>
+      <c r="K6">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L6">
+        <v>2.27</v>
+      </c>
+      <c r="M6">
+        <v>0.09463884</v>
+      </c>
+      <c r="N6">
+        <v>2.17536116</v>
+      </c>
+      <c r="O6">
+        <v>0.5220866783999999</v>
+      </c>
+      <c r="P6">
+        <v>1.6532744816</v>
+      </c>
+      <c r="Q6">
+        <v>9.363274481600001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1156529033529175</v>
+      </c>
+      <c r="T6">
+        <v>1.209653146113446</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
       </c>
       <c r="W6">
-        <v>-0.5615384615384614</v>
-      </c>
-      <c r="X6">
-        <v>0.1332091797841263</v>
+        <v>0.033972</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y6">
-        <v>-0.6947476413225877</v>
+        <v>23.98592374969938</v>
       </c>
       <c r="Z6">
-        <v>0.1616759649322555</v>
-      </c>
-      <c r="AA6">
-        <v>-0.9222361379938516</v>
-      </c>
-      <c r="AB6">
-        <v>0.1327744986895758</v>
-      </c>
-      <c r="AC6">
-        <v>-1.055010636683427</v>
-      </c>
-      <c r="AD6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.112158601789353</v>
+      </c>
+      <c r="C7">
+        <v>50.6292031163449</v>
+      </c>
+      <c r="D7">
+        <v>40.77570311634491</v>
+      </c>
+      <c r="E7">
+        <v>0.8165</v>
+      </c>
+      <c r="F7">
+        <v>2.6465</v>
+      </c>
+      <c r="G7">
+        <v>12.5</v>
+      </c>
+      <c r="H7">
+        <v>51.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.98</v>
+      </c>
+      <c r="K7">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L7">
+        <v>2.27</v>
+      </c>
+      <c r="M7">
+        <v>0.11829855</v>
+      </c>
+      <c r="N7">
+        <v>2.15170145</v>
+      </c>
+      <c r="O7">
+        <v>0.5164083479999999</v>
+      </c>
+      <c r="P7">
+        <v>1.635293102</v>
+      </c>
+      <c r="Q7">
+        <v>9.345293102000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1162736860940558</v>
+      </c>
+      <c r="T7">
+        <v>1.219424173141826</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.033972</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>19.1887389997595</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1119315363599052</v>
+      </c>
+      <c r="C8">
+        <v>50.19268850393056</v>
+      </c>
+      <c r="D8">
+        <v>40.86848850393056</v>
+      </c>
+      <c r="E8">
+        <v>1.3458</v>
+      </c>
+      <c r="F8">
+        <v>3.1758</v>
+      </c>
+      <c r="G8">
+        <v>12.5</v>
+      </c>
+      <c r="H8">
+        <v>51.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.98</v>
+      </c>
+      <c r="K8">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L8">
+        <v>2.27</v>
+      </c>
+      <c r="M8">
+        <v>0.14195826</v>
+      </c>
+      <c r="N8">
+        <v>2.12804174</v>
+      </c>
+      <c r="O8">
+        <v>0.5107300175999999</v>
+      </c>
+      <c r="P8">
+        <v>1.6173117224</v>
+      </c>
+      <c r="Q8">
+        <v>9.327311722400001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1169076769786225</v>
+      </c>
+      <c r="T8">
+        <v>1.229403094362299</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.033972</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.99061583313292</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1117044709304574</v>
+      </c>
+      <c r="C9">
+        <v>49.75659712213144</v>
+      </c>
+      <c r="D9">
+        <v>40.96169712213144</v>
+      </c>
+      <c r="E9">
+        <v>1.8751</v>
+      </c>
+      <c r="F9">
+        <v>3.7051</v>
+      </c>
+      <c r="G9">
+        <v>12.5</v>
+      </c>
+      <c r="H9">
+        <v>51.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.98</v>
+      </c>
+      <c r="K9">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L9">
+        <v>2.27</v>
+      </c>
+      <c r="M9">
+        <v>0.16561797</v>
+      </c>
+      <c r="N9">
+        <v>2.10438203</v>
+      </c>
+      <c r="O9">
+        <v>0.5050516871999999</v>
+      </c>
+      <c r="P9">
+        <v>1.5993303428</v>
+      </c>
+      <c r="Q9">
+        <v>9.309330342800001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1175553020757606</v>
+      </c>
+      <c r="T9">
+        <v>1.239596616039126</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.033972</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.70624214268536</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1115442855010096</v>
+      </c>
+      <c r="C10">
+        <v>49.29330818770973</v>
+      </c>
+      <c r="D10">
+        <v>41.02770818770973</v>
+      </c>
+      <c r="E10">
+        <v>2.4044</v>
+      </c>
+      <c r="F10">
+        <v>4.2344</v>
+      </c>
+      <c r="G10">
+        <v>12.5</v>
+      </c>
+      <c r="H10">
+        <v>51.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.98</v>
+      </c>
+      <c r="K10">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L10">
+        <v>2.27</v>
+      </c>
+      <c r="M10">
+        <v>0.19393552</v>
+      </c>
+      <c r="N10">
+        <v>2.076064479999999</v>
+      </c>
+      <c r="O10">
+        <v>0.4982554751999999</v>
+      </c>
+      <c r="P10">
+        <v>1.5778090048</v>
+      </c>
+      <c r="Q10">
+        <v>9.2878090048</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1182170059793582</v>
+      </c>
+      <c r="T10">
+        <v>1.250011736013276</v>
+      </c>
+      <c r="U10">
+        <v>0.0458</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.034808</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.70492130580308</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1113255800715617</v>
+      </c>
+      <c r="C11">
+        <v>48.85447915436333</v>
+      </c>
+      <c r="D11">
+        <v>41.11817915436333</v>
+      </c>
+      <c r="E11">
+        <v>2.9337</v>
+      </c>
+      <c r="F11">
+        <v>4.7637</v>
+      </c>
+      <c r="G11">
+        <v>12.5</v>
+      </c>
+      <c r="H11">
+        <v>51.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.98</v>
+      </c>
+      <c r="K11">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L11">
+        <v>2.27</v>
+      </c>
+      <c r="M11">
+        <v>0.21817746</v>
+      </c>
+      <c r="N11">
+        <v>2.051822539999999</v>
+      </c>
+      <c r="O11">
+        <v>0.4924374095999998</v>
+      </c>
+      <c r="P11">
+        <v>1.559385130399999</v>
+      </c>
+      <c r="Q11">
+        <v>9.2693851304</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.118893252825892</v>
+      </c>
+      <c r="T11">
+        <v>1.260655759723121</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.034808</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.40437449404718</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
         <v>0.1</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0.1</v>
-      </c>
-      <c r="AG6">
-        <v>-3.43</v>
-      </c>
-      <c r="AH6">
-        <v>0.005617977528089887</v>
-      </c>
-      <c r="AI6">
-        <v>0.01788908765652952</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.240364400840925</v>
-      </c>
-      <c r="AK6">
-        <v>-1.66504854368932</v>
-      </c>
-      <c r="AL6">
-        <v>0.024</v>
-      </c>
-      <c r="AM6">
-        <v>0.001000000000000001</v>
-      </c>
-      <c r="AN6">
-        <v>-0.012531328320802</v>
-      </c>
-      <c r="AO6">
-        <v>-337.5</v>
-      </c>
-      <c r="AP6">
-        <v>0.4298245614035087</v>
-      </c>
-      <c r="AQ6">
-        <v>-8099.999999999993</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Green Packet Berhad (KLSE:GPACKET)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Telecom. Equipment</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.109</v>
-      </c>
-      <c r="G7">
-        <v>-0.3375843960990247</v>
-      </c>
-      <c r="H7">
-        <v>-0.3480870217554388</v>
-      </c>
-      <c r="I7">
-        <v>-0.3383345836459115</v>
-      </c>
-      <c r="J7">
-        <v>-0.3383345836459115</v>
-      </c>
-      <c r="K7">
-        <v>-30.4</v>
-      </c>
-      <c r="L7">
-        <v>-0.2280570142535634</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>8.57</v>
-      </c>
-      <c r="V7">
-        <v>0.3441767068273093</v>
-      </c>
-      <c r="W7">
-        <v>-0.4919093851132686</v>
-      </c>
-      <c r="X7">
-        <v>0.1431348236273172</v>
-      </c>
-      <c r="Y7">
-        <v>-0.6350442087405858</v>
-      </c>
-      <c r="Z7">
-        <v>2.780559032123489</v>
-      </c>
-      <c r="AA7">
-        <v>-0.9407592824363791</v>
-      </c>
-      <c r="AB7">
-        <v>0.131742796847546</v>
-      </c>
-      <c r="AC7">
-        <v>-1.072502079283925</v>
-      </c>
-      <c r="AD7">
-        <v>3.6</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>3.6</v>
-      </c>
-      <c r="AG7">
-        <v>-4.970000000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.1263157894736842</v>
-      </c>
-      <c r="AI7">
-        <v>0.1855670103092783</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.249372804816859</v>
-      </c>
-      <c r="AK7">
-        <v>-0.4589104339796861</v>
-      </c>
-      <c r="AL7">
-        <v>0.231</v>
-      </c>
-      <c r="AM7">
-        <v>0.231</v>
-      </c>
-      <c r="AN7">
-        <v>-0.08256880733944955</v>
-      </c>
-      <c r="AO7">
-        <v>-195.2380952380952</v>
-      </c>
-      <c r="AP7">
-        <v>0.1139908256880734</v>
-      </c>
-      <c r="AQ7">
-        <v>-195.2380952380952</v>
+      <c r="B12">
+        <v>0.1112740746421139</v>
+      </c>
+      <c r="C12">
+        <v>48.34654326835282</v>
+      </c>
+      <c r="D12">
+        <v>41.13954326835282</v>
+      </c>
+      <c r="E12">
+        <v>3.463</v>
+      </c>
+      <c r="F12">
+        <v>5.293</v>
+      </c>
+      <c r="G12">
+        <v>12.5</v>
+      </c>
+      <c r="H12">
+        <v>51.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.98</v>
+      </c>
+      <c r="K12">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L12">
+        <v>2.27</v>
+      </c>
+      <c r="M12">
+        <v>0.254064</v>
+      </c>
+      <c r="N12">
+        <v>2.015936</v>
+      </c>
+      <c r="O12">
+        <v>0.4838246399999999</v>
+      </c>
+      <c r="P12">
+        <v>1.53211136</v>
+      </c>
+      <c r="Q12">
+        <v>9.242111360000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1195845273801266</v>
+      </c>
+      <c r="T12">
+        <v>1.271536317293186</v>
+      </c>
+      <c r="U12">
+        <v>0.048</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.03648</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.934756596763018</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1110720892126661</v>
+      </c>
+      <c r="C13">
+        <v>47.90124018159405</v>
+      </c>
+      <c r="D13">
+        <v>41.22354018159405</v>
+      </c>
+      <c r="E13">
+        <v>3.9923</v>
+      </c>
+      <c r="F13">
+        <v>5.8223</v>
+      </c>
+      <c r="G13">
+        <v>12.5</v>
+      </c>
+      <c r="H13">
+        <v>51.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.98</v>
+      </c>
+      <c r="K13">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L13">
+        <v>2.27</v>
+      </c>
+      <c r="M13">
+        <v>0.2794704</v>
+      </c>
+      <c r="N13">
+        <v>1.990529599999999</v>
+      </c>
+      <c r="O13">
+        <v>0.4777271039999998</v>
+      </c>
+      <c r="P13">
+        <v>1.512802495999999</v>
+      </c>
+      <c r="Q13">
+        <v>9.222802496</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1202913361940068</v>
+      </c>
+      <c r="T13">
+        <v>1.282661381774937</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.03648</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.122505997057289</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1110069037832183</v>
+      </c>
+      <c r="C14">
+        <v>47.39912121071474</v>
+      </c>
+      <c r="D14">
+        <v>41.25072121071474</v>
+      </c>
+      <c r="E14">
+        <v>4.521599999999999</v>
+      </c>
+      <c r="F14">
+        <v>6.351599999999999</v>
+      </c>
+      <c r="G14">
+        <v>12.5</v>
+      </c>
+      <c r="H14">
+        <v>51.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.98</v>
+      </c>
+      <c r="K14">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L14">
+        <v>2.27</v>
+      </c>
+      <c r="M14">
+        <v>0.3144042</v>
+      </c>
+      <c r="N14">
+        <v>1.9555958</v>
+      </c>
+      <c r="O14">
+        <v>0.4693429919999998</v>
+      </c>
+      <c r="P14">
+        <v>1.486252808</v>
+      </c>
+      <c r="Q14">
+        <v>9.196252808000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1210142088445662</v>
+      </c>
+      <c r="T14">
+        <v>1.294039288631273</v>
+      </c>
+      <c r="U14">
+        <v>0.0495</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.03762</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.220005330717592</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1108163183537704</v>
+      </c>
+      <c r="C15">
+        <v>46.94949754725268</v>
+      </c>
+      <c r="D15">
+        <v>41.33039754725268</v>
+      </c>
+      <c r="E15">
+        <v>5.0509</v>
+      </c>
+      <c r="F15">
+        <v>6.8809</v>
+      </c>
+      <c r="G15">
+        <v>12.5</v>
+      </c>
+      <c r="H15">
+        <v>51.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.98</v>
+      </c>
+      <c r="K15">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L15">
+        <v>2.27</v>
+      </c>
+      <c r="M15">
+        <v>0.3406045500000001</v>
+      </c>
+      <c r="N15">
+        <v>1.929395449999999</v>
+      </c>
+      <c r="O15">
+        <v>0.4630549079999999</v>
+      </c>
+      <c r="P15">
+        <v>1.466340542</v>
+      </c>
+      <c r="Q15">
+        <v>9.176340542</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1217536992572074</v>
+      </c>
+      <c r="T15">
+        <v>1.305678756564766</v>
+      </c>
+      <c r="U15">
+        <v>0.0495</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.03762</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.664620305277775</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1106257329243226</v>
+      </c>
+      <c r="C16">
+        <v>46.50018227132965</v>
+      </c>
+      <c r="D16">
+        <v>41.41038227132965</v>
+      </c>
+      <c r="E16">
+        <v>5.5802</v>
+      </c>
+      <c r="F16">
+        <v>7.410200000000001</v>
+      </c>
+      <c r="G16">
+        <v>12.5</v>
+      </c>
+      <c r="H16">
+        <v>51.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.98</v>
+      </c>
+      <c r="K16">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L16">
+        <v>2.27</v>
+      </c>
+      <c r="M16">
+        <v>0.3668049</v>
+      </c>
+      <c r="N16">
+        <v>1.9031951</v>
+      </c>
+      <c r="O16">
+        <v>0.4567668239999999</v>
+      </c>
+      <c r="P16">
+        <v>1.446428276</v>
+      </c>
+      <c r="Q16">
+        <v>9.156428276</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1225103871213054</v>
+      </c>
+      <c r="T16">
+        <v>1.317588909799039</v>
+      </c>
+      <c r="U16">
+        <v>0.0495</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.03762</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.188575997757934</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1105947474948748</v>
+      </c>
+      <c r="C17">
+        <v>45.98391547547044</v>
+      </c>
+      <c r="D17">
+        <v>41.42341547547044</v>
+      </c>
+      <c r="E17">
+        <v>6.1095</v>
+      </c>
+      <c r="F17">
+        <v>7.9395</v>
+      </c>
+      <c r="G17">
+        <v>12.5</v>
+      </c>
+      <c r="H17">
+        <v>51.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.98</v>
+      </c>
+      <c r="K17">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L17">
+        <v>2.27</v>
+      </c>
+      <c r="M17">
+        <v>0.40412055</v>
+      </c>
+      <c r="N17">
+        <v>1.86587945</v>
+      </c>
+      <c r="O17">
+        <v>0.4478110679999999</v>
+      </c>
+      <c r="P17">
+        <v>1.418068382</v>
+      </c>
+      <c r="Q17">
+        <v>9.128068382</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1232848794057351</v>
+      </c>
+      <c r="T17">
+        <v>1.329779301932941</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.038684</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.61713577792567</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.110414802065427</v>
+      </c>
+      <c r="C18">
+        <v>45.53046723978731</v>
+      </c>
+      <c r="D18">
+        <v>41.49926723978732</v>
+      </c>
+      <c r="E18">
+        <v>6.6388</v>
+      </c>
+      <c r="F18">
+        <v>8.4688</v>
+      </c>
+      <c r="G18">
+        <v>12.5</v>
+      </c>
+      <c r="H18">
+        <v>51.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.98</v>
+      </c>
+      <c r="K18">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L18">
+        <v>2.27</v>
+      </c>
+      <c r="M18">
+        <v>0.43106192</v>
+      </c>
+      <c r="N18">
+        <v>1.83893808</v>
+      </c>
+      <c r="O18">
+        <v>0.4413451391999999</v>
+      </c>
+      <c r="P18">
+        <v>1.3975929408</v>
+      </c>
+      <c r="Q18">
+        <v>9.1075929408</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1240778119826512</v>
+      </c>
+      <c r="T18">
+        <v>1.342259941498603</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.038684</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.266064791805316</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1102348566359792</v>
+      </c>
+      <c r="C19">
+        <v>45.07729730297522</v>
+      </c>
+      <c r="D19">
+        <v>41.57539730297522</v>
+      </c>
+      <c r="E19">
+        <v>7.168100000000001</v>
+      </c>
+      <c r="F19">
+        <v>8.998100000000001</v>
+      </c>
+      <c r="G19">
+        <v>12.5</v>
+      </c>
+      <c r="H19">
+        <v>51.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.98</v>
+      </c>
+      <c r="K19">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L19">
+        <v>2.27</v>
+      </c>
+      <c r="M19">
+        <v>0.4580032900000001</v>
+      </c>
+      <c r="N19">
+        <v>1.811996709999999</v>
+      </c>
+      <c r="O19">
+        <v>0.4348792103999998</v>
+      </c>
+      <c r="P19">
+        <v>1.3771174996</v>
+      </c>
+      <c r="Q19">
+        <v>9.0871174996</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1248898513686496</v>
+      </c>
+      <c r="T19">
+        <v>1.355041319367052</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.038684</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.956296274640296</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1100549112065313</v>
+      </c>
+      <c r="C20">
+        <v>44.62440719945998</v>
+      </c>
+      <c r="D20">
+        <v>41.65180719945998</v>
+      </c>
+      <c r="E20">
+        <v>7.6974</v>
+      </c>
+      <c r="F20">
+        <v>9.5274</v>
+      </c>
+      <c r="G20">
+        <v>12.5</v>
+      </c>
+      <c r="H20">
+        <v>51.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.98</v>
+      </c>
+      <c r="K20">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L20">
+        <v>2.27</v>
+      </c>
+      <c r="M20">
+        <v>0.48494466</v>
+      </c>
+      <c r="N20">
+        <v>1.78505534</v>
+      </c>
+      <c r="O20">
+        <v>0.4284132815999999</v>
+      </c>
+      <c r="P20">
+        <v>1.3566420584</v>
+      </c>
+      <c r="Q20">
+        <v>9.066642058400001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1257216965933309</v>
+      </c>
+      <c r="T20">
+        <v>1.368134438159121</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.038684</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.680946481604725</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1102504057770835</v>
+      </c>
+      <c r="C21">
+        <v>44.01210785678252</v>
+      </c>
+      <c r="D21">
+        <v>41.56880785678252</v>
+      </c>
+      <c r="E21">
+        <v>8.226699999999999</v>
+      </c>
+      <c r="F21">
+        <v>10.0567</v>
+      </c>
+      <c r="G21">
+        <v>12.5</v>
+      </c>
+      <c r="H21">
+        <v>51.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.98</v>
+      </c>
+      <c r="K21">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L21">
+        <v>2.27</v>
+      </c>
+      <c r="M21">
+        <v>0.5380334499999999</v>
+      </c>
+      <c r="N21">
+        <v>1.73196655</v>
+      </c>
+      <c r="O21">
+        <v>0.4156719719999999</v>
+      </c>
+      <c r="P21">
+        <v>1.316294578</v>
+      </c>
+      <c r="Q21">
+        <v>9.026294578</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1265740812062759</v>
+      </c>
+      <c r="T21">
+        <v>1.381550843834946</v>
+      </c>
+      <c r="U21">
+        <v>0.0535</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.04066</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.219068535608706</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1100902203476357</v>
+      </c>
+      <c r="C22">
+        <v>43.55079180328501</v>
+      </c>
+      <c r="D22">
+        <v>41.63679180328501</v>
+      </c>
+      <c r="E22">
+        <v>8.756</v>
+      </c>
+      <c r="F22">
+        <v>10.586</v>
+      </c>
+      <c r="G22">
+        <v>12.5</v>
+      </c>
+      <c r="H22">
+        <v>51.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.98</v>
+      </c>
+      <c r="K22">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L22">
+        <v>2.27</v>
+      </c>
+      <c r="M22">
+        <v>0.566351</v>
+      </c>
+      <c r="N22">
+        <v>1.703649</v>
+      </c>
+      <c r="O22">
+        <v>0.4088757599999999</v>
+      </c>
+      <c r="P22">
+        <v>1.29477324</v>
+      </c>
+      <c r="Q22">
+        <v>9.00477324</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1274477754345446</v>
+      </c>
+      <c r="T22">
+        <v>1.395302659652666</v>
+      </c>
+      <c r="U22">
+        <v>0.0535</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.04066</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.008115108828269</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1103609549181879</v>
+      </c>
+      <c r="C23">
+        <v>42.9067192685146</v>
+      </c>
+      <c r="D23">
+        <v>41.5220192685146</v>
+      </c>
+      <c r="E23">
+        <v>9.285299999999999</v>
+      </c>
+      <c r="F23">
+        <v>11.1153</v>
+      </c>
+      <c r="G23">
+        <v>12.5</v>
+      </c>
+      <c r="H23">
+        <v>51.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.98</v>
+      </c>
+      <c r="K23">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L23">
+        <v>2.27</v>
+      </c>
+      <c r="M23">
+        <v>0.62467986</v>
+      </c>
+      <c r="N23">
+        <v>1.645320139999999</v>
+      </c>
+      <c r="O23">
+        <v>0.3948768335999999</v>
+      </c>
+      <c r="P23">
+        <v>1.2504433064</v>
+      </c>
+      <c r="Q23">
+        <v>8.9604433064</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1283435885040353</v>
+      </c>
+      <c r="T23">
+        <v>1.409402622706277</v>
+      </c>
+      <c r="U23">
+        <v>0.0562</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.042712</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.633861350996652</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1110071294887401</v>
+      </c>
+      <c r="C24">
+        <v>42.10602703415577</v>
+      </c>
+      <c r="D24">
+        <v>41.25062703415577</v>
+      </c>
+      <c r="E24">
+        <v>9.8146</v>
+      </c>
+      <c r="F24">
+        <v>11.6446</v>
+      </c>
+      <c r="G24">
+        <v>12.5</v>
+      </c>
+      <c r="H24">
+        <v>51.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.98</v>
+      </c>
+      <c r="K24">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L24">
+        <v>2.27</v>
+      </c>
+      <c r="M24">
+        <v>0.70915614</v>
+      </c>
+      <c r="N24">
+        <v>1.560843859999999</v>
+      </c>
+      <c r="O24">
+        <v>0.3746025263999999</v>
+      </c>
+      <c r="P24">
+        <v>1.1862413336</v>
+      </c>
+      <c r="Q24">
+        <v>8.896241333600001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1292623711394103</v>
+      </c>
+      <c r="T24">
+        <v>1.423864123274084</v>
+      </c>
+      <c r="U24">
+        <v>0.0609</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.04628400000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.200987585047208</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1109031840592922</v>
+      </c>
+      <c r="C25">
+        <v>41.62014424340767</v>
+      </c>
+      <c r="D25">
+        <v>41.29404424340766</v>
+      </c>
+      <c r="E25">
+        <v>10.3439</v>
+      </c>
+      <c r="F25">
+        <v>12.1739</v>
+      </c>
+      <c r="G25">
+        <v>12.5</v>
+      </c>
+      <c r="H25">
+        <v>51.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.98</v>
+      </c>
+      <c r="K25">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L25">
+        <v>2.27</v>
+      </c>
+      <c r="M25">
+        <v>0.74139051</v>
+      </c>
+      <c r="N25">
+        <v>1.52860949</v>
+      </c>
+      <c r="O25">
+        <v>0.3668662775999999</v>
+      </c>
+      <c r="P25">
+        <v>1.1617432124</v>
+      </c>
+      <c r="Q25">
+        <v>8.8717432124</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1302050182588211</v>
+      </c>
+      <c r="T25">
+        <v>1.438701247233263</v>
+      </c>
+      <c r="U25">
+        <v>0.0609</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.04628400000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.061814211784286</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1124955586298444</v>
+      </c>
+      <c r="C26">
+        <v>40.43558686358647</v>
+      </c>
+      <c r="D26">
+        <v>40.63878686358646</v>
+      </c>
+      <c r="E26">
+        <v>10.8732</v>
+      </c>
+      <c r="F26">
+        <v>12.7032</v>
+      </c>
+      <c r="G26">
+        <v>12.5</v>
+      </c>
+      <c r="H26">
+        <v>51.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.98</v>
+      </c>
+      <c r="K26">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L26">
+        <v>2.27</v>
+      </c>
+      <c r="M26">
+        <v>0.8917646399999999</v>
+      </c>
+      <c r="N26">
+        <v>1.37823536</v>
+      </c>
+      <c r="O26">
+        <v>0.3307764863999999</v>
+      </c>
+      <c r="P26">
+        <v>1.0474588736</v>
+      </c>
+      <c r="Q26">
+        <v>8.757458873600001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1311724718813742</v>
+      </c>
+      <c r="T26">
+        <v>1.453928821822946</v>
+      </c>
+      <c r="U26">
+        <v>0.0702</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.053352</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.545514699932484</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1133552932003966</v>
+      </c>
+      <c r="C27">
+        <v>39.56107992728515</v>
+      </c>
+      <c r="D27">
+        <v>40.29357992728515</v>
+      </c>
+      <c r="E27">
+        <v>11.4025</v>
+      </c>
+      <c r="F27">
+        <v>13.2325</v>
+      </c>
+      <c r="G27">
+        <v>12.5</v>
+      </c>
+      <c r="H27">
+        <v>51.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.98</v>
+      </c>
+      <c r="K27">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L27">
+        <v>2.27</v>
+      </c>
+      <c r="M27">
+        <v>0.99111425</v>
+      </c>
+      <c r="N27">
+        <v>1.27888575</v>
+      </c>
+      <c r="O27">
+        <v>0.3069325799999999</v>
+      </c>
+      <c r="P27">
+        <v>0.9719531699999998</v>
+      </c>
+      <c r="Q27">
+        <v>8.68195317</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1321657242671955</v>
+      </c>
+      <c r="T27">
+        <v>1.469562465068354</v>
+      </c>
+      <c r="U27">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.056924</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.290351490759011</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1133577477709488</v>
+      </c>
+      <c r="C28">
+        <v>39.03080274580002</v>
+      </c>
+      <c r="D28">
+        <v>40.29260274580002</v>
+      </c>
+      <c r="E28">
+        <v>11.9318</v>
+      </c>
+      <c r="F28">
+        <v>13.7618</v>
+      </c>
+      <c r="G28">
+        <v>12.5</v>
+      </c>
+      <c r="H28">
+        <v>51.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.98</v>
+      </c>
+      <c r="K28">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L28">
+        <v>2.27</v>
+      </c>
+      <c r="M28">
+        <v>1.03075882</v>
+      </c>
+      <c r="N28">
+        <v>1.23924118</v>
+      </c>
+      <c r="O28">
+        <v>0.2974178831999999</v>
+      </c>
+      <c r="P28">
+        <v>0.9418232967999998</v>
+      </c>
+      <c r="Q28">
+        <v>8.6518232968</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1331858213120929</v>
+      </c>
+      <c r="T28">
+        <v>1.485618639212286</v>
+      </c>
+      <c r="U28">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.056924</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.202261048806742</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1133602023415009</v>
+      </c>
+      <c r="C29">
+        <v>38.50052561171007</v>
+      </c>
+      <c r="D29">
+        <v>40.29162561171007</v>
+      </c>
+      <c r="E29">
+        <v>12.4611</v>
+      </c>
+      <c r="F29">
+        <v>14.2911</v>
+      </c>
+      <c r="G29">
+        <v>12.5</v>
+      </c>
+      <c r="H29">
+        <v>51.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.98</v>
+      </c>
+      <c r="K29">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L29">
+        <v>2.27</v>
+      </c>
+      <c r="M29">
+        <v>1.07040339</v>
+      </c>
+      <c r="N29">
+        <v>1.19959661</v>
+      </c>
+      <c r="O29">
+        <v>0.2879031863999999</v>
+      </c>
+      <c r="P29">
+        <v>0.9116934235999998</v>
+      </c>
+      <c r="Q29">
+        <v>8.6216934236</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1342338662212342</v>
+      </c>
+      <c r="T29">
+        <v>1.502114708538244</v>
+      </c>
+      <c r="U29">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.056924</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.120695824776863</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1133626569120531</v>
+      </c>
+      <c r="C30">
+        <v>37.97024852501183</v>
+      </c>
+      <c r="D30">
+        <v>40.29064852501183</v>
+      </c>
+      <c r="E30">
+        <v>12.9904</v>
+      </c>
+      <c r="F30">
+        <v>14.8204</v>
+      </c>
+      <c r="G30">
+        <v>12.5</v>
+      </c>
+      <c r="H30">
+        <v>51.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.98</v>
+      </c>
+      <c r="K30">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L30">
+        <v>2.27</v>
+      </c>
+      <c r="M30">
+        <v>1.11004796</v>
+      </c>
+      <c r="N30">
+        <v>1.15995204</v>
+      </c>
+      <c r="O30">
+        <v>0.2783884895999999</v>
+      </c>
+      <c r="P30">
+        <v>0.8815635503999997</v>
+      </c>
+      <c r="Q30">
+        <v>8.5915635504</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1353110234889627</v>
+      </c>
+      <c r="T30">
+        <v>1.519069002012146</v>
+      </c>
+      <c r="U30">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.056924</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.044956688177689</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1169576314826053</v>
+      </c>
+      <c r="C31">
+        <v>36.05902007177983</v>
+      </c>
+      <c r="D31">
+        <v>38.90872007177983</v>
+      </c>
+      <c r="E31">
+        <v>13.5197</v>
+      </c>
+      <c r="F31">
+        <v>15.3497</v>
+      </c>
+      <c r="G31">
+        <v>12.5</v>
+      </c>
+      <c r="H31">
+        <v>51.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.98</v>
+      </c>
+      <c r="K31">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L31">
+        <v>2.27</v>
+      </c>
+      <c r="M31">
+        <v>1.39989264</v>
+      </c>
+      <c r="N31">
+        <v>0.8701073599999996</v>
+      </c>
+      <c r="O31">
+        <v>0.2088257663999999</v>
+      </c>
+      <c r="P31">
+        <v>0.6612815935999996</v>
+      </c>
+      <c r="Q31">
+        <v>8.371281593600001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1364185232149371</v>
+      </c>
+      <c r="T31">
+        <v>1.536500881217707</v>
+      </c>
+      <c r="U31">
+        <v>0.0912</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.069312</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.621552921372599</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1170839660531575</v>
+      </c>
+      <c r="C32">
+        <v>35.4828784981955</v>
+      </c>
+      <c r="D32">
+        <v>38.86187849819549</v>
+      </c>
+      <c r="E32">
+        <v>14.049</v>
+      </c>
+      <c r="F32">
+        <v>15.879</v>
+      </c>
+      <c r="G32">
+        <v>12.5</v>
+      </c>
+      <c r="H32">
+        <v>51.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.98</v>
+      </c>
+      <c r="K32">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L32">
+        <v>2.27</v>
+      </c>
+      <c r="M32">
+        <v>1.4481648</v>
+      </c>
+      <c r="N32">
+        <v>0.8218351999999995</v>
+      </c>
+      <c r="O32">
+        <v>0.1972404479999999</v>
+      </c>
+      <c r="P32">
+        <v>0.6245947519999997</v>
+      </c>
+      <c r="Q32">
+        <v>8.334594752000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.137557665790225</v>
+      </c>
+      <c r="T32">
+        <v>1.554430814114854</v>
+      </c>
+      <c r="U32">
+        <v>0.0912</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.069312</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.567501157326845</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1172103006237097</v>
+      </c>
+      <c r="C33">
+        <v>34.9068495726092</v>
+      </c>
+      <c r="D33">
+        <v>38.8151495726092</v>
+      </c>
+      <c r="E33">
+        <v>14.5783</v>
+      </c>
+      <c r="F33">
+        <v>16.4083</v>
+      </c>
+      <c r="G33">
+        <v>12.5</v>
+      </c>
+      <c r="H33">
+        <v>51.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.98</v>
+      </c>
+      <c r="K33">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L33">
+        <v>2.27</v>
+      </c>
+      <c r="M33">
+        <v>1.49643696</v>
+      </c>
+      <c r="N33">
+        <v>0.7735630399999995</v>
+      </c>
+      <c r="O33">
+        <v>0.1856551295999999</v>
+      </c>
+      <c r="P33">
+        <v>0.5879079103999997</v>
+      </c>
+      <c r="Q33">
+        <v>8.297907910400001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1387298269908836</v>
+      </c>
+      <c r="T33">
+        <v>1.57288045521192</v>
+      </c>
+      <c r="U33">
+        <v>0.0912</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.069312</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>1.516936603864689</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1358008309611394</v>
+      </c>
+      <c r="C34">
+        <v>28.54205482284368</v>
+      </c>
+      <c r="D34">
+        <v>32.97965482284368</v>
+      </c>
+      <c r="E34">
+        <v>15.1076</v>
+      </c>
+      <c r="F34">
+        <v>16.9376</v>
+      </c>
+      <c r="G34">
+        <v>12.5</v>
+      </c>
+      <c r="H34">
+        <v>51.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.98</v>
+      </c>
+      <c r="K34">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L34">
+        <v>2.27</v>
+      </c>
+      <c r="M34">
+        <v>2.65242816</v>
+      </c>
+      <c r="N34">
+        <v>-0.3824281600000008</v>
+      </c>
+      <c r="O34">
+        <v>-0.09178275840000019</v>
+      </c>
+      <c r="P34">
+        <v>-0.2906454016000006</v>
+      </c>
+      <c r="Q34">
+        <v>7.4193545984</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1411495155303095</v>
+      </c>
+      <c r="T34">
+        <v>1.610965989090713</v>
+      </c>
+      <c r="U34">
+        <v>0.1566</v>
+      </c>
+      <c r="V34">
+        <v>0.2053967033738625</v>
+      </c>
+      <c r="W34">
+        <v>0.1244348762516532</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8558195973910936</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1369788309611394</v>
+      </c>
+      <c r="C35">
+        <v>27.70154138248538</v>
+      </c>
+      <c r="D35">
+        <v>32.66844138248538</v>
+      </c>
+      <c r="E35">
+        <v>15.6369</v>
+      </c>
+      <c r="F35">
+        <v>17.4669</v>
+      </c>
+      <c r="G35">
+        <v>12.5</v>
+      </c>
+      <c r="H35">
+        <v>51.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.98</v>
+      </c>
+      <c r="K35">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L35">
+        <v>2.27</v>
+      </c>
+      <c r="M35">
+        <v>2.73531654</v>
+      </c>
+      <c r="N35">
+        <v>-0.4653165400000008</v>
+      </c>
+      <c r="O35">
+        <v>-0.1116759696000002</v>
+      </c>
+      <c r="P35">
+        <v>-0.3536405704000006</v>
+      </c>
+      <c r="Q35">
+        <v>7.3563594296</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1426771202397171</v>
+      </c>
+      <c r="T35">
+        <v>1.635010257584604</v>
+      </c>
+      <c r="U35">
+        <v>0.1566</v>
+      </c>
+      <c r="V35">
+        <v>0.1991725608473818</v>
+      </c>
+      <c r="W35">
+        <v>0.1254095769713</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.8298856701974241</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1381568309611394</v>
+      </c>
+      <c r="C36">
+        <v>26.86684658312462</v>
+      </c>
+      <c r="D36">
+        <v>32.36304658312462</v>
+      </c>
+      <c r="E36">
+        <v>16.1662</v>
+      </c>
+      <c r="F36">
+        <v>17.9962</v>
+      </c>
+      <c r="G36">
+        <v>12.5</v>
+      </c>
+      <c r="H36">
+        <v>51.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.98</v>
+      </c>
+      <c r="K36">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L36">
+        <v>2.27</v>
+      </c>
+      <c r="M36">
+        <v>2.818204920000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.5482049200000012</v>
+      </c>
+      <c r="O36">
+        <v>-0.1315691808000003</v>
+      </c>
+      <c r="P36">
+        <v>-0.4166357392000009</v>
+      </c>
+      <c r="Q36">
+        <v>7.2933642608</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1442510160009249</v>
+      </c>
+      <c r="T36">
+        <v>1.65978314027528</v>
+      </c>
+      <c r="U36">
+        <v>0.1566</v>
+      </c>
+      <c r="V36">
+        <v>0.1933145443518705</v>
+      </c>
+      <c r="W36">
+        <v>0.1263269423544971</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.8054772681327939</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1588288955551349</v>
+      </c>
+      <c r="C37">
+        <v>21.77665051814262</v>
+      </c>
+      <c r="D37">
+        <v>27.80215051814263</v>
+      </c>
+      <c r="E37">
+        <v>16.6955</v>
+      </c>
+      <c r="F37">
+        <v>18.5255</v>
+      </c>
+      <c r="G37">
+        <v>12.5</v>
+      </c>
+      <c r="H37">
+        <v>51.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.98</v>
+      </c>
+      <c r="K37">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L37">
+        <v>2.27</v>
+      </c>
+      <c r="M37">
+        <v>3.868124400000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.598124400000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.3835498560000002</v>
+      </c>
+      <c r="P37">
+        <v>-1.214574544000001</v>
+      </c>
+      <c r="Q37">
+        <v>6.495425456</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1477565156224706</v>
+      </c>
+      <c r="T37">
+        <v>1.714959177365637</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.1408434537420771</v>
+      </c>
+      <c r="W37">
+        <v>0.1793918868586543</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5868477239253214</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1605288955551349</v>
+      </c>
+      <c r="C38">
+        <v>20.92882816942736</v>
+      </c>
+      <c r="D38">
+        <v>27.48362816942736</v>
+      </c>
+      <c r="E38">
+        <v>17.2248</v>
+      </c>
+      <c r="F38">
+        <v>19.0548</v>
+      </c>
+      <c r="G38">
+        <v>12.5</v>
+      </c>
+      <c r="H38">
+        <v>51.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.98</v>
+      </c>
+      <c r="K38">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L38">
+        <v>2.27</v>
+      </c>
+      <c r="M38">
+        <v>3.97864224</v>
+      </c>
+      <c r="N38">
+        <v>-1.708642240000001</v>
+      </c>
+      <c r="O38">
+        <v>-0.4100741376000001</v>
+      </c>
+      <c r="P38">
+        <v>-1.2985681024</v>
+      </c>
+      <c r="Q38">
+        <v>6.4114318976</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1494589611790716</v>
+      </c>
+      <c r="T38">
+        <v>1.741755414511975</v>
+      </c>
+      <c r="U38">
+        <v>0.2088</v>
+      </c>
+      <c r="V38">
+        <v>0.136931135582575</v>
+      </c>
+      <c r="W38">
+        <v>0.1802087788903584</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5705463982607292</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1622288955551349</v>
+      </c>
+      <c r="C39">
+        <v>20.08822161438184</v>
+      </c>
+      <c r="D39">
+        <v>27.17232161438185</v>
+      </c>
+      <c r="E39">
+        <v>17.7541</v>
+      </c>
+      <c r="F39">
+        <v>19.5841</v>
+      </c>
+      <c r="G39">
+        <v>12.5</v>
+      </c>
+      <c r="H39">
+        <v>51.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.98</v>
+      </c>
+      <c r="K39">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L39">
+        <v>2.27</v>
+      </c>
+      <c r="M39">
+        <v>4.08916008</v>
+      </c>
+      <c r="N39">
+        <v>-1.819160080000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.4365984192000001</v>
+      </c>
+      <c r="P39">
+        <v>-1.3825616608</v>
+      </c>
+      <c r="Q39">
+        <v>6.3274383392</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1512154526263585</v>
+      </c>
+      <c r="T39">
+        <v>1.769402325853435</v>
+      </c>
+      <c r="U39">
+        <v>0.2088</v>
+      </c>
+      <c r="V39">
+        <v>0.1332302940803432</v>
+      </c>
+      <c r="W39">
+        <v>0.1809815145960244</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5551262253347635</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1639288955551348</v>
+      </c>
+      <c r="C40">
+        <v>19.25458839977948</v>
+      </c>
+      <c r="D40">
+        <v>26.86798839977948</v>
+      </c>
+      <c r="E40">
+        <v>18.2834</v>
+      </c>
+      <c r="F40">
+        <v>20.1134</v>
+      </c>
+      <c r="G40">
+        <v>12.5</v>
+      </c>
+      <c r="H40">
+        <v>51.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.98</v>
+      </c>
+      <c r="K40">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L40">
+        <v>2.27</v>
+      </c>
+      <c r="M40">
+        <v>4.19967792</v>
+      </c>
+      <c r="N40">
+        <v>-1.92967792</v>
+      </c>
+      <c r="O40">
+        <v>-0.4631227008000001</v>
+      </c>
+      <c r="P40">
+        <v>-1.4665552192</v>
+      </c>
+      <c r="Q40">
+        <v>6.243444780800001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1530286050880739</v>
+      </c>
+      <c r="T40">
+        <v>1.797941073044619</v>
+      </c>
+      <c r="U40">
+        <v>0.2088</v>
+      </c>
+      <c r="V40">
+        <v>0.1297242337098079</v>
+      </c>
+      <c r="W40">
+        <v>0.1817135800013921</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5405176404575329</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1656288955551349</v>
+      </c>
+      <c r="C41">
+        <v>18.4276968141044</v>
+      </c>
+      <c r="D41">
+        <v>26.57039681410441</v>
+      </c>
+      <c r="E41">
+        <v>18.8127</v>
+      </c>
+      <c r="F41">
+        <v>20.6427</v>
+      </c>
+      <c r="G41">
+        <v>12.5</v>
+      </c>
+      <c r="H41">
+        <v>51.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.98</v>
+      </c>
+      <c r="K41">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L41">
+        <v>2.27</v>
+      </c>
+      <c r="M41">
+        <v>4.310195760000001</v>
+      </c>
+      <c r="N41">
+        <v>-2.040195760000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.4896469824000003</v>
+      </c>
+      <c r="P41">
+        <v>-1.550548777600001</v>
+      </c>
+      <c r="Q41">
+        <v>6.1594512224</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.154901205171485</v>
+      </c>
+      <c r="T41">
+        <v>1.827415516865023</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.1263979713069923</v>
+      </c>
+      <c r="W41">
+        <v>0.1824081035911</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5266582137791345</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1673288955551349</v>
+      </c>
+      <c r="C42">
+        <v>17.60732529918888</v>
+      </c>
+      <c r="D42">
+        <v>26.27932529918888</v>
+      </c>
+      <c r="E42">
+        <v>19.342</v>
+      </c>
+      <c r="F42">
+        <v>21.172</v>
+      </c>
+      <c r="G42">
+        <v>12.5</v>
+      </c>
+      <c r="H42">
+        <v>51.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.98</v>
+      </c>
+      <c r="K42">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L42">
+        <v>2.27</v>
+      </c>
+      <c r="M42">
+        <v>4.4207136</v>
+      </c>
+      <c r="N42">
+        <v>-2.1507136</v>
+      </c>
+      <c r="O42">
+        <v>-0.5161712640000001</v>
+      </c>
+      <c r="P42">
+        <v>-1.634542336</v>
+      </c>
+      <c r="Q42">
+        <v>6.075457664</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1568362252576764</v>
+      </c>
+      <c r="T42">
+        <v>1.857872442146107</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.1232380220243175</v>
+      </c>
+      <c r="W42">
+        <v>0.1830679010013225</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5134917584346562</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1690288955551348</v>
+      </c>
+      <c r="C43">
+        <v>16.79326190010361</v>
+      </c>
+      <c r="D43">
+        <v>25.99456190010361</v>
+      </c>
+      <c r="E43">
+        <v>19.8713</v>
+      </c>
+      <c r="F43">
+        <v>21.7013</v>
+      </c>
+      <c r="G43">
+        <v>12.5</v>
+      </c>
+      <c r="H43">
+        <v>51.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.98</v>
+      </c>
+      <c r="K43">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L43">
+        <v>2.27</v>
+      </c>
+      <c r="M43">
+        <v>4.53123144</v>
+      </c>
+      <c r="N43">
+        <v>-2.26123144</v>
+      </c>
+      <c r="O43">
+        <v>-0.5426955456000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.7185358944</v>
+      </c>
+      <c r="Q43">
+        <v>5.9914641056</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1588368392450946</v>
+      </c>
+      <c r="T43">
+        <v>1.889361805572312</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.1202322166090902</v>
+      </c>
+      <c r="W43">
+        <v>0.183695513172022</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5009675692045427</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1837902264322688</v>
+      </c>
+      <c r="C44">
+        <v>14.02845641461301</v>
+      </c>
+      <c r="D44">
+        <v>23.75905641461301</v>
+      </c>
+      <c r="E44">
+        <v>20.4006</v>
+      </c>
+      <c r="F44">
+        <v>22.2306</v>
+      </c>
+      <c r="G44">
+        <v>12.5</v>
+      </c>
+      <c r="H44">
+        <v>51.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.98</v>
+      </c>
+      <c r="K44">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L44">
+        <v>2.27</v>
+      </c>
+      <c r="M44">
+        <v>5.30866728</v>
+      </c>
+      <c r="N44">
+        <v>-3.03866728</v>
+      </c>
+      <c r="O44">
+        <v>-0.7292801472</v>
+      </c>
+      <c r="P44">
+        <v>-2.3093871328</v>
+      </c>
+      <c r="Q44">
+        <v>5.4006128672</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1617018379857583</v>
+      </c>
+      <c r="T44">
+        <v>1.934456455078787</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1026246270984984</v>
+      </c>
+      <c r="W44">
+        <v>0.2142932390488786</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4276026129104101</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1857902264322688</v>
+      </c>
+      <c r="C45">
+        <v>13.22550619938491</v>
+      </c>
+      <c r="D45">
+        <v>23.4854061993849</v>
+      </c>
+      <c r="E45">
+        <v>20.9299</v>
+      </c>
+      <c r="F45">
+        <v>22.7599</v>
+      </c>
+      <c r="G45">
+        <v>12.5</v>
+      </c>
+      <c r="H45">
+        <v>51.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.98</v>
+      </c>
+      <c r="K45">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L45">
+        <v>2.27</v>
+      </c>
+      <c r="M45">
+        <v>5.43506412</v>
+      </c>
+      <c r="N45">
+        <v>-3.16506412</v>
+      </c>
+      <c r="O45">
+        <v>-0.7596153888</v>
+      </c>
+      <c r="P45">
+        <v>-2.4054487312</v>
+      </c>
+      <c r="Q45">
+        <v>5.304551268800001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1638580105819996</v>
+      </c>
+      <c r="T45">
+        <v>1.968394287624029</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1002380078636496</v>
+      </c>
+      <c r="W45">
+        <v>0.2148631637221605</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4176583660985401</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1877902264322688</v>
+      </c>
+      <c r="C46">
+        <v>12.4287878615269</v>
+      </c>
+      <c r="D46">
+        <v>23.2179878615269</v>
+      </c>
+      <c r="E46">
+        <v>21.4592</v>
+      </c>
+      <c r="F46">
+        <v>23.2892</v>
+      </c>
+      <c r="G46">
+        <v>12.5</v>
+      </c>
+      <c r="H46">
+        <v>51.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.98</v>
+      </c>
+      <c r="K46">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L46">
+        <v>2.27</v>
+      </c>
+      <c r="M46">
+        <v>5.561460960000001</v>
+      </c>
+      <c r="N46">
+        <v>-3.291460960000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.7899506304000002</v>
+      </c>
+      <c r="P46">
+        <v>-2.501510329600001</v>
+      </c>
+      <c r="Q46">
+        <v>5.208489670400001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1660911893423925</v>
+      </c>
+      <c r="T46">
+        <v>2.003544185617315</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.09795987132129394</v>
+      </c>
+      <c r="W46">
+        <v>0.215407182728475</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4081661305053914</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1897902264322688</v>
+      </c>
+      <c r="C47">
+        <v>11.63809091849802</v>
+      </c>
+      <c r="D47">
+        <v>22.95659091849802</v>
+      </c>
+      <c r="E47">
+        <v>21.9885</v>
+      </c>
+      <c r="F47">
+        <v>23.8185</v>
+      </c>
+      <c r="G47">
+        <v>12.5</v>
+      </c>
+      <c r="H47">
+        <v>51.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.98</v>
+      </c>
+      <c r="K47">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L47">
+        <v>2.27</v>
+      </c>
+      <c r="M47">
+        <v>5.687857800000001</v>
+      </c>
+      <c r="N47">
+        <v>-3.417857800000001</v>
+      </c>
+      <c r="O47">
+        <v>-0.8202858720000002</v>
+      </c>
+      <c r="P47">
+        <v>-2.597571928000001</v>
+      </c>
+      <c r="Q47">
+        <v>5.112428072</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1684055746031632</v>
+      </c>
+      <c r="T47">
+        <v>2.039972261719448</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.09578298529193184</v>
+      </c>
+      <c r="W47">
+        <v>0.2159270231122867</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.399095772049716</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1917902264322688</v>
+      </c>
+      <c r="C48">
+        <v>10.85321426099992</v>
+      </c>
+      <c r="D48">
+        <v>22.70101426099992</v>
+      </c>
+      <c r="E48">
+        <v>22.5178</v>
+      </c>
+      <c r="F48">
+        <v>24.3478</v>
+      </c>
+      <c r="G48">
+        <v>12.5</v>
+      </c>
+      <c r="H48">
+        <v>51.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.98</v>
+      </c>
+      <c r="K48">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L48">
+        <v>2.27</v>
+      </c>
+      <c r="M48">
+        <v>5.814254640000001</v>
+      </c>
+      <c r="N48">
+        <v>-3.544254640000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.8506211136000003</v>
+      </c>
+      <c r="P48">
+        <v>-2.693633526400001</v>
+      </c>
+      <c r="Q48">
+        <v>5.0163664736</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1708056778365552</v>
+      </c>
+      <c r="T48">
+        <v>2.077749525825364</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.09370074648123768</v>
+      </c>
+      <c r="W48">
+        <v>0.2164242617402805</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.390419777005157</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1937902264322688</v>
+      </c>
+      <c r="C49">
+        <v>10.07396563695833</v>
+      </c>
+      <c r="D49">
+        <v>22.45106563695834</v>
+      </c>
+      <c r="E49">
+        <v>23.0471</v>
+      </c>
+      <c r="F49">
+        <v>24.8771</v>
+      </c>
+      <c r="G49">
+        <v>12.5</v>
+      </c>
+      <c r="H49">
+        <v>51.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.98</v>
+      </c>
+      <c r="K49">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L49">
+        <v>2.27</v>
+      </c>
+      <c r="M49">
+        <v>5.940651480000001</v>
+      </c>
+      <c r="N49">
+        <v>-3.670651480000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.8809563552000002</v>
+      </c>
+      <c r="P49">
+        <v>-2.789695124800001</v>
+      </c>
+      <c r="Q49">
+        <v>4.9203048752</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1732963510032826</v>
+      </c>
+      <c r="T49">
+        <v>2.116952347067351</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.09170711357738155</v>
+      </c>
+      <c r="W49">
+        <v>0.2169003412777213</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3821129732390898</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1957902264322688</v>
+      </c>
+      <c r="C50">
+        <v>9.300161169222797</v>
+      </c>
+      <c r="D50">
+        <v>22.20656116922279</v>
+      </c>
+      <c r="E50">
+        <v>23.5764</v>
+      </c>
+      <c r="F50">
+        <v>25.4064</v>
+      </c>
+      <c r="G50">
+        <v>12.5</v>
+      </c>
+      <c r="H50">
+        <v>51.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.98</v>
+      </c>
+      <c r="K50">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L50">
+        <v>2.27</v>
+      </c>
+      <c r="M50">
+        <v>6.06704832</v>
+      </c>
+      <c r="N50">
+        <v>-3.79704832</v>
+      </c>
+      <c r="O50">
+        <v>-0.9112915967999999</v>
+      </c>
+      <c r="P50">
+        <v>-2.8857567232</v>
+      </c>
+      <c r="Q50">
+        <v>4.824243276800001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1758828192918073</v>
+      </c>
+      <c r="T50">
+        <v>2.157662969126339</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.08979654871118611</v>
+      </c>
+      <c r="W50">
+        <v>0.2173565841677688</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3741522862966088</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1977902264322688</v>
+      </c>
+      <c r="C51">
+        <v>8.531624904442008</v>
+      </c>
+      <c r="D51">
+        <v>21.96732490444201</v>
+      </c>
+      <c r="E51">
+        <v>24.1057</v>
+      </c>
+      <c r="F51">
+        <v>25.9357</v>
+      </c>
+      <c r="G51">
+        <v>12.5</v>
+      </c>
+      <c r="H51">
+        <v>51.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.98</v>
+      </c>
+      <c r="K51">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L51">
+        <v>2.27</v>
+      </c>
+      <c r="M51">
+        <v>6.19344516</v>
+      </c>
+      <c r="N51">
+        <v>-3.923445160000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.9416268384000002</v>
+      </c>
+      <c r="P51">
+        <v>-2.9818183216</v>
+      </c>
+      <c r="Q51">
+        <v>4.7281816784</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1785707177092937</v>
+      </c>
+      <c r="T51">
+        <v>2.199970086168032</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.08796396608442721</v>
+      </c>
+      <c r="W51">
+        <v>0.2177942048990388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.36651652535178</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1997902264322688</v>
+      </c>
+      <c r="C52">
+        <v>7.768188390788755</v>
+      </c>
+      <c r="D52">
+        <v>21.73318839078876</v>
+      </c>
+      <c r="E52">
+        <v>24.635</v>
+      </c>
+      <c r="F52">
+        <v>26.465</v>
+      </c>
+      <c r="G52">
+        <v>12.5</v>
+      </c>
+      <c r="H52">
+        <v>51.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.98</v>
+      </c>
+      <c r="K52">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L52">
+        <v>2.27</v>
+      </c>
+      <c r="M52">
+        <v>6.319842</v>
+      </c>
+      <c r="N52">
+        <v>-4.049842000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.9719620800000002</v>
+      </c>
+      <c r="P52">
+        <v>-3.077879920000001</v>
+      </c>
+      <c r="Q52">
+        <v>4.63212008</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1813661320634796</v>
+      </c>
+      <c r="T52">
+        <v>2.243969487891393</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.08620468676273867</v>
+      </c>
+      <c r="W52">
+        <v>0.218214320801058</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3591861948447445</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2017902264322688</v>
+      </c>
+      <c r="C53">
+        <v>7.009690282404723</v>
+      </c>
+      <c r="D53">
+        <v>21.50399028240472</v>
+      </c>
+      <c r="E53">
+        <v>25.1643</v>
+      </c>
+      <c r="F53">
+        <v>26.9943</v>
+      </c>
+      <c r="G53">
+        <v>12.5</v>
+      </c>
+      <c r="H53">
+        <v>51.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.98</v>
+      </c>
+      <c r="K53">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L53">
+        <v>2.27</v>
+      </c>
+      <c r="M53">
+        <v>6.44623884</v>
+      </c>
+      <c r="N53">
+        <v>-4.176238840000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.0022973216</v>
+      </c>
+      <c r="P53">
+        <v>-3.1739415184</v>
+      </c>
+      <c r="Q53">
+        <v>4.5360584816</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1842756449627343</v>
+      </c>
+      <c r="T53">
+        <v>2.289764783562645</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.08451439878699869</v>
+      </c>
+      <c r="W53">
+        <v>0.2186179615696647</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3521433282791612</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2037902264322688</v>
+      </c>
+      <c r="C54">
+        <v>6.255975968613207</v>
+      </c>
+      <c r="D54">
+        <v>21.27957596861321</v>
+      </c>
+      <c r="E54">
+        <v>25.6936</v>
+      </c>
+      <c r="F54">
+        <v>27.5236</v>
+      </c>
+      <c r="G54">
+        <v>12.5</v>
+      </c>
+      <c r="H54">
+        <v>51.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.98</v>
+      </c>
+      <c r="K54">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L54">
+        <v>2.27</v>
+      </c>
+      <c r="M54">
+        <v>6.572635680000001</v>
+      </c>
+      <c r="N54">
+        <v>-4.302635680000002</v>
+      </c>
+      <c r="O54">
+        <v>-1.0326325632</v>
+      </c>
+      <c r="P54">
+        <v>-3.270003116800001</v>
+      </c>
+      <c r="Q54">
+        <v>4.439996883199999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1873063875661246</v>
+      </c>
+      <c r="T54">
+        <v>2.337468216553534</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0828891218872487</v>
+      </c>
+      <c r="W54">
+        <v>0.219006077693325</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3453713411968696</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2057902264322688</v>
+      </c>
+      <c r="C55">
+        <v>5.506897226109182</v>
+      </c>
+      <c r="D55">
+        <v>21.05979722610918</v>
+      </c>
+      <c r="E55">
+        <v>26.2229</v>
+      </c>
+      <c r="F55">
+        <v>28.0529</v>
+      </c>
+      <c r="G55">
+        <v>12.5</v>
+      </c>
+      <c r="H55">
+        <v>51.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.98</v>
+      </c>
+      <c r="K55">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L55">
+        <v>2.27</v>
+      </c>
+      <c r="M55">
+        <v>6.69903252</v>
+      </c>
+      <c r="N55">
+        <v>-4.429032520000001</v>
+      </c>
+      <c r="O55">
+        <v>-1.0629678048</v>
+      </c>
+      <c r="P55">
+        <v>-3.3660647152</v>
+      </c>
+      <c r="Q55">
+        <v>4.343935284800001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1904660979398719</v>
+      </c>
+      <c r="T55">
+        <v>2.387201582863184</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.08132517619126288</v>
+      </c>
+      <c r="W55">
+        <v>0.2193795479255264</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3388549007969287</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2077902264322688</v>
+      </c>
+      <c r="C56">
+        <v>4.762311892482373</v>
+      </c>
+      <c r="D56">
+        <v>20.84451189248237</v>
+      </c>
+      <c r="E56">
+        <v>26.7522</v>
+      </c>
+      <c r="F56">
+        <v>28.5822</v>
+      </c>
+      <c r="G56">
+        <v>12.5</v>
+      </c>
+      <c r="H56">
+        <v>51.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.98</v>
+      </c>
+      <c r="K56">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L56">
+        <v>2.27</v>
+      </c>
+      <c r="M56">
+        <v>6.82542936</v>
+      </c>
+      <c r="N56">
+        <v>-4.555429360000001</v>
+      </c>
+      <c r="O56">
+        <v>-1.0933030464</v>
+      </c>
+      <c r="P56">
+        <v>-3.462126313600001</v>
+      </c>
+      <c r="Q56">
+        <v>4.2478736864</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1937631870255213</v>
+      </c>
+      <c r="T56">
+        <v>2.439097269447166</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.07981915440994321</v>
+      </c>
+      <c r="W56">
+        <v>0.2197391859269056</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.33257981004143</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2097902264322688</v>
+      </c>
+      <c r="C57">
+        <v>4.022083559562329</v>
+      </c>
+      <c r="D57">
+        <v>20.63358355956233</v>
+      </c>
+      <c r="E57">
+        <v>27.2815</v>
+      </c>
+      <c r="F57">
+        <v>29.1115</v>
+      </c>
+      <c r="G57">
+        <v>12.5</v>
+      </c>
+      <c r="H57">
+        <v>51.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.98</v>
+      </c>
+      <c r="K57">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L57">
+        <v>2.27</v>
+      </c>
+      <c r="M57">
+        <v>6.951826200000001</v>
+      </c>
+      <c r="N57">
+        <v>-4.681826200000001</v>
+      </c>
+      <c r="O57">
+        <v>-1.123638288</v>
+      </c>
+      <c r="P57">
+        <v>-3.558187912000001</v>
+      </c>
+      <c r="Q57">
+        <v>4.151812088</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1972068134038663</v>
+      </c>
+      <c r="T57">
+        <v>2.493299430990437</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.07836789705703515</v>
+      </c>
+      <c r="W57">
+        <v>0.22008574618278</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3265329044043132</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2117902264322688</v>
+      </c>
+      <c r="C58">
+        <v>3.286081285195547</v>
+      </c>
+      <c r="D58">
+        <v>20.42688128519555</v>
+      </c>
+      <c r="E58">
+        <v>27.8108</v>
+      </c>
+      <c r="F58">
+        <v>29.6408</v>
+      </c>
+      <c r="G58">
+        <v>12.5</v>
+      </c>
+      <c r="H58">
+        <v>51.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.98</v>
+      </c>
+      <c r="K58">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L58">
+        <v>2.27</v>
+      </c>
+      <c r="M58">
+        <v>7.078223040000001</v>
+      </c>
+      <c r="N58">
+        <v>-4.808223040000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.1539735296</v>
+      </c>
+      <c r="P58">
+        <v>-3.654249510400001</v>
+      </c>
+      <c r="Q58">
+        <v>4.055750489599999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2008069682539541</v>
+      </c>
+      <c r="T58">
+        <v>2.54996532714931</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0769684703238738</v>
+      </c>
+      <c r="W58">
+        <v>0.220419929286659</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3207019596828076</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2137902264322689</v>
+      </c>
+      <c r="C59">
+        <v>2.554179322174665</v>
+      </c>
+      <c r="D59">
+        <v>20.22427932217466</v>
+      </c>
+      <c r="E59">
+        <v>28.3401</v>
+      </c>
+      <c r="F59">
+        <v>30.1701</v>
+      </c>
+      <c r="G59">
+        <v>12.5</v>
+      </c>
+      <c r="H59">
+        <v>51.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.98</v>
+      </c>
+      <c r="K59">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L59">
+        <v>2.27</v>
+      </c>
+      <c r="M59">
+        <v>7.204619880000001</v>
+      </c>
+      <c r="N59">
+        <v>-4.934619880000001</v>
+      </c>
+      <c r="O59">
+        <v>-1.1843087712</v>
+      </c>
+      <c r="P59">
+        <v>-3.750311108800001</v>
+      </c>
+      <c r="Q59">
+        <v>3.9596888912</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2045745721668368</v>
+      </c>
+      <c r="T59">
+        <v>2.609266846385341</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.07561814628310408</v>
+      </c>
+      <c r="W59">
+        <v>0.2207423866675948</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3150756095129337</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2157902264322688</v>
+      </c>
+      <c r="C60">
+        <v>1.826256863140969</v>
+      </c>
+      <c r="D60">
+        <v>20.02565686314097</v>
+      </c>
+      <c r="E60">
+        <v>28.8694</v>
+      </c>
+      <c r="F60">
+        <v>30.6994</v>
+      </c>
+      <c r="G60">
+        <v>12.5</v>
+      </c>
+      <c r="H60">
+        <v>51.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.98</v>
+      </c>
+      <c r="K60">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L60">
+        <v>2.27</v>
+      </c>
+      <c r="M60">
+        <v>7.33101672</v>
+      </c>
+      <c r="N60">
+        <v>-5.06101672</v>
+      </c>
+      <c r="O60">
+        <v>-1.2146440128</v>
+      </c>
+      <c r="P60">
+        <v>-3.8463727072</v>
+      </c>
+      <c r="Q60">
+        <v>3.8636272928</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2085215857898567</v>
+      </c>
+      <c r="T60">
+        <v>2.671392247489753</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.07431438514029196</v>
+      </c>
+      <c r="W60">
+        <v>0.2210537248284983</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3096432714178832</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2177902264322688</v>
+      </c>
+      <c r="C61">
+        <v>1.102197800372434</v>
+      </c>
+      <c r="D61">
+        <v>19.83089780037243</v>
+      </c>
+      <c r="E61">
+        <v>29.3987</v>
+      </c>
+      <c r="F61">
+        <v>31.2287</v>
+      </c>
+      <c r="G61">
+        <v>12.5</v>
+      </c>
+      <c r="H61">
+        <v>51.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.98</v>
+      </c>
+      <c r="K61">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L61">
+        <v>2.27</v>
+      </c>
+      <c r="M61">
+        <v>7.45741356</v>
+      </c>
+      <c r="N61">
+        <v>-5.18741356</v>
+      </c>
+      <c r="O61">
+        <v>-1.2449792544</v>
+      </c>
+      <c r="P61">
+        <v>-3.9424343056</v>
+      </c>
+      <c r="Q61">
+        <v>3.7675656944</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.21266113666278</v>
+      </c>
+      <c r="T61">
+        <v>2.736548155965112</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0730548192904565</v>
+      </c>
+      <c r="W61">
+        <v>0.221354509153439</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3043950803769021</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2197902264322688</v>
+      </c>
+      <c r="C62">
+        <v>0.3818904994538421</v>
+      </c>
+      <c r="D62">
+        <v>19.63989049945384</v>
+      </c>
+      <c r="E62">
+        <v>29.928</v>
+      </c>
+      <c r="F62">
+        <v>31.758</v>
+      </c>
+      <c r="G62">
+        <v>12.5</v>
+      </c>
+      <c r="H62">
+        <v>51.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.98</v>
+      </c>
+      <c r="K62">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L62">
+        <v>2.27</v>
+      </c>
+      <c r="M62">
+        <v>7.5838104</v>
+      </c>
+      <c r="N62">
+        <v>-5.3138104</v>
+      </c>
+      <c r="O62">
+        <v>-1.275314496</v>
+      </c>
+      <c r="P62">
+        <v>-4.038495904</v>
+      </c>
+      <c r="Q62">
+        <v>3.671504096</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2170076650793495</v>
+      </c>
+      <c r="T62">
+        <v>2.804961859864241</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07183723896894889</v>
+      </c>
+      <c r="W62">
+        <v>0.221645267334215</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2993218290372871</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2217902264322688</v>
+      </c>
+      <c r="C63">
+        <v>-0.3347724140980475</v>
+      </c>
+      <c r="D63">
+        <v>19.45252758590195</v>
+      </c>
+      <c r="E63">
+        <v>30.4573</v>
+      </c>
+      <c r="F63">
+        <v>32.2873</v>
+      </c>
+      <c r="G63">
+        <v>12.5</v>
+      </c>
+      <c r="H63">
+        <v>51.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.98</v>
+      </c>
+      <c r="K63">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L63">
+        <v>2.27</v>
+      </c>
+      <c r="M63">
+        <v>7.710207240000001</v>
+      </c>
+      <c r="N63">
+        <v>-5.440207240000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.3056497376</v>
+      </c>
+      <c r="P63">
+        <v>-4.134557502400001</v>
+      </c>
+      <c r="Q63">
+        <v>3.5754424976</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2215770923890764</v>
+      </c>
+      <c r="T63">
+        <v>2.876883958835119</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07065957931372022</v>
+      </c>
+      <c r="W63">
+        <v>0.2219264924598836</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2944149138071676</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2237902264322688</v>
+      </c>
+      <c r="C64">
+        <v>-1.047894256111345</v>
+      </c>
+      <c r="D64">
+        <v>19.26870574388866</v>
+      </c>
+      <c r="E64">
+        <v>30.9866</v>
+      </c>
+      <c r="F64">
+        <v>32.8166</v>
+      </c>
+      <c r="G64">
+        <v>12.5</v>
+      </c>
+      <c r="H64">
+        <v>51.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.98</v>
+      </c>
+      <c r="K64">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L64">
+        <v>2.27</v>
+      </c>
+      <c r="M64">
+        <v>7.836604080000001</v>
+      </c>
+      <c r="N64">
+        <v>-5.566604080000001</v>
+      </c>
+      <c r="O64">
+        <v>-1.3359849792</v>
+      </c>
+      <c r="P64">
+        <v>-4.230619100800001</v>
+      </c>
+      <c r="Q64">
+        <v>3.4793808992</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2263870158729995</v>
+      </c>
+      <c r="T64">
+        <v>2.952591431436043</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.06951990867962796</v>
+      </c>
+      <c r="W64">
+        <v>0.2221986458073049</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2896662861651165</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2257902264322688</v>
+      </c>
+      <c r="C65">
+        <v>-1.757574473730529</v>
+      </c>
+      <c r="D65">
+        <v>19.08832552626947</v>
+      </c>
+      <c r="E65">
+        <v>31.5159</v>
+      </c>
+      <c r="F65">
+        <v>33.3459</v>
+      </c>
+      <c r="G65">
+        <v>12.5</v>
+      </c>
+      <c r="H65">
+        <v>51.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.98</v>
+      </c>
+      <c r="K65">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L65">
+        <v>2.27</v>
+      </c>
+      <c r="M65">
+        <v>7.963000920000001</v>
+      </c>
+      <c r="N65">
+        <v>-5.693000920000001</v>
+      </c>
+      <c r="O65">
+        <v>-1.3663202208</v>
+      </c>
+      <c r="P65">
+        <v>-4.326680699200001</v>
+      </c>
+      <c r="Q65">
+        <v>3.3833193008</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2314569352209184</v>
+      </c>
+      <c r="T65">
+        <v>3.032391199853233</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0684164180656656</v>
+      </c>
+      <c r="W65">
+        <v>0.2224621593659191</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.28506840860694</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2277902264322688</v>
+      </c>
+      <c r="C66">
+        <v>-2.463908824816681</v>
+      </c>
+      <c r="D66">
+        <v>18.91129117518332</v>
+      </c>
+      <c r="E66">
+        <v>32.0452</v>
+      </c>
+      <c r="F66">
+        <v>33.8752</v>
+      </c>
+      <c r="G66">
+        <v>12.5</v>
+      </c>
+      <c r="H66">
+        <v>51.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.98</v>
+      </c>
+      <c r="K66">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L66">
+        <v>2.27</v>
+      </c>
+      <c r="M66">
+        <v>8.089397760000001</v>
+      </c>
+      <c r="N66">
+        <v>-5.819397760000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.3966554624</v>
+      </c>
+      <c r="P66">
+        <v>-4.422742297600001</v>
+      </c>
+      <c r="Q66">
+        <v>3.2872577024</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2368085167548328</v>
+      </c>
+      <c r="T66">
+        <v>3.116624288738045</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.06734741153338958</v>
+      </c>
+      <c r="W66">
+        <v>0.2227174381258266</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2806142147224566</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2297902264322688</v>
+      </c>
+      <c r="C67">
+        <v>-3.166989547456335</v>
+      </c>
+      <c r="D67">
+        <v>18.73751045254366</v>
+      </c>
+      <c r="E67">
+        <v>32.5745</v>
+      </c>
+      <c r="F67">
+        <v>34.4045</v>
+      </c>
+      <c r="G67">
+        <v>12.5</v>
+      </c>
+      <c r="H67">
+        <v>51.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.98</v>
+      </c>
+      <c r="K67">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L67">
+        <v>2.27</v>
+      </c>
+      <c r="M67">
+        <v>8.215794600000001</v>
+      </c>
+      <c r="N67">
+        <v>-5.945794600000001</v>
+      </c>
+      <c r="O67">
+        <v>-1.426990704</v>
+      </c>
+      <c r="P67">
+        <v>-4.518803896000001</v>
+      </c>
+      <c r="Q67">
+        <v>3.191196104</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.242465902947828</v>
+      </c>
+      <c r="T67">
+        <v>3.205670696987704</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.06631129750979897</v>
+      </c>
+      <c r="W67">
+        <v>0.22296486215466</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2762970729574957</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2317902264322688</v>
+      </c>
+      <c r="C68">
+        <v>-3.866905520209503</v>
+      </c>
+      <c r="D68">
+        <v>18.56689447979049</v>
+      </c>
+      <c r="E68">
+        <v>33.1038</v>
+      </c>
+      <c r="F68">
+        <v>34.9338</v>
+      </c>
+      <c r="G68">
+        <v>12.5</v>
+      </c>
+      <c r="H68">
+        <v>51.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.98</v>
+      </c>
+      <c r="K68">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L68">
+        <v>2.27</v>
+      </c>
+      <c r="M68">
+        <v>8.342191440000001</v>
+      </c>
+      <c r="N68">
+        <v>-6.072191440000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.4573259456</v>
+      </c>
+      <c r="P68">
+        <v>-4.614865494400001</v>
+      </c>
+      <c r="Q68">
+        <v>3.0951345056</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2484560765639406</v>
+      </c>
+      <c r="T68">
+        <v>3.299955129252048</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.06530658088086262</v>
+      </c>
+      <c r="W68">
+        <v>0.22320478848565</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2721107536702609</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2337902264322688</v>
+      </c>
+      <c r="C69">
+        <v>-4.563742413681759</v>
+      </c>
+      <c r="D69">
+        <v>18.39935758631825</v>
+      </c>
+      <c r="E69">
+        <v>33.63310000000001</v>
+      </c>
+      <c r="F69">
+        <v>35.4631</v>
+      </c>
+      <c r="G69">
+        <v>12.5</v>
+      </c>
+      <c r="H69">
+        <v>51.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.98</v>
+      </c>
+      <c r="K69">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L69">
+        <v>2.27</v>
+      </c>
+      <c r="M69">
+        <v>8.468588280000002</v>
+      </c>
+      <c r="N69">
+        <v>-6.198588280000003</v>
+      </c>
+      <c r="O69">
+        <v>-1.487661187200001</v>
+      </c>
+      <c r="P69">
+        <v>-4.710927092800002</v>
+      </c>
+      <c r="Q69">
+        <v>2.999072907199999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2548092910052722</v>
+      </c>
+      <c r="T69">
+        <v>3.399953769532414</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06433185579308855</v>
+      </c>
+      <c r="W69">
+        <v>0.2234375528366105</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.268049399137869</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2357902264322688</v>
+      </c>
+      <c r="C70">
+        <v>-5.257582833963543</v>
+      </c>
+      <c r="D70">
+        <v>18.23481716603646</v>
+      </c>
+      <c r="E70">
+        <v>34.16240000000001</v>
+      </c>
+      <c r="F70">
+        <v>35.9924</v>
+      </c>
+      <c r="G70">
+        <v>12.5</v>
+      </c>
+      <c r="H70">
+        <v>51.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.98</v>
+      </c>
+      <c r="K70">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L70">
+        <v>2.27</v>
+      </c>
+      <c r="M70">
+        <v>8.59498512</v>
+      </c>
+      <c r="N70">
+        <v>-6.324985120000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.5179964288</v>
+      </c>
+      <c r="P70">
+        <v>-4.806988691200001</v>
+      </c>
+      <c r="Q70">
+        <v>2.9030113088</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2615595813491869</v>
+      </c>
+      <c r="T70">
+        <v>3.506202324830301</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06338579909024901</v>
+      </c>
+      <c r="W70">
+        <v>0.2236634711772486</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2641074962093709</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2377902264322688</v>
+      </c>
+      <c r="C71">
+        <v>-5.948506458441244</v>
+      </c>
+      <c r="D71">
+        <v>18.07319354155876</v>
+      </c>
+      <c r="E71">
+        <v>34.6917</v>
+      </c>
+      <c r="F71">
+        <v>36.5217</v>
+      </c>
+      <c r="G71">
+        <v>12.5</v>
+      </c>
+      <c r="H71">
+        <v>51.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.98</v>
+      </c>
+      <c r="K71">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L71">
+        <v>2.27</v>
+      </c>
+      <c r="M71">
+        <v>8.72138196</v>
+      </c>
+      <c r="N71">
+        <v>-6.451381960000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.5483316704</v>
+      </c>
+      <c r="P71">
+        <v>-4.903050289600001</v>
+      </c>
+      <c r="Q71">
+        <v>2.8069497104</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2687453742959349</v>
+      </c>
+      <c r="T71">
+        <v>3.619305625631279</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06246716432082512</v>
+      </c>
+      <c r="W71">
+        <v>0.223882841160187</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2602798513367713</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2397902264322688</v>
+      </c>
+      <c r="C72">
+        <v>-6.636590164449196</v>
+      </c>
+      <c r="D72">
+        <v>17.91440983555081</v>
+      </c>
+      <c r="E72">
+        <v>35.221</v>
+      </c>
+      <c r="F72">
+        <v>37.051</v>
+      </c>
+      <c r="G72">
+        <v>12.5</v>
+      </c>
+      <c r="H72">
+        <v>51.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.98</v>
+      </c>
+      <c r="K72">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L72">
+        <v>2.27</v>
+      </c>
+      <c r="M72">
+        <v>8.8477788</v>
+      </c>
+      <c r="N72">
+        <v>-6.577778800000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.578666912</v>
+      </c>
+      <c r="P72">
+        <v>-4.999111888000001</v>
+      </c>
+      <c r="Q72">
+        <v>2.710888112</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2764102201057994</v>
+      </c>
+      <c r="T72">
+        <v>3.739949146485655</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06157477625909905</v>
+      </c>
+      <c r="W72">
+        <v>0.2240959434293272</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2565615677462461</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2417902264322688</v>
+      </c>
+      <c r="C73">
+        <v>-7.321908151199029</v>
+      </c>
+      <c r="D73">
+        <v>17.75839184880097</v>
+      </c>
+      <c r="E73">
+        <v>35.7503</v>
+      </c>
+      <c r="F73">
+        <v>37.5803</v>
+      </c>
+      <c r="G73">
+        <v>12.5</v>
+      </c>
+      <c r="H73">
+        <v>51.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.98</v>
+      </c>
+      <c r="K73">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L73">
+        <v>2.27</v>
+      </c>
+      <c r="M73">
+        <v>8.97417564</v>
+      </c>
+      <c r="N73">
+        <v>-6.704175640000001</v>
+      </c>
+      <c r="O73">
+        <v>-1.6090021536</v>
+      </c>
+      <c r="P73">
+        <v>-5.0951734864</v>
+      </c>
+      <c r="Q73">
+        <v>2.614826513600001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2846036759715165</v>
+      </c>
+      <c r="T73">
+        <v>3.868912910157573</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06070752588925258</v>
+      </c>
+      <c r="W73">
+        <v>0.2243030428176465</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2529480245385525</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2437902264322688</v>
+      </c>
+      <c r="C74">
+        <v>-8.004532055392666</v>
+      </c>
+      <c r="D74">
+        <v>17.60506794460733</v>
+      </c>
+      <c r="E74">
+        <v>36.2796</v>
+      </c>
+      <c r="F74">
+        <v>38.1096</v>
+      </c>
+      <c r="G74">
+        <v>12.5</v>
+      </c>
+      <c r="H74">
+        <v>51.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.98</v>
+      </c>
+      <c r="K74">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L74">
+        <v>2.27</v>
+      </c>
+      <c r="M74">
+        <v>9.10057248</v>
+      </c>
+      <c r="N74">
+        <v>-6.830572480000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.6393373952</v>
+      </c>
+      <c r="P74">
+        <v>-5.191235084800001</v>
+      </c>
+      <c r="Q74">
+        <v>2.5187649152</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.293382378684785</v>
+      </c>
+      <c r="T74">
+        <v>4.007088371234629</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0598643658074574</v>
+      </c>
+      <c r="W74">
+        <v>0.2245043894451792</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2494348575310725</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2457902264322688</v>
+      </c>
+      <c r="C75">
+        <v>-8.684531060897498</v>
+      </c>
+      <c r="D75">
+        <v>17.4543689391025</v>
+      </c>
+      <c r="E75">
+        <v>36.8089</v>
+      </c>
+      <c r="F75">
+        <v>38.6389</v>
+      </c>
+      <c r="G75">
+        <v>12.5</v>
+      </c>
+      <c r="H75">
+        <v>51.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.98</v>
+      </c>
+      <c r="K75">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L75">
+        <v>2.27</v>
+      </c>
+      <c r="M75">
+        <v>9.22696932</v>
+      </c>
+      <c r="N75">
+        <v>-6.956969320000001</v>
+      </c>
+      <c r="O75">
+        <v>-1.6696726368</v>
+      </c>
+      <c r="P75">
+        <v>-5.287296683200001</v>
+      </c>
+      <c r="Q75">
+        <v>2.4227033168</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3028113556731103</v>
+      </c>
+      <c r="T75">
+        <v>4.155499051650727</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0590443060018758</v>
+      </c>
+      <c r="W75">
+        <v>0.2247002197267521</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2460179416744825</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2477902264322688</v>
+      </c>
+      <c r="C76">
+        <v>-9.361972002836396</v>
+      </c>
+      <c r="D76">
+        <v>17.3062279971636</v>
+      </c>
+      <c r="E76">
+        <v>37.3382</v>
+      </c>
+      <c r="F76">
+        <v>39.1682</v>
+      </c>
+      <c r="G76">
+        <v>12.5</v>
+      </c>
+      <c r="H76">
+        <v>51.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.98</v>
+      </c>
+      <c r="K76">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L76">
+        <v>2.27</v>
+      </c>
+      <c r="M76">
+        <v>9.35336616</v>
+      </c>
+      <c r="N76">
+        <v>-7.083366160000001</v>
+      </c>
+      <c r="O76">
+        <v>-1.7000078784</v>
+      </c>
+      <c r="P76">
+        <v>-5.383358281600001</v>
+      </c>
+      <c r="Q76">
+        <v>2.3266417184</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3129656385836146</v>
+      </c>
+      <c r="T76">
+        <v>4.315325938252678</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05824640997482342</v>
+      </c>
+      <c r="W76">
+        <v>0.2248907572980122</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2426933748950976</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2497902264322688</v>
+      </c>
+      <c r="C77">
+        <v>-10.03691946642171</v>
+      </c>
+      <c r="D77">
+        <v>17.16058053357829</v>
+      </c>
+      <c r="E77">
+        <v>37.8675</v>
+      </c>
+      <c r="F77">
+        <v>39.6975</v>
+      </c>
+      <c r="G77">
+        <v>12.5</v>
+      </c>
+      <c r="H77">
+        <v>51.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.98</v>
+      </c>
+      <c r="K77">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L77">
+        <v>2.27</v>
+      </c>
+      <c r="M77">
+        <v>9.479763</v>
+      </c>
+      <c r="N77">
+        <v>-7.209763000000001</v>
+      </c>
+      <c r="O77">
+        <v>-1.73034312</v>
+      </c>
+      <c r="P77">
+        <v>-5.47941988</v>
+      </c>
+      <c r="Q77">
+        <v>2.230580120000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3239322641269592</v>
+      </c>
+      <c r="T77">
+        <v>4.487938975782785</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05746979117515911</v>
+      </c>
+      <c r="W77">
+        <v>0.225076213867372</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2394574632298296</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2517902264322688</v>
+      </c>
+      <c r="C78">
+        <v>-10.70943588084025</v>
+      </c>
+      <c r="D78">
+        <v>17.01736411915975</v>
+      </c>
+      <c r="E78">
+        <v>38.3968</v>
+      </c>
+      <c r="F78">
+        <v>40.2268</v>
+      </c>
+      <c r="G78">
+        <v>12.5</v>
+      </c>
+      <c r="H78">
+        <v>51.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.98</v>
+      </c>
+      <c r="K78">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L78">
+        <v>2.27</v>
+      </c>
+      <c r="M78">
+        <v>9.60615984</v>
+      </c>
+      <c r="N78">
+        <v>-7.336159840000001</v>
+      </c>
+      <c r="O78">
+        <v>-1.7606783616</v>
+      </c>
+      <c r="P78">
+        <v>-5.5754814784</v>
+      </c>
+      <c r="Q78">
+        <v>2.1345185216</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3358127751322492</v>
+      </c>
+      <c r="T78">
+        <v>4.674936433107068</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05671360971232807</v>
+      </c>
+      <c r="W78">
+        <v>0.2252567900006961</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2363067071347003</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2537902264322688</v>
+      </c>
+      <c r="C79">
+        <v>-11.37958160847593</v>
+      </c>
+      <c r="D79">
+        <v>16.87651839152407</v>
+      </c>
+      <c r="E79">
+        <v>38.92610000000001</v>
+      </c>
+      <c r="F79">
+        <v>40.7561</v>
+      </c>
+      <c r="G79">
+        <v>12.5</v>
+      </c>
+      <c r="H79">
+        <v>51.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.98</v>
+      </c>
+      <c r="K79">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L79">
+        <v>2.27</v>
+      </c>
+      <c r="M79">
+        <v>9.732556680000002</v>
+      </c>
+      <c r="N79">
+        <v>-7.462556680000002</v>
+      </c>
+      <c r="O79">
+        <v>-1.791013603200001</v>
+      </c>
+      <c r="P79">
+        <v>-5.671543076800002</v>
+      </c>
+      <c r="Q79">
+        <v>2.038456923199999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3487263740510427</v>
+      </c>
+      <c r="T79">
+        <v>4.878194538894332</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05597706932645367</v>
+      </c>
+      <c r="W79">
+        <v>0.2254326758448429</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2332377888602236</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2557902264322688</v>
+      </c>
+      <c r="C80">
+        <v>-12.04741502973812</v>
+      </c>
+      <c r="D80">
+        <v>16.73798497026189</v>
+      </c>
+      <c r="E80">
+        <v>39.4554</v>
+      </c>
+      <c r="F80">
+        <v>41.2854</v>
+      </c>
+      <c r="G80">
+        <v>12.5</v>
+      </c>
+      <c r="H80">
+        <v>51.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.98</v>
+      </c>
+      <c r="K80">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L80">
+        <v>2.27</v>
+      </c>
+      <c r="M80">
+        <v>9.858953520000002</v>
+      </c>
+      <c r="N80">
+        <v>-7.588953520000002</v>
+      </c>
+      <c r="O80">
+        <v>-1.8213488448</v>
+      </c>
+      <c r="P80">
+        <v>-5.767604675200002</v>
+      </c>
+      <c r="Q80">
+        <v>1.942395324799999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3628139365079082</v>
+      </c>
+      <c r="T80">
+        <v>5.099930654298619</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05525941459149914</v>
+      </c>
+      <c r="W80">
+        <v>0.22560405179555</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2302475607979131</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2577902264322688</v>
+      </c>
+      <c r="C81">
+        <v>-12.71299262374597</v>
+      </c>
+      <c r="D81">
+        <v>16.60170737625403</v>
+      </c>
+      <c r="E81">
+        <v>39.9847</v>
+      </c>
+      <c r="F81">
+        <v>41.8147</v>
+      </c>
+      <c r="G81">
+        <v>12.5</v>
+      </c>
+      <c r="H81">
+        <v>51.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.98</v>
+      </c>
+      <c r="K81">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L81">
+        <v>2.27</v>
+      </c>
+      <c r="M81">
+        <v>9.985350360000002</v>
+      </c>
+      <c r="N81">
+        <v>-7.715350360000002</v>
+      </c>
+      <c r="O81">
+        <v>-1.8516840864</v>
+      </c>
+      <c r="P81">
+        <v>-5.863666273600002</v>
+      </c>
+      <c r="Q81">
+        <v>1.846333726399999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3782431715797134</v>
+      </c>
+      <c r="T81">
+        <v>5.342784494979508</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05455992833084725</v>
+      </c>
+      <c r="W81">
+        <v>0.2257710891145937</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2273330347118635</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2597902264322688</v>
+      </c>
+      <c r="C82">
+        <v>-13.37636904510313</v>
+      </c>
+      <c r="D82">
+        <v>16.46763095489687</v>
+      </c>
+      <c r="E82">
+        <v>40.514</v>
+      </c>
+      <c r="F82">
+        <v>42.344</v>
+      </c>
+      <c r="G82">
+        <v>12.5</v>
+      </c>
+      <c r="H82">
+        <v>51.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.98</v>
+      </c>
+      <c r="K82">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L82">
+        <v>2.27</v>
+      </c>
+      <c r="M82">
+        <v>10.1117472</v>
+      </c>
+      <c r="N82">
+        <v>-7.8417472</v>
+      </c>
+      <c r="O82">
+        <v>-1.882019328</v>
+      </c>
+      <c r="P82">
+        <v>-5.959727872</v>
+      </c>
+      <c r="Q82">
+        <v>1.750272128000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.395215330158699</v>
+      </c>
+      <c r="T82">
+        <v>5.609923719728482</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05387792922671167</v>
+      </c>
+      <c r="W82">
+        <v>0.2259339505006613</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2244913717779653</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2617902264322688</v>
+      </c>
+      <c r="C83">
+        <v>-14.03759719698198</v>
+      </c>
+      <c r="D83">
+        <v>16.33570280301802</v>
+      </c>
+      <c r="E83">
+        <v>41.0433</v>
+      </c>
+      <c r="F83">
+        <v>42.8733</v>
+      </c>
+      <c r="G83">
+        <v>12.5</v>
+      </c>
+      <c r="H83">
+        <v>51.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.98</v>
+      </c>
+      <c r="K83">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L83">
+        <v>2.27</v>
+      </c>
+      <c r="M83">
+        <v>10.23814404</v>
+      </c>
+      <c r="N83">
+        <v>-7.96814404</v>
+      </c>
+      <c r="O83">
+        <v>-1.9123545696</v>
+      </c>
+      <c r="P83">
+        <v>-6.055789470400001</v>
+      </c>
+      <c r="Q83">
+        <v>1.6542105296</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4139740317459991</v>
+      </c>
+      <c r="T83">
+        <v>5.905182862872087</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05321276960662881</v>
+      </c>
+      <c r="W83">
+        <v>0.2260927906179371</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2217198733609533</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2637902264322688</v>
+      </c>
+      <c r="C84">
+        <v>-14.69672830072284</v>
+      </c>
+      <c r="D84">
+        <v>16.20587169927716</v>
+      </c>
+      <c r="E84">
+        <v>41.5726</v>
+      </c>
+      <c r="F84">
+        <v>43.4026</v>
+      </c>
+      <c r="G84">
+        <v>12.5</v>
+      </c>
+      <c r="H84">
+        <v>51.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.98</v>
+      </c>
+      <c r="K84">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L84">
+        <v>2.27</v>
+      </c>
+      <c r="M84">
+        <v>10.36454088</v>
+      </c>
+      <c r="N84">
+        <v>-8.09454088</v>
+      </c>
+      <c r="O84">
+        <v>-1.9426898112</v>
+      </c>
+      <c r="P84">
+        <v>-6.1518510688</v>
+      </c>
+      <c r="Q84">
+        <v>1.558148931200001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4348170335096657</v>
+      </c>
+      <c r="T84">
+        <v>6.233248577476092</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05256383339191383</v>
+      </c>
+      <c r="W84">
+        <v>0.226247756586011</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2190159724663076</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2657902264322689</v>
+      </c>
+      <c r="C85">
+        <v>-15.35381196214036</v>
+      </c>
+      <c r="D85">
+        <v>16.07808803785964</v>
+      </c>
+      <c r="E85">
+        <v>42.10190000000001</v>
+      </c>
+      <c r="F85">
+        <v>43.93190000000001</v>
+      </c>
+      <c r="G85">
+        <v>12.5</v>
+      </c>
+      <c r="H85">
+        <v>51.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.98</v>
+      </c>
+      <c r="K85">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L85">
+        <v>2.27</v>
+      </c>
+      <c r="M85">
+        <v>10.49093772</v>
+      </c>
+      <c r="N85">
+        <v>-8.220937720000002</v>
+      </c>
+      <c r="O85">
+        <v>-1.9730250528</v>
+      </c>
+      <c r="P85">
+        <v>-6.247912667200001</v>
+      </c>
+      <c r="Q85">
+        <v>1.462087332799999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4581121531278813</v>
+      </c>
+      <c r="T85">
+        <v>6.599910258504099</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05193053419442088</v>
+      </c>
+      <c r="W85">
+        <v>0.2263989884343723</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.216377225810087</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2677902264322688</v>
+      </c>
+      <c r="C86">
+        <v>-16.00889623471751</v>
+      </c>
+      <c r="D86">
+        <v>15.95230376528249</v>
+      </c>
+      <c r="E86">
+        <v>42.6312</v>
+      </c>
+      <c r="F86">
+        <v>44.4612</v>
+      </c>
+      <c r="G86">
+        <v>12.5</v>
+      </c>
+      <c r="H86">
+        <v>51.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.98</v>
+      </c>
+      <c r="K86">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L86">
+        <v>2.27</v>
+      </c>
+      <c r="M86">
+        <v>10.61733456</v>
+      </c>
+      <c r="N86">
+        <v>-8.34733456</v>
+      </c>
+      <c r="O86">
+        <v>-2.0033602944</v>
+      </c>
+      <c r="P86">
+        <v>-6.3439742656</v>
+      </c>
+      <c r="Q86">
+        <v>1.366025734400001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4843191626983737</v>
+      </c>
+      <c r="T86">
+        <v>7.012404649660601</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05131231354924921</v>
+      </c>
+      <c r="W86">
+        <v>0.2265466195244393</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.213801306455205</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2697902264322688</v>
+      </c>
+      <c r="C87">
+        <v>-16.6620276798563</v>
+      </c>
+      <c r="D87">
+        <v>15.82847232014369</v>
+      </c>
+      <c r="E87">
+        <v>43.1605</v>
+      </c>
+      <c r="F87">
+        <v>44.9905</v>
+      </c>
+      <c r="G87">
+        <v>12.5</v>
+      </c>
+      <c r="H87">
+        <v>51.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.98</v>
+      </c>
+      <c r="K87">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L87">
+        <v>2.27</v>
+      </c>
+      <c r="M87">
+        <v>10.7437314</v>
+      </c>
+      <c r="N87">
+        <v>-8.4737314</v>
+      </c>
+      <c r="O87">
+        <v>-2.033695536</v>
+      </c>
+      <c r="P87">
+        <v>-6.440035864</v>
+      </c>
+      <c r="Q87">
+        <v>1.269964136</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5140204402115985</v>
+      </c>
+      <c r="T87">
+        <v>7.479898292971307</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05070863927219922</v>
+      </c>
+      <c r="W87">
+        <v>0.2266907769417988</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2112859969674967</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2717902264322688</v>
+      </c>
+      <c r="C88">
+        <v>-17.31325142434385</v>
+      </c>
+      <c r="D88">
+        <v>15.70654857565614</v>
+      </c>
+      <c r="E88">
+        <v>43.6898</v>
+      </c>
+      <c r="F88">
+        <v>45.5198</v>
+      </c>
+      <c r="G88">
+        <v>12.5</v>
+      </c>
+      <c r="H88">
+        <v>51.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.98</v>
+      </c>
+      <c r="K88">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L88">
+        <v>2.27</v>
+      </c>
+      <c r="M88">
+        <v>10.87012824</v>
+      </c>
+      <c r="N88">
+        <v>-8.60012824</v>
+      </c>
+      <c r="O88">
+        <v>-2.0640307776</v>
+      </c>
+      <c r="P88">
+        <v>-6.536097462400001</v>
+      </c>
+      <c r="Q88">
+        <v>1.1739025376</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5479647573695698</v>
+      </c>
+      <c r="T88">
+        <v>8.014176742469258</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05011900393182481</v>
+      </c>
+      <c r="W88">
+        <v>0.2268315818610803</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.20882918304927</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2737902264322688</v>
+      </c>
+      <c r="C89">
+        <v>-17.96261121518291</v>
+      </c>
+      <c r="D89">
+        <v>15.58648878481709</v>
+      </c>
+      <c r="E89">
+        <v>44.2191</v>
+      </c>
+      <c r="F89">
+        <v>46.0491</v>
+      </c>
+      <c r="G89">
+        <v>12.5</v>
+      </c>
+      <c r="H89">
+        <v>51.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.98</v>
+      </c>
+      <c r="K89">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L89">
+        <v>2.27</v>
+      </c>
+      <c r="M89">
+        <v>10.99652508</v>
+      </c>
+      <c r="N89">
+        <v>-8.726525080000002</v>
+      </c>
+      <c r="O89">
+        <v>-2.0943660192</v>
+      </c>
+      <c r="P89">
+        <v>-6.632159060800001</v>
+      </c>
+      <c r="Q89">
+        <v>1.0778409392</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5871312771672292</v>
+      </c>
+      <c r="T89">
+        <v>8.630651876505356</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0495429234268613</v>
+      </c>
+      <c r="W89">
+        <v>0.2269691498856655</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.206428847611922</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2757902264322688</v>
+      </c>
+      <c r="C90">
+        <v>-18.61014947192665</v>
+      </c>
+      <c r="D90">
+        <v>15.46825052807335</v>
+      </c>
+      <c r="E90">
+        <v>44.7484</v>
+      </c>
+      <c r="F90">
+        <v>46.5784</v>
+      </c>
+      <c r="G90">
+        <v>12.5</v>
+      </c>
+      <c r="H90">
+        <v>51.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.98</v>
+      </c>
+      <c r="K90">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L90">
+        <v>2.27</v>
+      </c>
+      <c r="M90">
+        <v>11.12292192</v>
+      </c>
+      <c r="N90">
+        <v>-8.852921920000002</v>
+      </c>
+      <c r="O90">
+        <v>-2.1247012608</v>
+      </c>
+      <c r="P90">
+        <v>-6.728220659200002</v>
+      </c>
+      <c r="Q90">
+        <v>0.9817793407999993</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6328255502644984</v>
+      </c>
+      <c r="T90">
+        <v>9.349872866214136</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04897993566064697</v>
+      </c>
+      <c r="W90">
+        <v>0.2271035913642375</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2040830652526957</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2777902264322688</v>
+      </c>
+      <c r="C91">
+        <v>-19.25590733664947</v>
+      </c>
+      <c r="D91">
+        <v>15.35179266335053</v>
+      </c>
+      <c r="E91">
+        <v>45.2777</v>
+      </c>
+      <c r="F91">
+        <v>47.1077</v>
+      </c>
+      <c r="G91">
+        <v>12.5</v>
+      </c>
+      <c r="H91">
+        <v>51.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.98</v>
+      </c>
+      <c r="K91">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L91">
+        <v>2.27</v>
+      </c>
+      <c r="M91">
+        <v>11.24931876</v>
+      </c>
+      <c r="N91">
+        <v>-8.979318760000002</v>
+      </c>
+      <c r="O91">
+        <v>-2.1550365024</v>
+      </c>
+      <c r="P91">
+        <v>-6.824282257600002</v>
+      </c>
+      <c r="Q91">
+        <v>0.8857177423999989</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6868278730158164</v>
+      </c>
+      <c r="T91">
+        <v>10.19986130859724</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04842959930490936</v>
+      </c>
+      <c r="W91">
+        <v>0.2272350116859877</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.201789997103789</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2797902264322688</v>
+      </c>
+      <c r="C92">
+        <v>-19.8999247216772</v>
+      </c>
+      <c r="D92">
+        <v>15.2370752783228</v>
+      </c>
+      <c r="E92">
+        <v>45.807</v>
+      </c>
+      <c r="F92">
+        <v>47.637</v>
+      </c>
+      <c r="G92">
+        <v>12.5</v>
+      </c>
+      <c r="H92">
+        <v>51.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.98</v>
+      </c>
+      <c r="K92">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L92">
+        <v>2.27</v>
+      </c>
+      <c r="M92">
+        <v>11.3757156</v>
+      </c>
+      <c r="N92">
+        <v>-9.105715600000002</v>
+      </c>
+      <c r="O92">
+        <v>-2.185371744</v>
+      </c>
+      <c r="P92">
+        <v>-6.920343856000001</v>
+      </c>
+      <c r="Q92">
+        <v>0.7896561439999994</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7516306603173981</v>
+      </c>
+      <c r="T92">
+        <v>11.21984743945696</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04789149264596592</v>
+      </c>
+      <c r="W92">
+        <v>0.2273635115561433</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1995478860248581</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2817902264322688</v>
+      </c>
+      <c r="C93">
+        <v>-20.54224035519325</v>
+      </c>
+      <c r="D93">
+        <v>15.12405964480675</v>
+      </c>
+      <c r="E93">
+        <v>46.3363</v>
+      </c>
+      <c r="F93">
+        <v>48.1663</v>
+      </c>
+      <c r="G93">
+        <v>12.5</v>
+      </c>
+      <c r="H93">
+        <v>51.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.98</v>
+      </c>
+      <c r="K93">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L93">
+        <v>2.27</v>
+      </c>
+      <c r="M93">
+        <v>11.50211244</v>
+      </c>
+      <c r="N93">
+        <v>-9.232112440000002</v>
+      </c>
+      <c r="O93">
+        <v>-2.2157069856</v>
+      </c>
+      <c r="P93">
+        <v>-7.016405454400001</v>
+      </c>
+      <c r="Q93">
+        <v>0.6935945455999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8308340670193313</v>
+      </c>
+      <c r="T93">
+        <v>12.46649715495218</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04736521250699926</v>
+      </c>
+      <c r="W93">
+        <v>0.2274891872533286</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1973550521124969</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2837902264322688</v>
+      </c>
+      <c r="C94">
+        <v>-21.18289182483009</v>
+      </c>
+      <c r="D94">
+        <v>15.01270817516991</v>
+      </c>
+      <c r="E94">
+        <v>46.8656</v>
+      </c>
+      <c r="F94">
+        <v>48.6956</v>
+      </c>
+      <c r="G94">
+        <v>12.5</v>
+      </c>
+      <c r="H94">
+        <v>51.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.98</v>
+      </c>
+      <c r="K94">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L94">
+        <v>2.27</v>
+      </c>
+      <c r="M94">
+        <v>11.62850928</v>
+      </c>
+      <c r="N94">
+        <v>-9.358509280000002</v>
+      </c>
+      <c r="O94">
+        <v>-2.2460422272</v>
+      </c>
+      <c r="P94">
+        <v>-7.112467052800001</v>
+      </c>
+      <c r="Q94">
+        <v>0.5975329471999995</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9298383253967479</v>
+      </c>
+      <c r="T94">
+        <v>14.02480929932121</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04685037324061884</v>
+      </c>
+      <c r="W94">
+        <v>0.2276121308701402</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1952098885025785</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2857902264322688</v>
+      </c>
+      <c r="C95">
+        <v>-21.82191561934913</v>
+      </c>
+      <c r="D95">
+        <v>14.90298438065088</v>
+      </c>
+      <c r="E95">
+        <v>47.39490000000001</v>
+      </c>
+      <c r="F95">
+        <v>49.22490000000001</v>
+      </c>
+      <c r="G95">
+        <v>12.5</v>
+      </c>
+      <c r="H95">
+        <v>51.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.98</v>
+      </c>
+      <c r="K95">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L95">
+        <v>2.27</v>
+      </c>
+      <c r="M95">
+        <v>11.75490612</v>
+      </c>
+      <c r="N95">
+        <v>-9.484906120000002</v>
+      </c>
+      <c r="O95">
+        <v>-2.2763774688</v>
+      </c>
+      <c r="P95">
+        <v>-7.208528651200002</v>
+      </c>
+      <c r="Q95">
+        <v>0.5014713487999991</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.057129514739141</v>
+      </c>
+      <c r="T95">
+        <v>16.02835348493853</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04634660578641864</v>
+      </c>
+      <c r="W95">
+        <v>0.2277324305382032</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1931108574434109</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2877902264322688</v>
+      </c>
+      <c r="C96">
+        <v>-22.45934716850607</v>
+      </c>
+      <c r="D96">
+        <v>14.79485283149394</v>
+      </c>
+      <c r="E96">
+        <v>47.92420000000001</v>
+      </c>
+      <c r="F96">
+        <v>49.7542</v>
+      </c>
+      <c r="G96">
+        <v>12.5</v>
+      </c>
+      <c r="H96">
+        <v>51.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.98</v>
+      </c>
+      <c r="K96">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L96">
+        <v>2.27</v>
+      </c>
+      <c r="M96">
+        <v>11.88130296</v>
+      </c>
+      <c r="N96">
+        <v>-9.611302960000002</v>
+      </c>
+      <c r="O96">
+        <v>-2.3067127104</v>
+      </c>
+      <c r="P96">
+        <v>-7.304590249600001</v>
+      </c>
+      <c r="Q96">
+        <v>0.4054097503999996</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.226851100528998</v>
+      </c>
+      <c r="T96">
+        <v>18.69974573242829</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04585355678869078</v>
+      </c>
+      <c r="W96">
+        <v>0.2278501706388606</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1910564866195449</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2897902264322688</v>
+      </c>
+      <c r="C97">
+        <v>-23.09522088119332</v>
+      </c>
+      <c r="D97">
+        <v>14.68827911880669</v>
+      </c>
+      <c r="E97">
+        <v>48.45350000000001</v>
+      </c>
+      <c r="F97">
+        <v>50.2835</v>
+      </c>
+      <c r="G97">
+        <v>12.5</v>
+      </c>
+      <c r="H97">
+        <v>51.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.98</v>
+      </c>
+      <c r="K97">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L97">
+        <v>2.27</v>
+      </c>
+      <c r="M97">
+        <v>12.0076998</v>
+      </c>
+      <c r="N97">
+        <v>-9.737699800000001</v>
+      </c>
+      <c r="O97">
+        <v>-2.337047952</v>
+      </c>
+      <c r="P97">
+        <v>-7.400651848000001</v>
+      </c>
+      <c r="Q97">
+        <v>0.3093481520000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.464461320634798</v>
+      </c>
+      <c r="T97">
+        <v>22.43969487891396</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04537088776986246</v>
+      </c>
+      <c r="W97">
+        <v>0.2279654320005569</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1890453657077602</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2917902264322688</v>
+      </c>
+      <c r="C98">
+        <v>-23.7295701819456</v>
+      </c>
+      <c r="D98">
+        <v>14.5832298180544</v>
+      </c>
+      <c r="E98">
+        <v>48.9828</v>
+      </c>
+      <c r="F98">
+        <v>50.8128</v>
+      </c>
+      <c r="G98">
+        <v>12.5</v>
+      </c>
+      <c r="H98">
+        <v>51.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.98</v>
+      </c>
+      <c r="K98">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L98">
+        <v>2.27</v>
+      </c>
+      <c r="M98">
+        <v>12.13409664</v>
+      </c>
+      <c r="N98">
+        <v>-9.86409664</v>
+      </c>
+      <c r="O98">
+        <v>-2.3673831936</v>
+      </c>
+      <c r="P98">
+        <v>-7.496713446399999</v>
+      </c>
+      <c r="Q98">
+        <v>0.2132865536000015</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.820876650793493</v>
+      </c>
+      <c r="T98">
+        <v>28.04961859864239</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04489827435559306</v>
+      </c>
+      <c r="W98">
+        <v>0.2280782920838844</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1870761431483045</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2937902264322688</v>
+      </c>
+      <c r="C99">
+        <v>-24.36242754589022</v>
+      </c>
+      <c r="D99">
+        <v>14.47967245410978</v>
+      </c>
+      <c r="E99">
+        <v>49.5121</v>
+      </c>
+      <c r="F99">
+        <v>51.34209999999999</v>
+      </c>
+      <c r="G99">
+        <v>12.5</v>
+      </c>
+      <c r="H99">
+        <v>51.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.98</v>
+      </c>
+      <c r="K99">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L99">
+        <v>2.27</v>
+      </c>
+      <c r="M99">
+        <v>12.26049348</v>
+      </c>
+      <c r="N99">
+        <v>-9.99049348</v>
+      </c>
+      <c r="O99">
+        <v>-2.3977184352</v>
+      </c>
+      <c r="P99">
+        <v>-7.5927750448</v>
+      </c>
+      <c r="Q99">
+        <v>0.1172249552000011</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.414902201057992</v>
+      </c>
+      <c r="T99">
+        <v>37.39949146485652</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04443540554780344</v>
+      </c>
+      <c r="W99">
+        <v>0.2281888251551845</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1851475231158477</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2957902264322688</v>
+      </c>
+      <c r="C100">
+        <v>-24.99382453221865</v>
+      </c>
+      <c r="D100">
+        <v>14.37757546778135</v>
+      </c>
+      <c r="E100">
+        <v>50.0414</v>
+      </c>
+      <c r="F100">
+        <v>51.8714</v>
+      </c>
+      <c r="G100">
+        <v>12.5</v>
+      </c>
+      <c r="H100">
+        <v>51.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.98</v>
+      </c>
+      <c r="K100">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L100">
+        <v>2.27</v>
+      </c>
+      <c r="M100">
+        <v>12.38689032</v>
+      </c>
+      <c r="N100">
+        <v>-10.11689032</v>
+      </c>
+      <c r="O100">
+        <v>-2.4280536768</v>
+      </c>
+      <c r="P100">
+        <v>-7.688836643200001</v>
+      </c>
+      <c r="Q100">
+        <v>0.02116335679999981</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.602953301586987</v>
+      </c>
+      <c r="T100">
+        <v>56.09923719728477</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0439819830422136</v>
+      </c>
+      <c r="W100">
+        <v>0.2282971024495194</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1832582626758901</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2977902264322688</v>
+      </c>
+      <c r="C101">
+        <v>-25.62379181625205</v>
+      </c>
+      <c r="D101">
+        <v>14.27690818374795</v>
+      </c>
+      <c r="E101">
+        <v>50.5707</v>
+      </c>
+      <c r="F101">
+        <v>52.4007</v>
+      </c>
+      <c r="G101">
+        <v>12.5</v>
+      </c>
+      <c r="H101">
+        <v>51.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.98</v>
+      </c>
+      <c r="K101">
+        <v>7.710000000000001</v>
+      </c>
+      <c r="L101">
+        <v>2.27</v>
+      </c>
+      <c r="M101">
+        <v>12.51328716</v>
+      </c>
+      <c r="N101">
+        <v>-10.24328716</v>
+      </c>
+      <c r="O101">
+        <v>-2.4583889184</v>
+      </c>
+      <c r="P101">
+        <v>-7.784898241600001</v>
+      </c>
+      <c r="Q101">
+        <v>-0.07489824159999969</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.167106603173974</v>
+      </c>
+      <c r="T101">
+        <v>112.1984743945695</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04353772058724175</v>
+      </c>
+      <c r="W101">
+        <v>0.2284031923237667</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1814071691135073</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_telecom_equipment.xlsx
@@ -1641,7 +1641,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1778,22 +1778,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1153387510399289</v>
+        <v>0.1150961380374331</v>
       </c>
       <c r="C2">
-        <v>10.20755170608412</v>
+        <v>10.13780581916925</v>
       </c>
       <c r="D2">
-        <v>10.12655170608412</v>
+        <v>10.16200581916925</v>
       </c>
       <c r="E2">
-        <v>-4.61</v>
+        <v>-4.5048</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1052</v>
       </c>
       <c r="G2">
         <v>0.081</v>
@@ -1814,28 +1814,28 @@
         <v>1.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00529156</v>
       </c>
       <c r="N2">
-        <v>1.2</v>
+        <v>1.19470844</v>
       </c>
       <c r="O2">
-        <v>0.288</v>
+        <v>0.2867300255999999</v>
       </c>
       <c r="P2">
-        <v>0.9119999999999999</v>
+        <v>0.9079784143999999</v>
       </c>
       <c r="Q2">
-        <v>1.432</v>
+        <v>1.4279784144</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1153387510399289</v>
+        <v>0.1158725838761951</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181524431940836</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>226.776224780594</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1860,22 +1860,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1150961380374331</v>
+        <v>0.1148535250349373</v>
       </c>
       <c r="C3">
-        <v>10.13780581916925</v>
+        <v>10.06830906157319</v>
       </c>
       <c r="D3">
-        <v>10.16200581916925</v>
+        <v>10.19770906157319</v>
       </c>
       <c r="E3">
-        <v>-4.5048</v>
+        <v>-4.3996</v>
       </c>
       <c r="F3">
-        <v>0.1052</v>
+        <v>0.2104</v>
       </c>
       <c r="G3">
         <v>0.081</v>
@@ -1896,28 +1896,28 @@
         <v>1.2</v>
       </c>
       <c r="M3">
-        <v>0.00529156</v>
+        <v>0.01058312</v>
       </c>
       <c r="N3">
-        <v>1.19470844</v>
+        <v>1.18941688</v>
       </c>
       <c r="O3">
-        <v>0.2867300255999999</v>
+        <v>0.2854600512</v>
       </c>
       <c r="P3">
-        <v>0.9079784143999999</v>
+        <v>0.9039568287999999</v>
       </c>
       <c r="Q3">
-        <v>1.4279784144</v>
+        <v>1.4239568288</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1158725838761951</v>
+        <v>0.1164173112601401</v>
       </c>
       <c r="T3">
-        <v>1.181524431940836</v>
+        <v>1.19070931820128</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.776224780594</v>
+        <v>113.388112390297</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1942,22 +1942,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1148535250349373</v>
+        <v>0.1146109120324415</v>
       </c>
       <c r="C4">
-        <v>10.06830906157319</v>
+        <v>9.999064068430833</v>
       </c>
       <c r="D4">
-        <v>10.19770906157319</v>
+        <v>10.23366406843083</v>
       </c>
       <c r="E4">
-        <v>-4.3996</v>
+        <v>-4.2944</v>
       </c>
       <c r="F4">
-        <v>0.2104</v>
+        <v>0.3156</v>
       </c>
       <c r="G4">
         <v>0.081</v>
@@ -1978,28 +1978,28 @@
         <v>1.2</v>
       </c>
       <c r="M4">
-        <v>0.01058312</v>
+        <v>0.01587468</v>
       </c>
       <c r="N4">
-        <v>1.18941688</v>
+        <v>1.18412532</v>
       </c>
       <c r="O4">
-        <v>0.2854600512</v>
+        <v>0.2841900768</v>
       </c>
       <c r="P4">
-        <v>0.9039568287999999</v>
+        <v>0.8999352432</v>
       </c>
       <c r="Q4">
-        <v>1.4239568288</v>
+        <v>1.4199352432</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1164173112601401</v>
+        <v>0.1169732701365376</v>
       </c>
       <c r="T4">
-        <v>1.19070931820128</v>
+        <v>1.200083583559878</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.388112390297</v>
+        <v>75.59207492686467</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2024,22 +2024,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1146109120324415</v>
+        <v>0.1143682990299456</v>
       </c>
       <c r="C5">
-        <v>9.999064068430833</v>
+        <v>9.930073512172342</v>
       </c>
       <c r="D5">
-        <v>10.23366406843083</v>
+        <v>10.26987351217234</v>
       </c>
       <c r="E5">
-        <v>-4.2944</v>
+        <v>-4.1892</v>
       </c>
       <c r="F5">
-        <v>0.3156</v>
+        <v>0.4208</v>
       </c>
       <c r="G5">
         <v>0.081</v>
@@ -2060,28 +2060,28 @@
         <v>1.2</v>
       </c>
       <c r="M5">
-        <v>0.01587468</v>
+        <v>0.02116624</v>
       </c>
       <c r="N5">
-        <v>1.18412532</v>
+        <v>1.17883376</v>
       </c>
       <c r="O5">
-        <v>0.2841900768</v>
+        <v>0.2829201024</v>
       </c>
       <c r="P5">
-        <v>0.8999352432</v>
+        <v>0.8959136576000001</v>
       </c>
       <c r="Q5">
-        <v>1.4199352432</v>
+        <v>1.4159136576</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1169732701365376</v>
+        <v>0.1175408114895267</v>
       </c>
       <c r="T5">
-        <v>1.200083583559878</v>
+        <v>1.209653146113446</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.59207492686467</v>
+        <v>56.69405619514851</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2106,22 +2106,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1143682990299456</v>
+        <v>0.1141256860274498</v>
       </c>
       <c r="C6">
-        <v>9.930073512172342</v>
+        <v>9.86134010318527</v>
       </c>
       <c r="D6">
-        <v>10.26987351217234</v>
+        <v>10.30634010318527</v>
       </c>
       <c r="E6">
-        <v>-4.1892</v>
+        <v>-4.084000000000001</v>
       </c>
       <c r="F6">
-        <v>0.4208</v>
+        <v>0.526</v>
       </c>
       <c r="G6">
         <v>0.081</v>
@@ -2142,28 +2142,28 @@
         <v>1.2</v>
       </c>
       <c r="M6">
-        <v>0.02116624</v>
+        <v>0.0264578</v>
       </c>
       <c r="N6">
-        <v>1.17883376</v>
+        <v>1.1735422</v>
       </c>
       <c r="O6">
-        <v>0.2829201024</v>
+        <v>0.281650128</v>
       </c>
       <c r="P6">
-        <v>0.8959136576000001</v>
+        <v>0.891892072</v>
       </c>
       <c r="Q6">
-        <v>1.4159136576</v>
+        <v>1.411892072</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1175408114895267</v>
+        <v>0.1181203010815261</v>
       </c>
       <c r="T6">
-        <v>1.209653146113446</v>
+        <v>1.219424173141826</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.69405619514851</v>
+        <v>45.3552449561188</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2188,22 +2188,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1141256860274498</v>
+        <v>0.113883073024954</v>
       </c>
       <c r="C7">
-        <v>9.86134010318527</v>
+        <v>9.792866590490865</v>
       </c>
       <c r="D7">
-        <v>10.30634010318527</v>
+        <v>10.34306659049087</v>
       </c>
       <c r="E7">
-        <v>-4.084000000000001</v>
+        <v>-3.978800000000001</v>
       </c>
       <c r="F7">
-        <v>0.526</v>
+        <v>0.6312</v>
       </c>
       <c r="G7">
         <v>0.081</v>
@@ -2224,28 +2224,28 @@
         <v>1.2</v>
       </c>
       <c r="M7">
-        <v>0.0264578</v>
+        <v>0.03174936</v>
       </c>
       <c r="N7">
-        <v>1.1735422</v>
+        <v>1.16825064</v>
       </c>
       <c r="O7">
-        <v>0.281650128</v>
+        <v>0.2803801536</v>
       </c>
       <c r="P7">
-        <v>0.891892072</v>
+        <v>0.8878704864</v>
       </c>
       <c r="Q7">
-        <v>1.411892072</v>
+        <v>1.4078704864</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1181203010815261</v>
+        <v>0.1187121202393127</v>
       </c>
       <c r="T7">
-        <v>1.219424173141826</v>
+        <v>1.229403094362299</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.3552449561188</v>
+        <v>37.79603746343233</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2270,22 +2270,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.113883073024954</v>
+        <v>0.1136404600224581</v>
       </c>
       <c r="C8">
-        <v>9.792866590490865</v>
+        <v>9.724655762434901</v>
       </c>
       <c r="D8">
-        <v>10.34306659049087</v>
+        <v>10.3800557624349</v>
       </c>
       <c r="E8">
-        <v>-3.978800000000001</v>
+        <v>-3.873600000000001</v>
       </c>
       <c r="F8">
-        <v>0.6312</v>
+        <v>0.7363999999999999</v>
       </c>
       <c r="G8">
         <v>0.081</v>
@@ -2306,28 +2306,28 @@
         <v>1.2</v>
       </c>
       <c r="M8">
-        <v>0.03174936</v>
+        <v>0.03704092</v>
       </c>
       <c r="N8">
-        <v>1.16825064</v>
+        <v>1.16295908</v>
       </c>
       <c r="O8">
-        <v>0.2803801536</v>
+        <v>0.2791101792</v>
       </c>
       <c r="P8">
-        <v>0.8878704864</v>
+        <v>0.8838489008000001</v>
       </c>
       <c r="Q8">
-        <v>1.4078704864</v>
+        <v>1.4038489008</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1187121202393127</v>
+        <v>0.1193166666908152</v>
       </c>
       <c r="T8">
-        <v>1.229403094362299</v>
+        <v>1.239596616039126</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.79603746343233</v>
+        <v>32.39660354008486</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2352,22 +2352,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1136404600224581</v>
+        <v>0.1133978470199623</v>
       </c>
       <c r="C9">
-        <v>9.724655762434903</v>
+        <v>9.656710447393356</v>
       </c>
       <c r="D9">
-        <v>10.3800557624349</v>
+        <v>10.41731044739336</v>
       </c>
       <c r="E9">
-        <v>-3.8736</v>
+        <v>-3.7684</v>
       </c>
       <c r="F9">
-        <v>0.7364000000000001</v>
+        <v>0.8416</v>
       </c>
       <c r="G9">
         <v>0.081</v>
@@ -2388,28 +2388,28 @@
         <v>1.2</v>
       </c>
       <c r="M9">
-        <v>0.03704092</v>
+        <v>0.04233248</v>
       </c>
       <c r="N9">
-        <v>1.16295908</v>
+        <v>1.15766752</v>
       </c>
       <c r="O9">
-        <v>0.2791101792</v>
+        <v>0.2778402048</v>
       </c>
       <c r="P9">
-        <v>0.8838489008000001</v>
+        <v>0.8798273152</v>
       </c>
       <c r="Q9">
-        <v>1.4038489008</v>
+        <v>1.3998273152</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1193166666908152</v>
+        <v>0.1199343554564808</v>
       </c>
       <c r="T9">
-        <v>1.239596616039126</v>
+        <v>1.250011736013276</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.39660354008486</v>
+        <v>28.34702809757425</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2434,22 +2434,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1133978470199623</v>
+        <v>0.1131552340174665</v>
       </c>
       <c r="C10">
-        <v>9.656710447393356</v>
+        <v>9.58903351449335</v>
       </c>
       <c r="D10">
-        <v>10.41731044739336</v>
+        <v>10.45483351449335</v>
       </c>
       <c r="E10">
-        <v>-3.7684</v>
+        <v>-3.6632</v>
       </c>
       <c r="F10">
-        <v>0.8416</v>
+        <v>0.9468</v>
       </c>
       <c r="G10">
         <v>0.081</v>
@@ -2470,28 +2470,28 @@
         <v>1.2</v>
       </c>
       <c r="M10">
-        <v>0.04233248</v>
+        <v>0.04762404</v>
       </c>
       <c r="N10">
-        <v>1.15766752</v>
+        <v>1.15237596</v>
       </c>
       <c r="O10">
-        <v>0.2778402048</v>
+        <v>0.2765702304</v>
       </c>
       <c r="P10">
-        <v>0.8798273152</v>
+        <v>0.8758057295999999</v>
       </c>
       <c r="Q10">
-        <v>1.3998273152</v>
+        <v>1.3958057296</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1199343554564808</v>
+        <v>0.1205656197994137</v>
       </c>
       <c r="T10">
-        <v>1.250011736013276</v>
+        <v>1.260655759723121</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.34702809757425</v>
+        <v>25.19735830895489</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2516,22 +2516,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1131552340174665</v>
+        <v>0.1129126210149707</v>
       </c>
       <c r="C11">
-        <v>9.58903351449335</v>
+        <v>9.521627874349738</v>
       </c>
       <c r="D11">
-        <v>10.45483351449335</v>
+        <v>10.49262787434974</v>
       </c>
       <c r="E11">
-        <v>-3.6632</v>
+        <v>-3.558000000000001</v>
       </c>
       <c r="F11">
-        <v>0.9468</v>
+        <v>1.052</v>
       </c>
       <c r="G11">
         <v>0.081</v>
@@ -2552,28 +2552,28 @@
         <v>1.2</v>
       </c>
       <c r="M11">
-        <v>0.04762404</v>
+        <v>0.05291559999999999</v>
       </c>
       <c r="N11">
-        <v>1.15237596</v>
+        <v>1.1470844</v>
       </c>
       <c r="O11">
-        <v>0.2765702304</v>
+        <v>0.275300256</v>
       </c>
       <c r="P11">
-        <v>0.8758057295999999</v>
+        <v>0.871784144</v>
       </c>
       <c r="Q11">
-        <v>1.3958057296</v>
+        <v>1.391784144</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1205656197994137</v>
+        <v>0.1212109122388563</v>
       </c>
       <c r="T11">
-        <v>1.260655759723121</v>
+        <v>1.271536317293186</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.19735830895489</v>
+        <v>22.6776224780594</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2598,22 +2598,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1129126210149707</v>
+        <v>0.1126700080124748</v>
       </c>
       <c r="C12">
-        <v>9.521627874349738</v>
+        <v>9.45449647981772</v>
       </c>
       <c r="D12">
-        <v>10.49262787434974</v>
+        <v>10.53069647981772</v>
       </c>
       <c r="E12">
-        <v>-3.558</v>
+        <v>-3.4528</v>
       </c>
       <c r="F12">
-        <v>1.052</v>
+        <v>1.1572</v>
       </c>
       <c r="G12">
         <v>0.081</v>
@@ -2634,28 +2634,28 @@
         <v>1.2</v>
       </c>
       <c r="M12">
-        <v>0.0529156</v>
+        <v>0.05820716</v>
       </c>
       <c r="N12">
-        <v>1.1470844</v>
+        <v>1.14179284</v>
       </c>
       <c r="O12">
-        <v>0.275300256</v>
+        <v>0.2740302816</v>
       </c>
       <c r="P12">
-        <v>0.871784144</v>
+        <v>0.8677625583999999</v>
       </c>
       <c r="Q12">
-        <v>1.391784144</v>
+        <v>1.3877625584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1212109122388563</v>
+        <v>0.1218707056319942</v>
       </c>
       <c r="T12">
-        <v>1.271536317293186</v>
+        <v>1.282661381774937</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.6776224780594</v>
+        <v>20.61602043459945</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2680,22 +2680,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1126700080124748</v>
+        <v>0.112427395009979</v>
       </c>
       <c r="C13">
-        <v>9.45449647981772</v>
+        <v>9.387642326761879</v>
       </c>
       <c r="D13">
-        <v>10.53069647981772</v>
+        <v>10.56904232676188</v>
       </c>
       <c r="E13">
-        <v>-3.4528</v>
+        <v>-3.3476</v>
       </c>
       <c r="F13">
-        <v>1.1572</v>
+        <v>1.2624</v>
       </c>
       <c r="G13">
         <v>0.081</v>
@@ -2716,28 +2716,28 @@
         <v>1.2</v>
       </c>
       <c r="M13">
-        <v>0.05820716</v>
+        <v>0.06349871999999999</v>
       </c>
       <c r="N13">
-        <v>1.14179284</v>
+        <v>1.13650128</v>
       </c>
       <c r="O13">
-        <v>0.2740302816</v>
+        <v>0.2727603072</v>
       </c>
       <c r="P13">
-        <v>0.8677625583999999</v>
+        <v>0.8637409728000001</v>
       </c>
       <c r="Q13">
-        <v>1.3877625584</v>
+        <v>1.3837409728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1218707056319942</v>
+        <v>0.1225454943295216</v>
       </c>
       <c r="T13">
-        <v>1.282661381774937</v>
+        <v>1.294039288631273</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.61602043459945</v>
+        <v>18.89801873171617</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2762,22 +2762,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.112427395009979</v>
+        <v>0.1121847820074832</v>
       </c>
       <c r="C14">
-        <v>9.387642326761879</v>
+        <v>9.321068454842141</v>
       </c>
       <c r="D14">
-        <v>10.56904232676188</v>
+        <v>10.60766845484214</v>
       </c>
       <c r="E14">
-        <v>-3.3476</v>
+        <v>-3.2424</v>
       </c>
       <c r="F14">
-        <v>1.2624</v>
+        <v>1.3676</v>
       </c>
       <c r="G14">
         <v>0.081</v>
@@ -2798,28 +2798,28 @@
         <v>1.2</v>
       </c>
       <c r="M14">
-        <v>0.06349871999999999</v>
+        <v>0.06879028</v>
       </c>
       <c r="N14">
-        <v>1.13650128</v>
+        <v>1.13120972</v>
       </c>
       <c r="O14">
-        <v>0.2727603072</v>
+        <v>0.2714903328</v>
       </c>
       <c r="P14">
-        <v>0.8637409728000001</v>
+        <v>0.8597193872</v>
       </c>
       <c r="Q14">
-        <v>1.3837409728</v>
+        <v>1.3797193872</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1225454943295216</v>
+        <v>0.1232357954109002</v>
       </c>
       <c r="T14">
-        <v>1.294039288631273</v>
+        <v>1.305678756564766</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.89801873171617</v>
+        <v>17.44432498312262</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2844,22 +2844,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1121847820074832</v>
+        <v>0.1119421690049873</v>
       </c>
       <c r="C15">
-        <v>9.321068454842141</v>
+        <v>9.254777948316955</v>
       </c>
       <c r="D15">
-        <v>10.60766845484214</v>
+        <v>10.64657794831695</v>
       </c>
       <c r="E15">
-        <v>-3.2424</v>
+        <v>-3.1372</v>
       </c>
       <c r="F15">
-        <v>1.3676</v>
+        <v>1.4728</v>
       </c>
       <c r="G15">
         <v>0.081</v>
@@ -2880,28 +2880,28 @@
         <v>1.2</v>
       </c>
       <c r="M15">
-        <v>0.06879028</v>
+        <v>0.07408184</v>
       </c>
       <c r="N15">
-        <v>1.13120972</v>
+        <v>1.12591816</v>
       </c>
       <c r="O15">
-        <v>0.2714903328</v>
+        <v>0.2702203584</v>
       </c>
       <c r="P15">
-        <v>0.8597193872</v>
+        <v>0.8556978015999999</v>
       </c>
       <c r="Q15">
-        <v>1.3797193872</v>
+        <v>1.3756978016</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1232357954109002</v>
+        <v>0.1239421500057992</v>
       </c>
       <c r="T15">
-        <v>1.305678756564766</v>
+        <v>1.317588909799039</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.44432498312262</v>
+        <v>16.19830177004243</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2926,22 +2926,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1119421690049873</v>
+        <v>0.1116995560024915</v>
       </c>
       <c r="C16">
-        <v>9.254777948316955</v>
+        <v>9.188773936864273</v>
       </c>
       <c r="D16">
-        <v>10.64657794831695</v>
+        <v>10.68577393686427</v>
       </c>
       <c r="E16">
-        <v>-3.1372</v>
+        <v>-3.032</v>
       </c>
       <c r="F16">
-        <v>1.4728</v>
+        <v>1.578</v>
       </c>
       <c r="G16">
         <v>0.081</v>
@@ -2962,28 +2962,28 @@
         <v>1.2</v>
       </c>
       <c r="M16">
-        <v>0.07408184</v>
+        <v>0.0793734</v>
       </c>
       <c r="N16">
-        <v>1.12591816</v>
+        <v>1.1206266</v>
       </c>
       <c r="O16">
-        <v>0.2702203584</v>
+        <v>0.268950384</v>
       </c>
       <c r="P16">
-        <v>0.8556978015999999</v>
+        <v>0.851676216</v>
       </c>
       <c r="Q16">
-        <v>1.3756978016</v>
+        <v>1.371676216</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1239421500057992</v>
+        <v>0.1246651247088136</v>
       </c>
       <c r="T16">
-        <v>1.317588909799039</v>
+        <v>1.329779301932941</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.19830177004243</v>
+        <v>15.11841498537293</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3008,22 +3008,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1116995560024915</v>
+        <v>0.1114569429999957</v>
       </c>
       <c r="C17">
-        <v>9.188773936864273</v>
+        <v>9.123059596420712</v>
       </c>
       <c r="D17">
-        <v>10.68577393686427</v>
+        <v>10.72525959642071</v>
       </c>
       <c r="E17">
-        <v>-3.032</v>
+        <v>-2.9268</v>
       </c>
       <c r="F17">
-        <v>1.578</v>
+        <v>1.6832</v>
       </c>
       <c r="G17">
         <v>0.081</v>
@@ -3044,28 +3044,28 @@
         <v>1.2</v>
       </c>
       <c r="M17">
-        <v>0.07937339999999998</v>
+        <v>0.08466496</v>
       </c>
       <c r="N17">
-        <v>1.1206266</v>
+        <v>1.11533504</v>
       </c>
       <c r="O17">
-        <v>0.268950384</v>
+        <v>0.2676804096</v>
       </c>
       <c r="P17">
-        <v>0.851676216</v>
+        <v>0.8476546303999999</v>
       </c>
       <c r="Q17">
-        <v>1.371676216</v>
+        <v>1.3676546304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1246651247088136</v>
+        <v>0.125405313095233</v>
       </c>
       <c r="T17">
-        <v>1.329779301932941</v>
+        <v>1.342259941498603</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.11841498537294</v>
+        <v>14.17351404878712</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3090,22 +3090,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1114569429999957</v>
+        <v>0.1112143299974998</v>
       </c>
       <c r="C18">
-        <v>9.123059596420712</v>
+        <v>9.057638150039379</v>
       </c>
       <c r="D18">
-        <v>10.72525959642071</v>
+        <v>10.76503815003938</v>
       </c>
       <c r="E18">
-        <v>-2.9268</v>
+        <v>-2.8216</v>
       </c>
       <c r="F18">
-        <v>1.6832</v>
+        <v>1.7884</v>
       </c>
       <c r="G18">
         <v>0.081</v>
@@ -3126,28 +3126,28 @@
         <v>1.2</v>
       </c>
       <c r="M18">
-        <v>0.08466496</v>
+        <v>0.08995652</v>
       </c>
       <c r="N18">
-        <v>1.11533504</v>
+        <v>1.11004348</v>
       </c>
       <c r="O18">
-        <v>0.2676804096</v>
+        <v>0.2664104352</v>
       </c>
       <c r="P18">
-        <v>0.8476546303999999</v>
+        <v>0.8436330447999999</v>
       </c>
       <c r="Q18">
-        <v>1.3676546304</v>
+        <v>1.3636330448</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.125405313095233</v>
+        <v>0.1261633373463854</v>
       </c>
       <c r="T18">
-        <v>1.342259941498603</v>
+        <v>1.355041319367052</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.17351404878712</v>
+        <v>13.33977792827023</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3172,22 +3172,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1112143299974998</v>
+        <v>0.111176916995004</v>
       </c>
       <c r="C19">
-        <v>9.057638150039379</v>
+        <v>8.958598617948962</v>
       </c>
       <c r="D19">
-        <v>10.76503815003938</v>
+        <v>10.77119861794896</v>
       </c>
       <c r="E19">
-        <v>-2.8216</v>
+        <v>-2.7164</v>
       </c>
       <c r="F19">
-        <v>1.7884</v>
+        <v>1.8936</v>
       </c>
       <c r="G19">
         <v>0.081</v>
@@ -3208,45 +3208,45 @@
         <v>1.2</v>
       </c>
       <c r="M19">
-        <v>0.08995652</v>
+        <v>0.09808848000000001</v>
       </c>
       <c r="N19">
-        <v>1.11004348</v>
+        <v>1.10191152</v>
       </c>
       <c r="O19">
-        <v>0.2664104352</v>
+        <v>0.2644587648</v>
       </c>
       <c r="P19">
-        <v>0.8436330447999999</v>
+        <v>0.8374527552</v>
       </c>
       <c r="Q19">
-        <v>1.3636330448</v>
+        <v>1.3574527552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1261633373463854</v>
+        <v>0.1269398499939073</v>
       </c>
       <c r="T19">
-        <v>1.355041319367052</v>
+        <v>1.368134438159121</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.33977792827023</v>
+        <v>12.23385253803505</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3254,22 +3254,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.111176916995004</v>
+        <v>0.1109457039925082</v>
       </c>
       <c r="C20">
-        <v>8.958598617948962</v>
+        <v>8.891627403890418</v>
       </c>
       <c r="D20">
-        <v>10.77119861794896</v>
+        <v>10.80942740389042</v>
       </c>
       <c r="E20">
-        <v>-2.7164</v>
+        <v>-2.6112</v>
       </c>
       <c r="F20">
-        <v>1.8936</v>
+        <v>1.9988</v>
       </c>
       <c r="G20">
         <v>0.081</v>
@@ -3290,28 +3290,28 @@
         <v>1.2</v>
       </c>
       <c r="M20">
-        <v>0.09808847999999999</v>
+        <v>0.10353784</v>
       </c>
       <c r="N20">
-        <v>1.10191152</v>
+        <v>1.09646216</v>
       </c>
       <c r="O20">
-        <v>0.2644587648</v>
+        <v>0.2631509184</v>
       </c>
       <c r="P20">
-        <v>0.8374527552</v>
+        <v>0.8333112415999999</v>
       </c>
       <c r="Q20">
-        <v>1.3574527552</v>
+        <v>1.3533112416</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1269398499939073</v>
+        <v>0.12773553579322</v>
       </c>
       <c r="T20">
-        <v>1.368134438159121</v>
+        <v>1.381550843834946</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.23385253803505</v>
+        <v>11.58996556234899</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3336,22 +3336,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1109457039925082</v>
+        <v>0.1107144909900124</v>
       </c>
       <c r="C21">
-        <v>8.891627403890418</v>
+        <v>8.824928517080977</v>
       </c>
       <c r="D21">
-        <v>10.80942740389042</v>
+        <v>10.84792851708098</v>
       </c>
       <c r="E21">
-        <v>-2.6112</v>
+        <v>-2.506</v>
       </c>
       <c r="F21">
-        <v>1.9988</v>
+        <v>2.104</v>
       </c>
       <c r="G21">
         <v>0.081</v>
@@ -3372,28 +3372,28 @@
         <v>1.2</v>
       </c>
       <c r="M21">
-        <v>0.10353784</v>
+        <v>0.1089872</v>
       </c>
       <c r="N21">
-        <v>1.09646216</v>
+        <v>1.0910128</v>
       </c>
       <c r="O21">
-        <v>0.2631509184</v>
+        <v>0.261843072</v>
       </c>
       <c r="P21">
-        <v>0.8333112415999999</v>
+        <v>0.8291697279999999</v>
       </c>
       <c r="Q21">
-        <v>1.3533112416</v>
+        <v>1.349169728</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.12773553579322</v>
+        <v>0.1285511137375155</v>
       </c>
       <c r="T21">
-        <v>1.381550843834946</v>
+        <v>1.395302659652666</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.58996556234899</v>
+        <v>11.01046728423154</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3418,22 +3418,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1107144909900124</v>
+        <v>0.1104832779875165</v>
       </c>
       <c r="C22">
-        <v>8.824928517080977</v>
+        <v>8.758504877855064</v>
       </c>
       <c r="D22">
-        <v>10.84792851708098</v>
+        <v>10.88670487785506</v>
       </c>
       <c r="E22">
-        <v>-2.506</v>
+        <v>-2.4008</v>
       </c>
       <c r="F22">
-        <v>2.104</v>
+        <v>2.2092</v>
       </c>
       <c r="G22">
         <v>0.081</v>
@@ -3454,28 +3454,28 @@
         <v>1.2</v>
       </c>
       <c r="M22">
-        <v>0.1089872</v>
+        <v>0.11443656</v>
       </c>
       <c r="N22">
-        <v>1.0910128</v>
+        <v>1.08556344</v>
       </c>
       <c r="O22">
-        <v>0.261843072</v>
+        <v>0.2605352256</v>
       </c>
       <c r="P22">
-        <v>0.8291697279999999</v>
+        <v>0.8250282144000001</v>
       </c>
       <c r="Q22">
-        <v>1.349169728</v>
+        <v>1.3450282144</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1285511137375155</v>
+        <v>0.1293873392247045</v>
       </c>
       <c r="T22">
-        <v>1.395302659652666</v>
+        <v>1.409402622706277</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.01046728423154</v>
+        <v>10.48615931831575</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3500,22 +3500,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1104832779875165</v>
+        <v>0.1102520649850207</v>
       </c>
       <c r="C23">
-        <v>8.758504877855064</v>
+        <v>8.692359448452294</v>
       </c>
       <c r="D23">
-        <v>10.88670487785506</v>
+        <v>10.92575944845229</v>
       </c>
       <c r="E23">
-        <v>-2.400800000000001</v>
+        <v>-2.2956</v>
       </c>
       <c r="F23">
-        <v>2.2092</v>
+        <v>2.3144</v>
       </c>
       <c r="G23">
         <v>0.081</v>
@@ -3536,28 +3536,28 @@
         <v>1.2</v>
       </c>
       <c r="M23">
-        <v>0.11443656</v>
+        <v>0.11988592</v>
       </c>
       <c r="N23">
-        <v>1.08556344</v>
+        <v>1.08011408</v>
       </c>
       <c r="O23">
-        <v>0.2605352256</v>
+        <v>0.2592273792</v>
       </c>
       <c r="P23">
-        <v>0.8250282144000001</v>
+        <v>0.8208867008</v>
       </c>
       <c r="Q23">
-        <v>1.3450282144</v>
+        <v>1.3408867008</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1293873392247045</v>
+        <v>0.1302450063910522</v>
       </c>
       <c r="T23">
-        <v>1.409402622706277</v>
+        <v>1.423864123274084</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.48615931831576</v>
+        <v>10.00951571293777</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3582,22 +3582,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1102520649850207</v>
+        <v>0.1103180119825249</v>
       </c>
       <c r="C24">
-        <v>8.692359448452294</v>
+        <v>8.575991698409506</v>
       </c>
       <c r="D24">
-        <v>10.92575944845229</v>
+        <v>10.91459169840951</v>
       </c>
       <c r="E24">
-        <v>-2.2956</v>
+        <v>-2.1904</v>
       </c>
       <c r="F24">
-        <v>2.3144</v>
+        <v>2.4196</v>
       </c>
       <c r="G24">
         <v>0.081</v>
@@ -3618,45 +3618,45 @@
         <v>1.2</v>
       </c>
       <c r="M24">
-        <v>0.11988592</v>
+        <v>0.1294486</v>
       </c>
       <c r="N24">
-        <v>1.08011408</v>
+        <v>1.0705514</v>
       </c>
       <c r="O24">
-        <v>0.2592273792</v>
+        <v>0.256932336</v>
       </c>
       <c r="P24">
-        <v>0.8208867008</v>
+        <v>0.8136190640000001</v>
       </c>
       <c r="Q24">
-        <v>1.3408867008</v>
+        <v>1.333619064</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1302450063910522</v>
+        <v>0.1311249506266557</v>
       </c>
       <c r="T24">
-        <v>1.423864123274084</v>
+        <v>1.438701247233263</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.00951571293777</v>
+        <v>9.270088668398113</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3664,22 +3664,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1103180119825249</v>
+        <v>0.110099718980029</v>
       </c>
       <c r="C25">
-        <v>8.575991698409506</v>
+        <v>8.507845965996619</v>
       </c>
       <c r="D25">
-        <v>10.91459169840951</v>
+        <v>10.95164596599662</v>
       </c>
       <c r="E25">
-        <v>-2.1904</v>
+        <v>-2.0852</v>
       </c>
       <c r="F25">
-        <v>2.4196</v>
+        <v>2.5248</v>
       </c>
       <c r="G25">
         <v>0.081</v>
@@ -3700,28 +3700,28 @@
         <v>1.2</v>
       </c>
       <c r="M25">
-        <v>0.1294486</v>
+        <v>0.1350768</v>
       </c>
       <c r="N25">
-        <v>1.0705514</v>
+        <v>1.0649232</v>
       </c>
       <c r="O25">
-        <v>0.256932336</v>
+        <v>0.255581568</v>
       </c>
       <c r="P25">
-        <v>0.8136190640000001</v>
+        <v>0.809341632</v>
       </c>
       <c r="Q25">
-        <v>1.333619064</v>
+        <v>1.329341632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1311249506266557</v>
+        <v>0.1320280512895119</v>
       </c>
       <c r="T25">
-        <v>1.438701247233263</v>
+        <v>1.453928821822946</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.270088668398113</v>
+        <v>8.883834973881525</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3746,22 +3746,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.110099718980029</v>
+        <v>0.1098814259775332</v>
       </c>
       <c r="C26">
-        <v>8.507845965996619</v>
+        <v>8.439952683875006</v>
       </c>
       <c r="D26">
-        <v>10.95164596599662</v>
+        <v>10.98895268387501</v>
       </c>
       <c r="E26">
-        <v>-2.0852</v>
+        <v>-1.98</v>
       </c>
       <c r="F26">
-        <v>2.5248</v>
+        <v>2.63</v>
       </c>
       <c r="G26">
         <v>0.081</v>
@@ -3782,28 +3782,28 @@
         <v>1.2</v>
       </c>
       <c r="M26">
-        <v>0.1350768</v>
+        <v>0.140705</v>
       </c>
       <c r="N26">
-        <v>1.0649232</v>
+        <v>1.059295</v>
       </c>
       <c r="O26">
-        <v>0.255581568</v>
+        <v>0.2542308</v>
       </c>
       <c r="P26">
-        <v>0.809341632</v>
+        <v>0.8050641999999999</v>
       </c>
       <c r="Q26">
-        <v>1.329341632</v>
+        <v>1.3250642</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1320280512895119</v>
+        <v>0.132955234636711</v>
       </c>
       <c r="T26">
-        <v>1.453928821822946</v>
+        <v>1.469562465068354</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.883834973881525</v>
+        <v>8.528481574926264</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3828,22 +3828,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1098814259775332</v>
+        <v>0.1096631329750374</v>
       </c>
       <c r="C27">
-        <v>8.439952683875006</v>
+        <v>8.372314440774488</v>
       </c>
       <c r="D27">
-        <v>10.98895268387501</v>
+        <v>11.02651444077449</v>
       </c>
       <c r="E27">
-        <v>-1.98</v>
+        <v>-1.8748</v>
       </c>
       <c r="F27">
-        <v>2.63</v>
+        <v>2.7352</v>
       </c>
       <c r="G27">
         <v>0.081</v>
@@ -3864,28 +3864,28 @@
         <v>1.2</v>
       </c>
       <c r="M27">
-        <v>0.140705</v>
+        <v>0.1463332</v>
       </c>
       <c r="N27">
-        <v>1.059295</v>
+        <v>1.0536668</v>
       </c>
       <c r="O27">
-        <v>0.2542308</v>
+        <v>0.252880032</v>
       </c>
       <c r="P27">
-        <v>0.8050641999999999</v>
+        <v>0.800786768</v>
       </c>
       <c r="Q27">
-        <v>1.3250642</v>
+        <v>1.320786768</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.132955234636711</v>
+        <v>0.1339074769932938</v>
       </c>
       <c r="T27">
-        <v>1.469562465068354</v>
+        <v>1.485618639212286</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.528481574926264</v>
+        <v>8.200463052813717</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3910,22 +3910,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1096631329750374</v>
+        <v>0.1094448399725416</v>
       </c>
       <c r="C28">
-        <v>8.372314440774488</v>
+        <v>8.304933860940817</v>
       </c>
       <c r="D28">
-        <v>11.02651444077449</v>
+        <v>11.06433386094082</v>
       </c>
       <c r="E28">
-        <v>-1.8748</v>
+        <v>-1.7696</v>
       </c>
       <c r="F28">
-        <v>2.7352</v>
+        <v>2.8404</v>
       </c>
       <c r="G28">
         <v>0.081</v>
@@ -3946,28 +3946,28 @@
         <v>1.2</v>
       </c>
       <c r="M28">
-        <v>0.1463332</v>
+        <v>0.1519614</v>
       </c>
       <c r="N28">
-        <v>1.0536668</v>
+        <v>1.0480386</v>
       </c>
       <c r="O28">
-        <v>0.252880032</v>
+        <v>0.251529264</v>
       </c>
       <c r="P28">
-        <v>0.800786768</v>
+        <v>0.796509336</v>
       </c>
       <c r="Q28">
-        <v>1.320786768</v>
+        <v>1.316509336</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1339074769932938</v>
+        <v>0.1348858081815638</v>
       </c>
       <c r="T28">
-        <v>1.485618639212286</v>
+        <v>1.502114708538244</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.200463052813717</v>
+        <v>7.896742199005798</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3992,22 +3992,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1094448399725416</v>
+        <v>0.1092265469700457</v>
       </c>
       <c r="C29">
-        <v>8.304933860940817</v>
+        <v>8.237813604746856</v>
       </c>
       <c r="D29">
-        <v>11.06433386094082</v>
+        <v>11.10241360474686</v>
       </c>
       <c r="E29">
-        <v>-1.7696</v>
+        <v>-1.6644</v>
       </c>
       <c r="F29">
-        <v>2.8404</v>
+        <v>2.9456</v>
       </c>
       <c r="G29">
         <v>0.081</v>
@@ -4028,28 +4028,28 @@
         <v>1.2</v>
       </c>
       <c r="M29">
-        <v>0.1519614</v>
+        <v>0.1575896</v>
       </c>
       <c r="N29">
-        <v>1.0480386</v>
+        <v>1.0424104</v>
       </c>
       <c r="O29">
-        <v>0.251529264</v>
+        <v>0.250178496</v>
       </c>
       <c r="P29">
-        <v>0.796509336</v>
+        <v>0.7922319040000001</v>
       </c>
       <c r="Q29">
-        <v>1.316509336</v>
+        <v>1.312231904</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1348858081815638</v>
+        <v>0.1358913152361746</v>
       </c>
       <c r="T29">
-        <v>1.502114708538244</v>
+        <v>1.519069002012146</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.896742199005798</v>
+        <v>7.614715691898451</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4074,22 +4074,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1092265469700457</v>
+        <v>0.1091845739675499</v>
       </c>
       <c r="C30">
-        <v>8.237813604746856</v>
+        <v>8.139965577076593</v>
       </c>
       <c r="D30">
-        <v>11.10241360474686</v>
+        <v>11.10976557707659</v>
       </c>
       <c r="E30">
-        <v>-1.6644</v>
+        <v>-1.5592</v>
       </c>
       <c r="F30">
-        <v>2.9456</v>
+        <v>3.0508</v>
       </c>
       <c r="G30">
         <v>0.081</v>
@@ -4110,45 +4110,45 @@
         <v>1.2</v>
       </c>
       <c r="M30">
-        <v>0.1575896</v>
+        <v>0.16565844</v>
       </c>
       <c r="N30">
-        <v>1.0424104</v>
+        <v>1.03434156</v>
       </c>
       <c r="O30">
-        <v>0.250178496</v>
+        <v>0.2482419744</v>
       </c>
       <c r="P30">
-        <v>0.7922319040000001</v>
+        <v>0.7860995855999999</v>
       </c>
       <c r="Q30">
-        <v>1.312231904</v>
+        <v>1.3060995856</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1358913152361746</v>
+        <v>0.1369251464331689</v>
       </c>
       <c r="T30">
-        <v>1.519069002012146</v>
+        <v>1.536500881217707</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.614715691898451</v>
+        <v>7.24382047784586</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4156,22 +4156,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1091845739675499</v>
+        <v>0.1089723609650541</v>
       </c>
       <c r="C31">
-        <v>8.139965577076595</v>
+        <v>8.072086276732581</v>
       </c>
       <c r="D31">
-        <v>11.10976557707659</v>
+        <v>11.14708627673258</v>
       </c>
       <c r="E31">
-        <v>-1.559200000000001</v>
+        <v>-1.454000000000001</v>
       </c>
       <c r="F31">
-        <v>3.0508</v>
+        <v>3.156</v>
       </c>
       <c r="G31">
         <v>0.081</v>
@@ -4192,28 +4192,28 @@
         <v>1.2</v>
       </c>
       <c r="M31">
-        <v>0.16565844</v>
+        <v>0.1713708</v>
       </c>
       <c r="N31">
-        <v>1.03434156</v>
+        <v>1.0286292</v>
       </c>
       <c r="O31">
-        <v>0.2482419744</v>
+        <v>0.246871008</v>
       </c>
       <c r="P31">
-        <v>0.7860995855999999</v>
+        <v>0.781758192</v>
       </c>
       <c r="Q31">
-        <v>1.3060995856</v>
+        <v>1.301758192</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1369251464331689</v>
+        <v>0.137988515664363</v>
       </c>
       <c r="T31">
-        <v>1.536500881217707</v>
+        <v>1.554430814114854</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.243820477845861</v>
+        <v>7.002359795250999</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4238,22 +4238,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1089723609650541</v>
+        <v>0.1087601479625582</v>
       </c>
       <c r="C32">
-        <v>8.072086276732581</v>
+        <v>8.004458562129248</v>
       </c>
       <c r="D32">
-        <v>11.14708627673258</v>
+        <v>11.18465856212925</v>
       </c>
       <c r="E32">
-        <v>-1.454000000000001</v>
+        <v>-1.348800000000001</v>
       </c>
       <c r="F32">
-        <v>3.156</v>
+        <v>3.2612</v>
       </c>
       <c r="G32">
         <v>0.081</v>
@@ -4274,28 +4274,28 @@
         <v>1.2</v>
       </c>
       <c r="M32">
-        <v>0.1713708</v>
+        <v>0.17708316</v>
       </c>
       <c r="N32">
-        <v>1.0286292</v>
+        <v>1.02291684</v>
       </c>
       <c r="O32">
-        <v>0.246871008</v>
+        <v>0.2455000416</v>
       </c>
       <c r="P32">
-        <v>0.781758192</v>
+        <v>0.7774167984</v>
       </c>
       <c r="Q32">
-        <v>1.301758192</v>
+        <v>1.2974167984</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.137988515664363</v>
+        <v>0.1390827071921134</v>
       </c>
       <c r="T32">
-        <v>1.554430814114854</v>
+        <v>1.57288045521192</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.002359795250999</v>
+        <v>6.776477221210644</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4320,22 +4320,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1087601479625582</v>
+        <v>0.1085479349600624</v>
       </c>
       <c r="C33">
-        <v>8.004458562129248</v>
+        <v>7.93708498584934</v>
       </c>
       <c r="D33">
-        <v>11.18465856212925</v>
+        <v>11.22248498584934</v>
       </c>
       <c r="E33">
-        <v>-1.348800000000001</v>
+        <v>-1.2436</v>
       </c>
       <c r="F33">
-        <v>3.2612</v>
+        <v>3.3664</v>
       </c>
       <c r="G33">
         <v>0.081</v>
@@ -4356,28 +4356,28 @@
         <v>1.2</v>
       </c>
       <c r="M33">
-        <v>0.17708316</v>
+        <v>0.18279552</v>
       </c>
       <c r="N33">
-        <v>1.02291684</v>
+        <v>1.01720448</v>
       </c>
       <c r="O33">
-        <v>0.2455000416</v>
+        <v>0.2441290752</v>
       </c>
       <c r="P33">
-        <v>0.7774167984</v>
+        <v>0.7730754047999999</v>
       </c>
       <c r="Q33">
-        <v>1.2974167984</v>
+        <v>1.2930754048</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1390827071921134</v>
+        <v>0.1402090808236212</v>
       </c>
       <c r="T33">
-        <v>1.57288045521192</v>
+        <v>1.59187273281184</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.776477221210644</v>
+        <v>6.564712308047811</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4402,22 +4402,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1085479349600624</v>
+        <v>0.1083357219575666</v>
       </c>
       <c r="C34">
-        <v>7.93708498584934</v>
+        <v>7.869968135124045</v>
       </c>
       <c r="D34">
-        <v>11.22248498584934</v>
+        <v>11.26056813512405</v>
       </c>
       <c r="E34">
-        <v>-1.2436</v>
+        <v>-1.1384</v>
       </c>
       <c r="F34">
-        <v>3.3664</v>
+        <v>3.4716</v>
       </c>
       <c r="G34">
         <v>0.081</v>
@@ -4438,28 +4438,28 @@
         <v>1.2</v>
       </c>
       <c r="M34">
-        <v>0.18279552</v>
+        <v>0.18850788</v>
       </c>
       <c r="N34">
-        <v>1.01720448</v>
+        <v>1.01149212</v>
       </c>
       <c r="O34">
-        <v>0.2441290752</v>
+        <v>0.2427581088</v>
       </c>
       <c r="P34">
-        <v>0.7730754047999999</v>
+        <v>0.7687340112000001</v>
       </c>
       <c r="Q34">
-        <v>1.2930754048</v>
+        <v>1.2887340112</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1402090808236212</v>
+        <v>0.1413690775486068</v>
       </c>
       <c r="T34">
-        <v>1.59187273281184</v>
+        <v>1.611431944071459</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.564712308047811</v>
+        <v>6.365781632046363</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4484,22 +4484,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1083357219575666</v>
+        <v>0.1081235089550708</v>
       </c>
       <c r="C35">
-        <v>7.869968135124045</v>
+        <v>7.803110632422875</v>
       </c>
       <c r="D35">
-        <v>11.26056813512405</v>
+        <v>11.29891063242288</v>
       </c>
       <c r="E35">
-        <v>-1.1384</v>
+        <v>-1.0332</v>
       </c>
       <c r="F35">
-        <v>3.4716</v>
+        <v>3.5768</v>
       </c>
       <c r="G35">
         <v>0.081</v>
@@ -4520,28 +4520,28 @@
         <v>1.2</v>
       </c>
       <c r="M35">
-        <v>0.18850788</v>
+        <v>0.19422024</v>
       </c>
       <c r="N35">
-        <v>1.01149212</v>
+        <v>1.00577976</v>
       </c>
       <c r="O35">
-        <v>0.2427581088</v>
+        <v>0.2413871424</v>
       </c>
       <c r="P35">
-        <v>0.7687340112000001</v>
+        <v>0.7643926176</v>
       </c>
       <c r="Q35">
-        <v>1.2887340112</v>
+        <v>1.2843926176</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1413690775486068</v>
+        <v>0.1425642256895011</v>
       </c>
       <c r="T35">
-        <v>1.611431944071459</v>
+        <v>1.631583858702582</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.365781632046363</v>
+        <v>6.178552760515587</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4566,22 +4566,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1081235089550708</v>
+        <v>0.1081772959525749</v>
       </c>
       <c r="C36">
-        <v>7.803110632422875</v>
+        <v>7.68816775292313</v>
       </c>
       <c r="D36">
-        <v>11.29891063242288</v>
+        <v>11.28916775292313</v>
       </c>
       <c r="E36">
-        <v>-1.0332</v>
+        <v>-0.9279999999999999</v>
       </c>
       <c r="F36">
-        <v>3.5768</v>
+        <v>3.682</v>
       </c>
       <c r="G36">
         <v>0.081</v>
@@ -4602,45 +4602,45 @@
         <v>1.2</v>
       </c>
       <c r="M36">
-        <v>0.19422024</v>
+        <v>0.2036146</v>
       </c>
       <c r="N36">
-        <v>1.00577976</v>
+        <v>0.9963853999999999</v>
       </c>
       <c r="O36">
-        <v>0.2413871424</v>
+        <v>0.239132496</v>
       </c>
       <c r="P36">
-        <v>0.7643926176</v>
+        <v>0.7572529039999999</v>
       </c>
       <c r="Q36">
-        <v>1.2843926176</v>
+        <v>1.277252904</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1425642256895011</v>
+        <v>0.143796147619346</v>
       </c>
       <c r="T36">
-        <v>1.631583858702582</v>
+        <v>1.652355832245432</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.178552760515587</v>
+        <v>5.893487009281258</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4648,22 +4648,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1081772959525749</v>
+        <v>0.1079726829500791</v>
       </c>
       <c r="C37">
-        <v>7.68816775292313</v>
+        <v>7.620120894785439</v>
       </c>
       <c r="D37">
-        <v>11.28916775292313</v>
+        <v>11.32632089478544</v>
       </c>
       <c r="E37">
-        <v>-0.9279999999999999</v>
+        <v>-0.8228</v>
       </c>
       <c r="F37">
-        <v>3.682</v>
+        <v>3.7872</v>
       </c>
       <c r="G37">
         <v>0.081</v>
@@ -4684,28 +4684,28 @@
         <v>1.2</v>
       </c>
       <c r="M37">
-        <v>0.2036146</v>
+        <v>0.20943216</v>
       </c>
       <c r="N37">
-        <v>0.9963853999999999</v>
+        <v>0.99056784</v>
       </c>
       <c r="O37">
-        <v>0.239132496</v>
+        <v>0.2377362816</v>
       </c>
       <c r="P37">
-        <v>0.7572529039999999</v>
+        <v>0.7528315584</v>
       </c>
       <c r="Q37">
-        <v>1.277252904</v>
+        <v>1.2728315584</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.143796147619346</v>
+        <v>0.1450665671094986</v>
       </c>
       <c r="T37">
-        <v>1.652355832245432</v>
+        <v>1.673776929961496</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.893487009281258</v>
+        <v>5.729779036801224</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4730,22 +4730,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1079726829500791</v>
+        <v>0.1077680699475833</v>
       </c>
       <c r="C38">
-        <v>7.620120894785439</v>
+        <v>7.552319389324218</v>
       </c>
       <c r="D38">
-        <v>11.32632089478544</v>
+        <v>11.36371938932422</v>
       </c>
       <c r="E38">
-        <v>-0.8228000000000004</v>
+        <v>-0.7176000000000005</v>
       </c>
       <c r="F38">
-        <v>3.7872</v>
+        <v>3.8924</v>
       </c>
       <c r="G38">
         <v>0.081</v>
@@ -4766,28 +4766,28 @@
         <v>1.2</v>
       </c>
       <c r="M38">
-        <v>0.20943216</v>
+        <v>0.21524972</v>
       </c>
       <c r="N38">
-        <v>0.99056784</v>
+        <v>0.98475028</v>
       </c>
       <c r="O38">
-        <v>0.2377362816</v>
+        <v>0.2363400672</v>
       </c>
       <c r="P38">
-        <v>0.7528315584</v>
+        <v>0.7484102128</v>
       </c>
       <c r="Q38">
-        <v>1.2728315584</v>
+        <v>1.2684102128</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1450665671094986</v>
+        <v>0.1463773173771163</v>
       </c>
       <c r="T38">
-        <v>1.673776929961496</v>
+        <v>1.695878062525689</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.729779036801225</v>
+        <v>5.574920143914705</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4812,22 +4812,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1077680699475833</v>
+        <v>0.1075634569450874</v>
       </c>
       <c r="C39">
-        <v>7.552319389324218</v>
+        <v>7.484765674988521</v>
       </c>
       <c r="D39">
-        <v>11.36371938932422</v>
+        <v>11.40136567498852</v>
       </c>
       <c r="E39">
-        <v>-0.7176000000000005</v>
+        <v>-0.6124000000000005</v>
       </c>
       <c r="F39">
-        <v>3.8924</v>
+        <v>3.9976</v>
       </c>
       <c r="G39">
         <v>0.081</v>
@@ -4848,28 +4848,28 @@
         <v>1.2</v>
       </c>
       <c r="M39">
-        <v>0.21524972</v>
+        <v>0.22106728</v>
       </c>
       <c r="N39">
-        <v>0.98475028</v>
+        <v>0.97893272</v>
       </c>
       <c r="O39">
-        <v>0.2363400672</v>
+        <v>0.2349438528</v>
       </c>
       <c r="P39">
-        <v>0.7484102128</v>
+        <v>0.7439888672</v>
       </c>
       <c r="Q39">
-        <v>1.2684102128</v>
+        <v>1.2639888672</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1463773173771163</v>
+        <v>0.1477303499114313</v>
       </c>
       <c r="T39">
-        <v>1.695878062525689</v>
+        <v>1.718692134850017</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.574920143914705</v>
+        <v>5.428211719074844</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4894,22 +4894,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1075634569450874</v>
+        <v>0.1073588439425916</v>
       </c>
       <c r="C40">
-        <v>7.484765674988521</v>
+        <v>7.417462222647664</v>
       </c>
       <c r="D40">
-        <v>11.40136567498852</v>
+        <v>11.43926222264767</v>
       </c>
       <c r="E40">
-        <v>-0.6124000000000005</v>
+        <v>-0.5072000000000001</v>
       </c>
       <c r="F40">
-        <v>3.9976</v>
+        <v>4.1028</v>
       </c>
       <c r="G40">
         <v>0.081</v>
@@ -4930,28 +4930,28 @@
         <v>1.2</v>
       </c>
       <c r="M40">
-        <v>0.22106728</v>
+        <v>0.22688484</v>
       </c>
       <c r="N40">
-        <v>0.97893272</v>
+        <v>0.9731151599999999</v>
       </c>
       <c r="O40">
-        <v>0.2349438528</v>
+        <v>0.2335476384</v>
       </c>
       <c r="P40">
-        <v>0.7439888672</v>
+        <v>0.7395675215999999</v>
       </c>
       <c r="Q40">
-        <v>1.2639888672</v>
+        <v>1.2595675216</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1477303499114313</v>
+        <v>0.149127744168183</v>
       </c>
       <c r="T40">
-        <v>1.718692134850017</v>
+        <v>1.742254209545635</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.428211719074844</v>
+        <v>5.289026803201129</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1073588439425916</v>
+        <v>0.1071542309400958</v>
       </c>
       <c r="C41">
-        <v>7.417462222647664</v>
+        <v>7.350411536131819</v>
       </c>
       <c r="D41">
-        <v>11.43926222264767</v>
+        <v>11.47741153613182</v>
       </c>
       <c r="E41">
-        <v>-0.5072000000000001</v>
+        <v>-0.4020000000000001</v>
       </c>
       <c r="F41">
-        <v>4.1028</v>
+        <v>4.208</v>
       </c>
       <c r="G41">
         <v>0.081</v>
@@ -5012,28 +5012,28 @@
         <v>1.2</v>
       </c>
       <c r="M41">
-        <v>0.22688484</v>
+        <v>0.2327024</v>
       </c>
       <c r="N41">
-        <v>0.9731151599999999</v>
+        <v>0.9672976</v>
       </c>
       <c r="O41">
-        <v>0.2335476384</v>
+        <v>0.232151424</v>
       </c>
       <c r="P41">
-        <v>0.7395675215999999</v>
+        <v>0.735146176</v>
       </c>
       <c r="Q41">
-        <v>1.2595675216</v>
+        <v>1.255146176</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.149127744168183</v>
+        <v>0.150571718233493</v>
       </c>
       <c r="T41">
-        <v>1.742254209545635</v>
+        <v>1.766601686731106</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.289026803201129</v>
+        <v>5.156801133121101</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5058,22 +5058,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1071542309400958</v>
+        <v>0.1069496179375999</v>
       </c>
       <c r="C42">
-        <v>7.350411536131819</v>
+        <v>7.28361615278347</v>
       </c>
       <c r="D42">
-        <v>11.47741153613182</v>
+        <v>11.51581615278347</v>
       </c>
       <c r="E42">
-        <v>-0.4020000000000001</v>
+        <v>-0.2968000000000002</v>
       </c>
       <c r="F42">
-        <v>4.208</v>
+        <v>4.3132</v>
       </c>
       <c r="G42">
         <v>0.081</v>
@@ -5094,28 +5094,28 @@
         <v>1.2</v>
       </c>
       <c r="M42">
-        <v>0.2327024</v>
+        <v>0.23851996</v>
       </c>
       <c r="N42">
-        <v>0.9672976</v>
+        <v>0.96148004</v>
       </c>
       <c r="O42">
-        <v>0.232151424</v>
+        <v>0.2307552096</v>
       </c>
       <c r="P42">
-        <v>0.735146176</v>
+        <v>0.7307248304</v>
       </c>
       <c r="Q42">
-        <v>1.255146176</v>
+        <v>1.2507248304</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.150571718233493</v>
+        <v>0.1520646405722033</v>
       </c>
       <c r="T42">
-        <v>1.766601686731106</v>
+        <v>1.791774502126255</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.156801133121101</v>
+        <v>5.031025495727905</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5140,22 +5140,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1069496179375999</v>
+        <v>0.1067450049351041</v>
       </c>
       <c r="C43">
-        <v>7.28361615278347</v>
+        <v>7.217078644019955</v>
       </c>
       <c r="D43">
-        <v>11.51581615278347</v>
+        <v>11.55447864401996</v>
       </c>
       <c r="E43">
-        <v>-0.2968000000000002</v>
+        <v>-0.1916000000000002</v>
       </c>
       <c r="F43">
-        <v>4.3132</v>
+        <v>4.4184</v>
       </c>
       <c r="G43">
         <v>0.081</v>
@@ -5176,28 +5176,28 @@
         <v>1.2</v>
       </c>
       <c r="M43">
-        <v>0.23851996</v>
+        <v>0.24433752</v>
       </c>
       <c r="N43">
-        <v>0.96148004</v>
+        <v>0.95566248</v>
       </c>
       <c r="O43">
-        <v>0.2307552096</v>
+        <v>0.2293589952</v>
       </c>
       <c r="P43">
-        <v>0.7307248304</v>
+        <v>0.7263034848</v>
       </c>
       <c r="Q43">
-        <v>1.2507248304</v>
+        <v>1.2463034848</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1520646405722033</v>
+        <v>0.1536090429915588</v>
       </c>
       <c r="T43">
-        <v>1.791774502126255</v>
+        <v>1.817815345638477</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.031025495727905</v>
+        <v>4.91123917440105</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5222,22 +5222,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1067450049351041</v>
+        <v>0.1065403919326083</v>
       </c>
       <c r="C44">
-        <v>7.217078644019952</v>
+        <v>7.150801615907426</v>
       </c>
       <c r="D44">
-        <v>11.55447864401995</v>
+        <v>11.59340161590743</v>
       </c>
       <c r="E44">
-        <v>-0.1916000000000011</v>
+        <v>-0.08640000000000025</v>
       </c>
       <c r="F44">
-        <v>4.418399999999999</v>
+        <v>4.5236</v>
       </c>
       <c r="G44">
         <v>0.081</v>
@@ -5258,28 +5258,28 @@
         <v>1.2</v>
       </c>
       <c r="M44">
-        <v>0.24433752</v>
+        <v>0.25015508</v>
       </c>
       <c r="N44">
-        <v>0.95566248</v>
+        <v>0.9498449199999999</v>
       </c>
       <c r="O44">
-        <v>0.2293589952</v>
+        <v>0.2279627808</v>
       </c>
       <c r="P44">
-        <v>0.7263034848</v>
+        <v>0.7218821391999999</v>
       </c>
       <c r="Q44">
-        <v>1.2463034848</v>
+        <v>1.2418821392</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1536090429915588</v>
+        <v>0.1552076349694882</v>
       </c>
       <c r="T44">
-        <v>1.817815345638477</v>
+        <v>1.844769902958146</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.91123917440105</v>
+        <v>4.797024309880094</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5304,22 +5304,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1065403919326083</v>
+        <v>0.1063357789301125</v>
       </c>
       <c r="C45">
-        <v>7.150801615907426</v>
+        <v>7.084787709746397</v>
       </c>
       <c r="D45">
-        <v>11.59340161590743</v>
+        <v>11.6325877097464</v>
       </c>
       <c r="E45">
-        <v>-0.08640000000000025</v>
+        <v>0.01879999999999971</v>
       </c>
       <c r="F45">
-        <v>4.5236</v>
+        <v>4.6288</v>
       </c>
       <c r="G45">
         <v>0.081</v>
@@ -5340,28 +5340,28 @@
         <v>1.2</v>
       </c>
       <c r="M45">
-        <v>0.25015508</v>
+        <v>0.25597264</v>
       </c>
       <c r="N45">
-        <v>0.9498449199999999</v>
+        <v>0.94402736</v>
       </c>
       <c r="O45">
-        <v>0.2279627808</v>
+        <v>0.2265665664</v>
       </c>
       <c r="P45">
-        <v>0.7218821391999999</v>
+        <v>0.7174607936</v>
       </c>
       <c r="Q45">
-        <v>1.2418821392</v>
+        <v>1.2374607936</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1552076349694882</v>
+        <v>0.156863319518058</v>
       </c>
       <c r="T45">
-        <v>1.844769902958146</v>
+        <v>1.872687123039232</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.797024309880094</v>
+        <v>4.688001030110092</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5386,22 +5386,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1063357789301125</v>
+        <v>0.1061311659276166</v>
       </c>
       <c r="C46">
-        <v>7.084787709746397</v>
+        <v>7.019039602669253</v>
       </c>
       <c r="D46">
-        <v>11.6325877097464</v>
+        <v>11.67203960266925</v>
       </c>
       <c r="E46">
-        <v>0.01879999999999971</v>
+        <v>0.1239999999999997</v>
       </c>
       <c r="F46">
-        <v>4.6288</v>
+        <v>4.734</v>
       </c>
       <c r="G46">
         <v>0.081</v>
@@ -5422,28 +5422,28 @@
         <v>1.2</v>
       </c>
       <c r="M46">
-        <v>0.25597264</v>
+        <v>0.2617902</v>
       </c>
       <c r="N46">
-        <v>0.94402736</v>
+        <v>0.9382097999999999</v>
       </c>
       <c r="O46">
-        <v>0.2265665664</v>
+        <v>0.225170352</v>
       </c>
       <c r="P46">
-        <v>0.7174607936</v>
+        <v>0.713039448</v>
       </c>
       <c r="Q46">
-        <v>1.2374607936</v>
+        <v>1.233039448</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.156863319518058</v>
+        <v>0.1585792107774848</v>
       </c>
       <c r="T46">
-        <v>1.872687123039232</v>
+        <v>1.90161951475963</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.688001030110092</v>
+        <v>4.583823229440979</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5468,22 +5468,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1061311659276166</v>
+        <v>0.1068005529251208</v>
       </c>
       <c r="C47">
-        <v>7.019039602669253</v>
+        <v>6.785756967845089</v>
       </c>
       <c r="D47">
-        <v>11.67203960266925</v>
+        <v>11.54395696784509</v>
       </c>
       <c r="E47">
-        <v>0.1239999999999997</v>
+        <v>0.2291999999999996</v>
       </c>
       <c r="F47">
-        <v>4.734</v>
+        <v>4.8392</v>
       </c>
       <c r="G47">
         <v>0.081</v>
@@ -5504,45 +5504,45 @@
         <v>1.2</v>
       </c>
       <c r="M47">
-        <v>0.2617902</v>
+        <v>0.27970576</v>
       </c>
       <c r="N47">
-        <v>0.9382097999999999</v>
+        <v>0.9202942399999999</v>
       </c>
       <c r="O47">
-        <v>0.225170352</v>
+        <v>0.2208706176</v>
       </c>
       <c r="P47">
-        <v>0.713039448</v>
+        <v>0.6994236223999999</v>
       </c>
       <c r="Q47">
-        <v>1.233039448</v>
+        <v>1.2194236224</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1585792107774848</v>
+        <v>0.1603586535650385</v>
       </c>
       <c r="T47">
-        <v>1.90161951475963</v>
+        <v>1.931623476543746</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.583823229440979</v>
+        <v>4.290222696879749</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5550,22 +5550,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1068005529251208</v>
+        <v>0.106614939922625</v>
       </c>
       <c r="C48">
-        <v>6.785756967845089</v>
+        <v>6.715790226583986</v>
       </c>
       <c r="D48">
-        <v>11.54395696784509</v>
+        <v>11.57919022658399</v>
       </c>
       <c r="E48">
-        <v>0.2291999999999996</v>
+        <v>0.3343999999999996</v>
       </c>
       <c r="F48">
-        <v>4.8392</v>
+        <v>4.9444</v>
       </c>
       <c r="G48">
         <v>0.081</v>
@@ -5586,28 +5586,28 @@
         <v>1.2</v>
       </c>
       <c r="M48">
-        <v>0.27970576</v>
+        <v>0.28578632</v>
       </c>
       <c r="N48">
-        <v>0.9202942399999999</v>
+        <v>0.9142136799999999</v>
       </c>
       <c r="O48">
-        <v>0.2208706176</v>
+        <v>0.2194112832</v>
       </c>
       <c r="P48">
-        <v>0.6994236223999999</v>
+        <v>0.6948023967999999</v>
       </c>
       <c r="Q48">
-        <v>1.2194236224</v>
+        <v>1.2148023968</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1603586535650385</v>
+        <v>0.1622052451370282</v>
       </c>
       <c r="T48">
-        <v>1.931623476543746</v>
+        <v>1.962759663300848</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.290222696879749</v>
+        <v>4.198941362903584</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5632,22 +5632,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.106614939922625</v>
+        <v>0.1064293269201291</v>
       </c>
       <c r="C49">
-        <v>6.715790226583986</v>
+        <v>6.646039214286883</v>
       </c>
       <c r="D49">
-        <v>11.57919022658399</v>
+        <v>11.61463921428688</v>
       </c>
       <c r="E49">
-        <v>0.3343999999999996</v>
+        <v>0.4395999999999995</v>
       </c>
       <c r="F49">
-        <v>4.9444</v>
+        <v>5.0496</v>
       </c>
       <c r="G49">
         <v>0.081</v>
@@ -5668,28 +5668,28 @@
         <v>1.2</v>
       </c>
       <c r="M49">
-        <v>0.28578632</v>
+        <v>0.29186688</v>
       </c>
       <c r="N49">
-        <v>0.9142136799999999</v>
+        <v>0.90813312</v>
       </c>
       <c r="O49">
-        <v>0.2194112832</v>
+        <v>0.2179519488</v>
       </c>
       <c r="P49">
-        <v>0.6948023967999999</v>
+        <v>0.6901811712</v>
       </c>
       <c r="Q49">
-        <v>1.2148023968</v>
+        <v>1.2101811712</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1622052451370282</v>
+        <v>0.1641228594617868</v>
       </c>
       <c r="T49">
-        <v>1.962759663300848</v>
+        <v>1.995093395702454</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.198941362903584</v>
+        <v>4.111463417843094</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5714,22 +5714,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1064293269201291</v>
+        <v>0.1062437139176333</v>
       </c>
       <c r="C50">
-        <v>6.646039214286883</v>
+        <v>6.576505918361475</v>
       </c>
       <c r="D50">
-        <v>11.61463921428688</v>
+        <v>11.65030591836148</v>
       </c>
       <c r="E50">
-        <v>0.4395999999999995</v>
+        <v>0.5447999999999995</v>
       </c>
       <c r="F50">
-        <v>5.0496</v>
+        <v>5.1548</v>
       </c>
       <c r="G50">
         <v>0.081</v>
@@ -5750,28 +5750,28 @@
         <v>1.2</v>
       </c>
       <c r="M50">
-        <v>0.29186688</v>
+        <v>0.29794744</v>
       </c>
       <c r="N50">
-        <v>0.90813312</v>
+        <v>0.90205256</v>
       </c>
       <c r="O50">
-        <v>0.2179519488</v>
+        <v>0.2164926144</v>
       </c>
       <c r="P50">
-        <v>0.6901811712</v>
+        <v>0.6855599456</v>
       </c>
       <c r="Q50">
-        <v>1.2101811712</v>
+        <v>1.2055599456</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1641228594617868</v>
+        <v>0.1661156743483006</v>
       </c>
       <c r="T50">
-        <v>1.995093395702454</v>
+        <v>2.028695117610005</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.111463417843094</v>
+        <v>4.027556001152417</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5796,22 +5796,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1062437139176333</v>
+        <v>0.1073881009151375</v>
       </c>
       <c r="C51">
-        <v>6.576505918361475</v>
+        <v>6.254828085601384</v>
       </c>
       <c r="D51">
-        <v>11.65030591836148</v>
+        <v>11.43382808560138</v>
       </c>
       <c r="E51">
-        <v>0.5447999999999995</v>
+        <v>0.6499999999999995</v>
       </c>
       <c r="F51">
-        <v>5.1548</v>
+        <v>5.26</v>
       </c>
       <c r="G51">
         <v>0.081</v>
@@ -5832,45 +5832,45 @@
         <v>1.2</v>
       </c>
       <c r="M51">
-        <v>0.29794744</v>
+        <v>0.322438</v>
       </c>
       <c r="N51">
-        <v>0.90205256</v>
+        <v>0.877562</v>
       </c>
       <c r="O51">
-        <v>0.2164926144</v>
+        <v>0.21061488</v>
       </c>
       <c r="P51">
-        <v>0.6855599456</v>
+        <v>0.66694712</v>
       </c>
       <c r="Q51">
-        <v>1.2055599456</v>
+        <v>1.18694712</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1661156743483006</v>
+        <v>0.168188201830275</v>
       </c>
       <c r="T51">
-        <v>2.028695117610005</v>
+        <v>2.063640908393859</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.027556001152417</v>
+        <v>3.721645711733728</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5878,22 +5878,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1073881009151375</v>
+        <v>0.1072290879126417</v>
       </c>
       <c r="C52">
-        <v>6.254828085601384</v>
+        <v>6.179225258466756</v>
       </c>
       <c r="D52">
-        <v>11.43382808560138</v>
+        <v>11.46342525846676</v>
       </c>
       <c r="E52">
-        <v>0.6499999999999995</v>
+        <v>0.7551999999999994</v>
       </c>
       <c r="F52">
-        <v>5.26</v>
+        <v>5.3652</v>
       </c>
       <c r="G52">
         <v>0.081</v>
@@ -5914,28 +5914,28 @@
         <v>1.2</v>
       </c>
       <c r="M52">
-        <v>0.322438</v>
+        <v>0.32888676</v>
       </c>
       <c r="N52">
-        <v>0.877562</v>
+        <v>0.8711132399999999</v>
       </c>
       <c r="O52">
-        <v>0.21061488</v>
+        <v>0.2090671776</v>
       </c>
       <c r="P52">
-        <v>0.66694712</v>
+        <v>0.6620460624</v>
       </c>
       <c r="Q52">
-        <v>1.18694712</v>
+        <v>1.1820460624</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.168188201830275</v>
+        <v>0.1703453222706973</v>
       </c>
       <c r="T52">
-        <v>2.063640908393859</v>
+        <v>2.100013057985216</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.721645711733728</v>
+        <v>3.648672266405616</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5960,22 +5960,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1072290879126417</v>
+        <v>0.1070700749101458</v>
       </c>
       <c r="C53">
-        <v>6.179225258466756</v>
+        <v>6.103776057236116</v>
       </c>
       <c r="D53">
-        <v>11.46342525846676</v>
+        <v>11.49317605723612</v>
       </c>
       <c r="E53">
-        <v>0.7551999999999994</v>
+        <v>0.8603999999999994</v>
       </c>
       <c r="F53">
-        <v>5.3652</v>
+        <v>5.4704</v>
       </c>
       <c r="G53">
         <v>0.081</v>
@@ -5996,28 +5996,28 @@
         <v>1.2</v>
       </c>
       <c r="M53">
-        <v>0.32888676</v>
+        <v>0.33533552</v>
       </c>
       <c r="N53">
-        <v>0.8711132399999999</v>
+        <v>0.86466448</v>
       </c>
       <c r="O53">
-        <v>0.2090671776</v>
+        <v>0.2075194752</v>
       </c>
       <c r="P53">
-        <v>0.6620460624</v>
+        <v>0.6571450048</v>
       </c>
       <c r="Q53">
-        <v>1.1820460624</v>
+        <v>1.1771450048</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1703453222706973</v>
+        <v>0.1725923227294705</v>
       </c>
       <c r="T53">
-        <v>2.100013057985216</v>
+        <v>2.137900713809547</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.648672266405616</v>
+        <v>3.578505492051662</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6042,22 +6042,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1070700749101458</v>
+        <v>0.10691106190765</v>
       </c>
       <c r="C54">
-        <v>6.103776057236116</v>
+        <v>6.028481681128497</v>
       </c>
       <c r="D54">
-        <v>11.49317605723612</v>
+        <v>11.5230816811285</v>
       </c>
       <c r="E54">
-        <v>0.8603999999999994</v>
+        <v>0.9655999999999993</v>
       </c>
       <c r="F54">
-        <v>5.4704</v>
+        <v>5.5756</v>
       </c>
       <c r="G54">
         <v>0.081</v>
@@ -6078,28 +6078,28 @@
         <v>1.2</v>
       </c>
       <c r="M54">
-        <v>0.33533552</v>
+        <v>0.34178428</v>
       </c>
       <c r="N54">
-        <v>0.86466448</v>
+        <v>0.85821572</v>
       </c>
       <c r="O54">
-        <v>0.2075194752</v>
+        <v>0.2059717728</v>
       </c>
       <c r="P54">
-        <v>0.6571450048</v>
+        <v>0.6522439472</v>
       </c>
       <c r="Q54">
-        <v>1.1771450048</v>
+        <v>1.1722439472</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1725923227294705</v>
+        <v>0.1749349402290425</v>
       </c>
       <c r="T54">
-        <v>2.137900713809547</v>
+        <v>2.177400610307253</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.578505492051662</v>
+        <v>3.510986520503518</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6124,22 +6124,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.10691106190765</v>
+        <v>0.1079011689051542</v>
       </c>
       <c r="C55">
-        <v>6.028481681128497</v>
+        <v>5.739563982952441</v>
       </c>
       <c r="D55">
-        <v>11.5230816811285</v>
+        <v>11.33936398295244</v>
       </c>
       <c r="E55">
-        <v>0.9655999999999993</v>
+        <v>1.0708</v>
       </c>
       <c r="F55">
-        <v>5.5756</v>
+        <v>5.680800000000001</v>
       </c>
       <c r="G55">
         <v>0.081</v>
@@ -6160,45 +6160,45 @@
         <v>1.2</v>
       </c>
       <c r="M55">
-        <v>0.34178428</v>
+        <v>0.3641392800000001</v>
       </c>
       <c r="N55">
-        <v>0.85821572</v>
+        <v>0.8358607199999999</v>
       </c>
       <c r="O55">
-        <v>0.2059717728</v>
+        <v>0.2006065728</v>
       </c>
       <c r="P55">
-        <v>0.6522439472</v>
+        <v>0.6352541472</v>
       </c>
       <c r="Q55">
-        <v>1.1722439472</v>
+        <v>1.1552541472</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1749349402290425</v>
+        <v>0.1773794106633786</v>
       </c>
       <c r="T55">
-        <v>2.177400610307253</v>
+        <v>2.218617893609208</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.510986520503518</v>
+        <v>3.295442337338613</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6206,22 +6206,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1079011689051542</v>
+        <v>0.1077634359026583</v>
       </c>
       <c r="C56">
-        <v>5.739563982952441</v>
+        <v>5.659569245136717</v>
       </c>
       <c r="D56">
-        <v>11.33936398295244</v>
+        <v>11.36456924513672</v>
       </c>
       <c r="E56">
-        <v>1.0708</v>
+        <v>1.176</v>
       </c>
       <c r="F56">
-        <v>5.680800000000001</v>
+        <v>5.786</v>
       </c>
       <c r="G56">
         <v>0.081</v>
@@ -6242,28 +6242,28 @@
         <v>1.2</v>
       </c>
       <c r="M56">
-        <v>0.3641392800000001</v>
+        <v>0.3708826000000001</v>
       </c>
       <c r="N56">
-        <v>0.8358607199999999</v>
+        <v>0.8291173999999999</v>
       </c>
       <c r="O56">
-        <v>0.2006065728</v>
+        <v>0.198988176</v>
       </c>
       <c r="P56">
-        <v>0.6352541472</v>
+        <v>0.6301292239999999</v>
       </c>
       <c r="Q56">
-        <v>1.1552541472</v>
+        <v>1.150129224</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1773794106633786</v>
+        <v>0.1799325242281296</v>
       </c>
       <c r="T56">
-        <v>2.218617893609208</v>
+        <v>2.261667056169027</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.295442337338613</v>
+        <v>3.235525203932457</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6288,22 +6288,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1077634359026583</v>
+        <v>0.1076257029001625</v>
       </c>
       <c r="C57">
-        <v>5.659569245136717</v>
+        <v>5.579686810013125</v>
       </c>
       <c r="D57">
-        <v>11.36456924513672</v>
+        <v>11.38988681001313</v>
       </c>
       <c r="E57">
-        <v>1.176</v>
+        <v>1.2812</v>
       </c>
       <c r="F57">
-        <v>5.786</v>
+        <v>5.8912</v>
       </c>
       <c r="G57">
         <v>0.081</v>
@@ -6324,28 +6324,28 @@
         <v>1.2</v>
       </c>
       <c r="M57">
-        <v>0.3708826000000001</v>
+        <v>0.3776259200000001</v>
       </c>
       <c r="N57">
-        <v>0.8291173999999999</v>
+        <v>0.8223740799999999</v>
       </c>
       <c r="O57">
-        <v>0.198988176</v>
+        <v>0.1973697792</v>
       </c>
       <c r="P57">
-        <v>0.6301292239999999</v>
+        <v>0.6250043007999999</v>
       </c>
       <c r="Q57">
-        <v>1.150129224</v>
+        <v>1.1450043008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1799325242281296</v>
+        <v>0.1826016884094602</v>
       </c>
       <c r="T57">
-        <v>2.261667056169027</v>
+        <v>2.306672998845201</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.235525203932457</v>
+        <v>3.177747968147949</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6370,22 +6370,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1076257029001625</v>
+        <v>0.1074879698976667</v>
       </c>
       <c r="C58">
-        <v>5.579686810013125</v>
+        <v>5.499917429808737</v>
       </c>
       <c r="D58">
-        <v>11.38988681001313</v>
+        <v>11.41531742980874</v>
       </c>
       <c r="E58">
-        <v>1.2812</v>
+        <v>1.3864</v>
       </c>
       <c r="F58">
-        <v>5.8912</v>
+        <v>5.9964</v>
       </c>
       <c r="G58">
         <v>0.081</v>
@@ -6406,28 +6406,28 @@
         <v>1.2</v>
       </c>
       <c r="M58">
-        <v>0.3776259200000001</v>
+        <v>0.3843692400000001</v>
       </c>
       <c r="N58">
-        <v>0.8223740799999999</v>
+        <v>0.8156307599999999</v>
       </c>
       <c r="O58">
-        <v>0.1973697792</v>
+        <v>0.1957513824</v>
       </c>
       <c r="P58">
-        <v>0.6250043007999999</v>
+        <v>0.6198793775999999</v>
       </c>
       <c r="Q58">
-        <v>1.1450043008</v>
+        <v>1.1398793776</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1826016884094602</v>
+        <v>0.1853949997620155</v>
       </c>
       <c r="T58">
-        <v>2.306672998845201</v>
+        <v>2.353772241180733</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.177747968147949</v>
+        <v>3.121998003794476</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6452,22 +6452,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1074879698976667</v>
+        <v>0.1073502368951708</v>
       </c>
       <c r="C59">
-        <v>5.499917429808737</v>
+        <v>5.42026186348376</v>
       </c>
       <c r="D59">
-        <v>11.41531742980874</v>
+        <v>11.44086186348376</v>
       </c>
       <c r="E59">
-        <v>1.3864</v>
+        <v>1.4916</v>
       </c>
       <c r="F59">
-        <v>5.9964</v>
+        <v>6.1016</v>
       </c>
       <c r="G59">
         <v>0.081</v>
@@ -6488,28 +6488,28 @@
         <v>1.2</v>
       </c>
       <c r="M59">
-        <v>0.3843692400000001</v>
+        <v>0.3911125600000001</v>
       </c>
       <c r="N59">
-        <v>0.8156307599999999</v>
+        <v>0.8088874399999999</v>
       </c>
       <c r="O59">
-        <v>0.1957513824</v>
+        <v>0.1941329856</v>
       </c>
       <c r="P59">
-        <v>0.6198793775999999</v>
+        <v>0.6147544543999999</v>
       </c>
       <c r="Q59">
-        <v>1.1398793776</v>
+        <v>1.1347544544</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1853949997620155</v>
+        <v>0.188321325940883</v>
       </c>
       <c r="T59">
-        <v>2.353772241180733</v>
+        <v>2.403114304579861</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.121998003794476</v>
+        <v>3.068170452004916</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6534,22 +6534,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1073502368951708</v>
+        <v>0.107212503892675</v>
       </c>
       <c r="C60">
-        <v>5.420261863483761</v>
+        <v>5.34072087680703</v>
       </c>
       <c r="D60">
-        <v>11.44086186348376</v>
+        <v>11.46652087680703</v>
       </c>
       <c r="E60">
-        <v>1.491599999999999</v>
+        <v>1.596799999999999</v>
       </c>
       <c r="F60">
-        <v>6.101599999999999</v>
+        <v>6.206799999999999</v>
       </c>
       <c r="G60">
         <v>0.081</v>
@@ -6570,28 +6570,28 @@
         <v>1.2</v>
       </c>
       <c r="M60">
-        <v>0.39111256</v>
+        <v>0.39785588</v>
       </c>
       <c r="N60">
-        <v>0.8088874399999999</v>
+        <v>0.8021441199999999</v>
       </c>
       <c r="O60">
-        <v>0.1941329856</v>
+        <v>0.1925145888</v>
       </c>
       <c r="P60">
-        <v>0.6147544543999999</v>
+        <v>0.6096295312</v>
       </c>
       <c r="Q60">
-        <v>1.1347544544</v>
+        <v>1.1296295312</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.188321325940883</v>
+        <v>0.1913903997382317</v>
       </c>
       <c r="T60">
-        <v>2.403114304579861</v>
+        <v>2.454863297900898</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.068170452004916</v>
+        <v>3.016167562987884</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6616,22 +6616,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.107212503892675</v>
+        <v>0.1106315708901792</v>
       </c>
       <c r="C61">
-        <v>5.34072087680703</v>
+        <v>4.630803104774424</v>
       </c>
       <c r="D61">
-        <v>11.46652087680703</v>
+        <v>10.86180310477442</v>
       </c>
       <c r="E61">
-        <v>1.596799999999999</v>
+        <v>1.701999999999999</v>
       </c>
       <c r="F61">
-        <v>6.206799999999999</v>
+        <v>6.311999999999999</v>
       </c>
       <c r="G61">
         <v>0.081</v>
@@ -6652,45 +6652,45 @@
         <v>1.2</v>
       </c>
       <c r="M61">
-        <v>0.39785588</v>
+        <v>0.4538328</v>
       </c>
       <c r="N61">
-        <v>0.8021441199999999</v>
+        <v>0.7461671999999999</v>
       </c>
       <c r="O61">
-        <v>0.1925145888</v>
+        <v>0.179080128</v>
       </c>
       <c r="P61">
-        <v>0.6096295312</v>
+        <v>0.567087072</v>
       </c>
       <c r="Q61">
-        <v>1.1296295312</v>
+        <v>1.087087072</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1913903997382317</v>
+        <v>0.1946129272254479</v>
       </c>
       <c r="T61">
-        <v>2.454863297900898</v>
+        <v>2.509199740887987</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.016167562987884</v>
+        <v>2.644145597233166</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6698,22 +6698,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1106315708901792</v>
+        <v>0.1105531178876833</v>
       </c>
       <c r="C62">
-        <v>4.630803104774424</v>
+        <v>4.538762950877373</v>
       </c>
       <c r="D62">
-        <v>10.86180310477442</v>
+        <v>10.87496295087737</v>
       </c>
       <c r="E62">
-        <v>1.701999999999999</v>
+        <v>1.807199999999999</v>
       </c>
       <c r="F62">
-        <v>6.311999999999999</v>
+        <v>6.417199999999999</v>
       </c>
       <c r="G62">
         <v>0.081</v>
@@ -6734,28 +6734,28 @@
         <v>1.2</v>
       </c>
       <c r="M62">
-        <v>0.4538328</v>
+        <v>0.46139668</v>
       </c>
       <c r="N62">
-        <v>0.7461671999999999</v>
+        <v>0.73860332</v>
       </c>
       <c r="O62">
-        <v>0.179080128</v>
+        <v>0.1772647968</v>
       </c>
       <c r="P62">
-        <v>0.567087072</v>
+        <v>0.5613385232</v>
       </c>
       <c r="Q62">
-        <v>1.087087072</v>
+        <v>1.0813385232</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1946129272254479</v>
+        <v>0.1980007125325214</v>
       </c>
       <c r="T62">
-        <v>2.509199740887987</v>
+        <v>2.566322668130824</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.644145597233166</v>
+        <v>2.600798948098196</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6780,22 +6780,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1105531178876833</v>
+        <v>0.1104746648851875</v>
       </c>
       <c r="C63">
-        <v>4.538762950877373</v>
+        <v>4.446754723838881</v>
       </c>
       <c r="D63">
-        <v>10.87496295087737</v>
+        <v>10.88815472383888</v>
       </c>
       <c r="E63">
-        <v>1.807199999999999</v>
+        <v>1.912399999999999</v>
       </c>
       <c r="F63">
-        <v>6.417199999999999</v>
+        <v>6.522399999999999</v>
       </c>
       <c r="G63">
         <v>0.081</v>
@@ -6816,28 +6816,28 @@
         <v>1.2</v>
       </c>
       <c r="M63">
-        <v>0.46139668</v>
+        <v>0.46896056</v>
       </c>
       <c r="N63">
-        <v>0.73860332</v>
+        <v>0.73103944</v>
       </c>
       <c r="O63">
-        <v>0.1772647968</v>
+        <v>0.1754494656</v>
       </c>
       <c r="P63">
-        <v>0.5613385232</v>
+        <v>0.5555899744</v>
       </c>
       <c r="Q63">
-        <v>1.0813385232</v>
+        <v>1.0755899744</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1980007125325214</v>
+        <v>0.2015668023294409</v>
       </c>
       <c r="T63">
-        <v>2.566322668130824</v>
+        <v>2.626452065228547</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.600798948098196</v>
+        <v>2.55885057796758</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6862,22 +6862,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1104746648851875</v>
+        <v>0.1103962118826917</v>
       </c>
       <c r="C64">
-        <v>4.446754723838881</v>
+        <v>4.354778539985804</v>
       </c>
       <c r="D64">
-        <v>10.88815472383888</v>
+        <v>10.9013785399858</v>
       </c>
       <c r="E64">
-        <v>1.912399999999999</v>
+        <v>2.0176</v>
       </c>
       <c r="F64">
-        <v>6.522399999999999</v>
+        <v>6.6276</v>
       </c>
       <c r="G64">
         <v>0.081</v>
@@ -6898,28 +6898,28 @@
         <v>1.2</v>
       </c>
       <c r="M64">
-        <v>0.46896056</v>
+        <v>0.47652444</v>
       </c>
       <c r="N64">
-        <v>0.73103944</v>
+        <v>0.7234755599999999</v>
       </c>
       <c r="O64">
-        <v>0.1754494656</v>
+        <v>0.1736341344</v>
       </c>
       <c r="P64">
-        <v>0.5555899744</v>
+        <v>0.5498414255999999</v>
       </c>
       <c r="Q64">
-        <v>1.0755899744</v>
+        <v>1.0698414256</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2015668023294409</v>
+        <v>0.2053256537370046</v>
       </c>
       <c r="T64">
-        <v>2.626452065228547</v>
+        <v>2.689831700007228</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.55885057796758</v>
+        <v>2.518233902126824</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6944,22 +6944,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1103962118826917</v>
+        <v>0.1122147188801959</v>
       </c>
       <c r="C65">
-        <v>4.354778539985804</v>
+        <v>3.951086978301013</v>
       </c>
       <c r="D65">
-        <v>10.9013785399858</v>
+        <v>10.60288697830101</v>
       </c>
       <c r="E65">
-        <v>2.0176</v>
+        <v>2.1228</v>
       </c>
       <c r="F65">
-        <v>6.6276</v>
+        <v>6.7328</v>
       </c>
       <c r="G65">
         <v>0.081</v>
@@ -6980,45 +6980,45 @@
         <v>1.2</v>
       </c>
       <c r="M65">
-        <v>0.47652444</v>
+        <v>0.5103462400000001</v>
       </c>
       <c r="N65">
-        <v>0.7234755599999999</v>
+        <v>0.6896537599999999</v>
       </c>
       <c r="O65">
-        <v>0.1736341344</v>
+        <v>0.1655169024</v>
       </c>
       <c r="P65">
-        <v>0.5498414255999999</v>
+        <v>0.5241368576</v>
       </c>
       <c r="Q65">
-        <v>1.0698414256</v>
+        <v>1.0441368576</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2053256537370046</v>
+        <v>0.2092933302227663</v>
       </c>
       <c r="T65">
-        <v>2.689831700007228</v>
+        <v>2.756732425606947</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.24</v>
       </c>
       <c r="W65">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.518233902126824</v>
+        <v>2.351344843845621</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7026,22 +7026,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1122147188801959</v>
+        <v>0.1121659058777</v>
       </c>
       <c r="C66">
-        <v>3.951086978301013</v>
+        <v>3.853685542061878</v>
       </c>
       <c r="D66">
-        <v>10.60288697830101</v>
+        <v>10.61068554206188</v>
       </c>
       <c r="E66">
-        <v>2.1228</v>
+        <v>2.228</v>
       </c>
       <c r="F66">
-        <v>6.7328</v>
+        <v>6.838</v>
       </c>
       <c r="G66">
         <v>0.081</v>
@@ -7062,28 +7062,28 @@
         <v>1.2</v>
       </c>
       <c r="M66">
-        <v>0.5103462400000001</v>
+        <v>0.5183204</v>
       </c>
       <c r="N66">
-        <v>0.6896537599999999</v>
+        <v>0.6816795999999999</v>
       </c>
       <c r="O66">
-        <v>0.1655169024</v>
+        <v>0.163603104</v>
       </c>
       <c r="P66">
-        <v>0.5241368576</v>
+        <v>0.5180764959999999</v>
       </c>
       <c r="Q66">
-        <v>1.0441368576</v>
+        <v>1.038076496</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2092933302227663</v>
+        <v>0.213487731079143</v>
       </c>
       <c r="T66">
-        <v>2.756732425606947</v>
+        <v>2.827456049812365</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.351344843845621</v>
+        <v>2.315170307786458</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7108,22 +7108,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1121659058777</v>
+        <v>0.1121170928752042</v>
       </c>
       <c r="C67">
-        <v>3.853685542061878</v>
+        <v>3.75629558616049</v>
       </c>
       <c r="D67">
-        <v>10.61068554206188</v>
+        <v>10.61849558616049</v>
       </c>
       <c r="E67">
-        <v>2.228</v>
+        <v>2.3332</v>
       </c>
       <c r="F67">
-        <v>6.838</v>
+        <v>6.9432</v>
       </c>
       <c r="G67">
         <v>0.081</v>
@@ -7144,28 +7144,28 @@
         <v>1.2</v>
       </c>
       <c r="M67">
-        <v>0.5183204</v>
+        <v>0.5262945600000001</v>
       </c>
       <c r="N67">
-        <v>0.6816795999999999</v>
+        <v>0.6737054399999999</v>
       </c>
       <c r="O67">
-        <v>0.163603104</v>
+        <v>0.1616893056</v>
       </c>
       <c r="P67">
-        <v>0.5180764959999999</v>
+        <v>0.5120161343999999</v>
       </c>
       <c r="Q67">
-        <v>1.038076496</v>
+        <v>1.0320161344</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.213487731079143</v>
+        <v>0.2179288613976594</v>
       </c>
       <c r="T67">
-        <v>2.827456049812365</v>
+        <v>2.902339887206336</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.315170307786458</v>
+        <v>2.280091969789693</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7190,22 +7190,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1121170928752042</v>
+        <v>0.1120682798727084</v>
       </c>
       <c r="C68">
-        <v>3.75629558616049</v>
+        <v>3.658917135965992</v>
       </c>
       <c r="D68">
-        <v>10.61849558616049</v>
+        <v>10.62631713596599</v>
       </c>
       <c r="E68">
-        <v>2.3332</v>
+        <v>2.4384</v>
       </c>
       <c r="F68">
-        <v>6.9432</v>
+        <v>7.0484</v>
       </c>
       <c r="G68">
         <v>0.081</v>
@@ -7226,28 +7226,28 @@
         <v>1.2</v>
       </c>
       <c r="M68">
-        <v>0.5262945600000001</v>
+        <v>0.53426872</v>
       </c>
       <c r="N68">
-        <v>0.6737054399999999</v>
+        <v>0.6657312799999999</v>
       </c>
       <c r="O68">
-        <v>0.1616893056</v>
+        <v>0.1597755072</v>
       </c>
       <c r="P68">
-        <v>0.5120161343999999</v>
+        <v>0.5059557727999999</v>
       </c>
       <c r="Q68">
-        <v>1.0320161344</v>
+        <v>1.0259557728</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2179288613976594</v>
+        <v>0.2226391511294193</v>
       </c>
       <c r="T68">
-        <v>2.902339887206336</v>
+        <v>2.981762138987821</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.280091969789693</v>
+        <v>2.246060746359996</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7272,22 +7272,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1120682798727084</v>
+        <v>0.1120194668702126</v>
       </c>
       <c r="C69">
-        <v>3.658917135965992</v>
+        <v>3.561550216922321</v>
       </c>
       <c r="D69">
-        <v>10.62631713596599</v>
+        <v>10.63415021692232</v>
       </c>
       <c r="E69">
-        <v>2.4384</v>
+        <v>2.5436</v>
       </c>
       <c r="F69">
-        <v>7.0484</v>
+        <v>7.1536</v>
       </c>
       <c r="G69">
         <v>0.081</v>
@@ -7308,28 +7308,28 @@
         <v>1.2</v>
       </c>
       <c r="M69">
-        <v>0.53426872</v>
+        <v>0.5422428800000001</v>
       </c>
       <c r="N69">
-        <v>0.6657312799999999</v>
+        <v>0.6577571199999999</v>
       </c>
       <c r="O69">
-        <v>0.1597755072</v>
+        <v>0.1578617088</v>
       </c>
       <c r="P69">
-        <v>0.5059557727999999</v>
+        <v>0.4998954111999999</v>
       </c>
       <c r="Q69">
-        <v>1.0259557728</v>
+        <v>1.0198954112</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2226391511294193</v>
+        <v>0.2276438339694142</v>
       </c>
       <c r="T69">
-        <v>2.981762138987821</v>
+        <v>3.066148281505648</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.246060746359996</v>
+        <v>2.213030441266467</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7354,22 +7354,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1120194668702126</v>
+        <v>0.1119706538677167</v>
       </c>
       <c r="C70">
-        <v>3.561550216922321</v>
+        <v>3.464194854548498</v>
       </c>
       <c r="D70">
-        <v>10.63415021692232</v>
+        <v>10.6419948545485</v>
       </c>
       <c r="E70">
-        <v>2.5436</v>
+        <v>2.6488</v>
       </c>
       <c r="F70">
-        <v>7.1536</v>
+        <v>7.2588</v>
       </c>
       <c r="G70">
         <v>0.081</v>
@@ -7390,28 +7390,28 @@
         <v>1.2</v>
       </c>
       <c r="M70">
-        <v>0.5422428800000001</v>
+        <v>0.55021704</v>
       </c>
       <c r="N70">
-        <v>0.6577571199999999</v>
+        <v>0.6497829599999999</v>
       </c>
       <c r="O70">
-        <v>0.1578617088</v>
+        <v>0.1559479104</v>
       </c>
       <c r="P70">
-        <v>0.4998954111999999</v>
+        <v>0.4938350495999999</v>
       </c>
       <c r="Q70">
-        <v>1.0198954112</v>
+        <v>1.0138350496</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2276438339694142</v>
+        <v>0.2329713995732798</v>
       </c>
       <c r="T70">
-        <v>3.066148281505648</v>
+        <v>3.155978691282691</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.213030441266467</v>
+        <v>2.180957536320576</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7436,22 +7436,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1119706538677167</v>
+        <v>0.1119218408652209</v>
       </c>
       <c r="C71">
-        <v>3.464194854548498</v>
+        <v>3.366851074438907</v>
       </c>
       <c r="D71">
-        <v>10.6419948545485</v>
+        <v>10.64985107443891</v>
       </c>
       <c r="E71">
-        <v>2.6488</v>
+        <v>2.754</v>
       </c>
       <c r="F71">
-        <v>7.2588</v>
+        <v>7.364000000000001</v>
       </c>
       <c r="G71">
         <v>0.081</v>
@@ -7472,28 +7472,28 @@
         <v>1.2</v>
       </c>
       <c r="M71">
-        <v>0.55021704</v>
+        <v>0.5581912000000001</v>
       </c>
       <c r="N71">
-        <v>0.6497829599999999</v>
+        <v>0.6418087999999998</v>
       </c>
       <c r="O71">
-        <v>0.1559479104</v>
+        <v>0.1540341119999999</v>
       </c>
       <c r="P71">
-        <v>0.4938350495999999</v>
+        <v>0.4877746879999999</v>
       </c>
       <c r="Q71">
-        <v>1.0138350496</v>
+        <v>1.007774688</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2329713995732798</v>
+        <v>0.238654136217403</v>
       </c>
       <c r="T71">
-        <v>3.155978691282691</v>
+        <v>3.251797795044868</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.180957536320576</v>
+        <v>2.149801000087425</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7518,22 +7518,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1119218408652209</v>
+        <v>0.1118730278627251</v>
       </c>
       <c r="C72">
-        <v>3.366851074438907</v>
+        <v>3.269518902263551</v>
       </c>
       <c r="D72">
-        <v>10.64985107443891</v>
+        <v>10.65771890226355</v>
       </c>
       <c r="E72">
-        <v>2.754</v>
+        <v>2.8592</v>
       </c>
       <c r="F72">
-        <v>7.364000000000001</v>
+        <v>7.469200000000001</v>
       </c>
       <c r="G72">
         <v>0.081</v>
@@ -7554,28 +7554,28 @@
         <v>1.2</v>
       </c>
       <c r="M72">
-        <v>0.5581912000000001</v>
+        <v>0.5661653600000001</v>
       </c>
       <c r="N72">
-        <v>0.6418087999999998</v>
+        <v>0.6338346399999999</v>
       </c>
       <c r="O72">
-        <v>0.1540341119999999</v>
+        <v>0.1521203136</v>
       </c>
       <c r="P72">
-        <v>0.4877746879999999</v>
+        <v>0.4817143263999999</v>
       </c>
       <c r="Q72">
-        <v>1.007774688</v>
+        <v>1.0017143264</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.238654136217403</v>
+        <v>0.2447287857335348</v>
       </c>
       <c r="T72">
-        <v>3.251797795044868</v>
+        <v>3.354225112859611</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.149801000087425</v>
+        <v>2.11952211276225</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7600,22 +7600,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1118730278627251</v>
+        <v>0.1118242148602292</v>
       </c>
       <c r="C73">
-        <v>3.269518902263552</v>
+        <v>3.172198363768357</v>
       </c>
       <c r="D73">
-        <v>10.65771890226355</v>
+        <v>10.66559836376836</v>
       </c>
       <c r="E73">
-        <v>2.859199999999999</v>
+        <v>2.964399999999999</v>
       </c>
       <c r="F73">
-        <v>7.469199999999999</v>
+        <v>7.5744</v>
       </c>
       <c r="G73">
         <v>0.081</v>
@@ -7636,28 +7636,28 @@
         <v>1.2</v>
       </c>
       <c r="M73">
-        <v>0.56616536</v>
+        <v>0.57413952</v>
       </c>
       <c r="N73">
-        <v>0.63383464</v>
+        <v>0.6258604799999999</v>
       </c>
       <c r="O73">
-        <v>0.1521203136</v>
+        <v>0.1502065152</v>
       </c>
       <c r="P73">
-        <v>0.4817143264</v>
+        <v>0.4756539648</v>
       </c>
       <c r="Q73">
-        <v>1.0017143264</v>
+        <v>0.9956539648</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2447287857335347</v>
+        <v>0.2512373387865329</v>
       </c>
       <c r="T73">
-        <v>3.35422511285961</v>
+        <v>3.46396866766112</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.11952211276225</v>
+        <v>2.090084305640552</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7682,22 +7682,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1118242148602292</v>
+        <v>0.1117754018577334</v>
       </c>
       <c r="C74">
-        <v>3.172198363768357</v>
+        <v>3.074889484775439</v>
       </c>
       <c r="D74">
-        <v>10.66559836376836</v>
+        <v>10.67348948477544</v>
       </c>
       <c r="E74">
-        <v>2.964399999999999</v>
+        <v>3.069599999999999</v>
       </c>
       <c r="F74">
-        <v>7.5744</v>
+        <v>7.6796</v>
       </c>
       <c r="G74">
         <v>0.081</v>
@@ -7718,28 +7718,28 @@
         <v>1.2</v>
       </c>
       <c r="M74">
-        <v>0.57413952</v>
+        <v>0.5821136800000001</v>
       </c>
       <c r="N74">
-        <v>0.6258604799999999</v>
+        <v>0.6178863199999999</v>
       </c>
       <c r="O74">
-        <v>0.1502065152</v>
+        <v>0.1482927168</v>
       </c>
       <c r="P74">
-        <v>0.4756539648</v>
+        <v>0.4695936031999999</v>
       </c>
       <c r="Q74">
-        <v>0.9956539648</v>
+        <v>0.9895936031999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2512373387865329</v>
+        <v>0.258228006880494</v>
       </c>
       <c r="T74">
-        <v>3.46396866766112</v>
+        <v>3.581841374670148</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.090084305640552</v>
+        <v>2.061453013782462</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7764,22 +7764,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1117754018577334</v>
+        <v>0.1117265888552375</v>
       </c>
       <c r="C75">
-        <v>3.074889484775439</v>
+        <v>2.977592291183391</v>
       </c>
       <c r="D75">
-        <v>10.67348948477544</v>
+        <v>10.68139229118339</v>
       </c>
       <c r="E75">
-        <v>3.069599999999999</v>
+        <v>3.174799999999999</v>
       </c>
       <c r="F75">
-        <v>7.6796</v>
+        <v>7.7848</v>
       </c>
       <c r="G75">
         <v>0.081</v>
@@ -7800,28 +7800,28 @@
         <v>1.2</v>
       </c>
       <c r="M75">
-        <v>0.5821136800000001</v>
+        <v>0.59008784</v>
       </c>
       <c r="N75">
-        <v>0.6178863199999999</v>
+        <v>0.6099121599999999</v>
       </c>
       <c r="O75">
-        <v>0.1482927168</v>
+        <v>0.1463789184</v>
       </c>
       <c r="P75">
-        <v>0.4695936031999999</v>
+        <v>0.4635332416</v>
       </c>
       <c r="Q75">
-        <v>0.9895936031999999</v>
+        <v>0.9835332416</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.258228006880494</v>
+        <v>0.2657564186739906</v>
       </c>
       <c r="T75">
-        <v>3.581841374670148</v>
+        <v>3.708781212987563</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.061453013782462</v>
+        <v>2.03359554062324</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7846,22 +7846,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1117265888552375</v>
+        <v>0.1116777758527417</v>
       </c>
       <c r="C76">
-        <v>2.977592291183391</v>
+        <v>2.880306808967563</v>
       </c>
       <c r="D76">
-        <v>10.68139229118339</v>
+        <v>10.68930680896756</v>
       </c>
       <c r="E76">
-        <v>3.174799999999999</v>
+        <v>3.279999999999999</v>
       </c>
       <c r="F76">
-        <v>7.7848</v>
+        <v>7.89</v>
       </c>
       <c r="G76">
         <v>0.081</v>
@@ -7882,28 +7882,28 @@
         <v>1.2</v>
       </c>
       <c r="M76">
-        <v>0.59008784</v>
+        <v>0.598062</v>
       </c>
       <c r="N76">
-        <v>0.6099121599999999</v>
+        <v>0.601938</v>
       </c>
       <c r="O76">
-        <v>0.1463789184</v>
+        <v>0.14446512</v>
       </c>
       <c r="P76">
-        <v>0.4635332416</v>
+        <v>0.45747288</v>
       </c>
       <c r="Q76">
-        <v>0.9835332416</v>
+        <v>0.97747288</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2657564186739906</v>
+        <v>0.2738871034109669</v>
       </c>
       <c r="T76">
-        <v>3.708781212987563</v>
+        <v>3.845876238370373</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.03359554062324</v>
+        <v>2.00648093341493</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7928,22 +7928,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1116777758527417</v>
+        <v>0.1198308828502459</v>
       </c>
       <c r="C77">
-        <v>2.880306808967563</v>
+        <v>1.597881051455569</v>
       </c>
       <c r="D77">
-        <v>10.68930680896756</v>
+        <v>9.512081051455569</v>
       </c>
       <c r="E77">
-        <v>3.279999999999999</v>
+        <v>3.385199999999999</v>
       </c>
       <c r="F77">
-        <v>7.89</v>
+        <v>7.9952</v>
       </c>
       <c r="G77">
         <v>0.081</v>
@@ -7964,45 +7964,45 @@
         <v>1.2</v>
       </c>
       <c r="M77">
-        <v>0.598062</v>
+        <v>0.719568</v>
       </c>
       <c r="N77">
-        <v>0.601938</v>
+        <v>0.480432</v>
       </c>
       <c r="O77">
-        <v>0.14446512</v>
+        <v>0.11530368</v>
       </c>
       <c r="P77">
-        <v>0.45747288</v>
+        <v>0.36512832</v>
       </c>
       <c r="Q77">
-        <v>0.97747288</v>
+        <v>0.88512832</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2738871034109669</v>
+        <v>0.282695345209358</v>
       </c>
       <c r="T77">
-        <v>3.845876238370373</v>
+        <v>3.994395849201749</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.24</v>
       </c>
       <c r="W77">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.00648093341493</v>
+        <v>1.667667267026883</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8010,22 +8010,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1198308828502459</v>
+        <v>0.1198899898477501</v>
       </c>
       <c r="C78">
-        <v>1.597881051455569</v>
+        <v>1.485092569501079</v>
       </c>
       <c r="D78">
-        <v>9.512081051455569</v>
+        <v>9.50449256950108</v>
       </c>
       <c r="E78">
-        <v>3.385199999999999</v>
+        <v>3.4904</v>
       </c>
       <c r="F78">
-        <v>7.9952</v>
+        <v>8.1004</v>
       </c>
       <c r="G78">
         <v>0.081</v>
@@ -8046,28 +8046,28 @@
         <v>1.2</v>
       </c>
       <c r="M78">
-        <v>0.719568</v>
+        <v>0.729036</v>
       </c>
       <c r="N78">
-        <v>0.480432</v>
+        <v>0.4709639999999999</v>
       </c>
       <c r="O78">
-        <v>0.11530368</v>
+        <v>0.11303136</v>
       </c>
       <c r="P78">
-        <v>0.36512832</v>
+        <v>0.35793264</v>
       </c>
       <c r="Q78">
-        <v>0.88512832</v>
+        <v>0.87793264</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.282695345209358</v>
+        <v>0.2922695210771743</v>
       </c>
       <c r="T78">
-        <v>3.994395849201749</v>
+        <v>4.155830208801071</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.667667267026883</v>
+        <v>1.646009250571988</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8092,22 +8092,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1198899898477501</v>
+        <v>0.1199490968452543</v>
       </c>
       <c r="C79">
-        <v>1.485092569501079</v>
+        <v>1.372316185667891</v>
       </c>
       <c r="D79">
-        <v>9.50449256950108</v>
+        <v>9.496916185667892</v>
       </c>
       <c r="E79">
-        <v>3.4904</v>
+        <v>3.5956</v>
       </c>
       <c r="F79">
-        <v>8.1004</v>
+        <v>8.2056</v>
       </c>
       <c r="G79">
         <v>0.081</v>
@@ -8128,28 +8128,28 @@
         <v>1.2</v>
       </c>
       <c r="M79">
-        <v>0.729036</v>
+        <v>0.738504</v>
       </c>
       <c r="N79">
-        <v>0.4709639999999999</v>
+        <v>0.4614959999999999</v>
       </c>
       <c r="O79">
-        <v>0.11303136</v>
+        <v>0.11075904</v>
       </c>
       <c r="P79">
-        <v>0.35793264</v>
+        <v>0.3507369599999999</v>
       </c>
       <c r="Q79">
-        <v>0.87793264</v>
+        <v>0.8707369599999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2922695210771743</v>
+        <v>0.3027140765693375</v>
       </c>
       <c r="T79">
-        <v>4.155830208801071</v>
+        <v>4.331940419273058</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.646009250571988</v>
+        <v>1.624906567872347</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8174,22 +8174,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1199490968452543</v>
+        <v>0.1200082038427584</v>
       </c>
       <c r="C80">
-        <v>1.372316185667891</v>
+        <v>1.259551871047462</v>
       </c>
       <c r="D80">
-        <v>9.496916185667892</v>
+        <v>9.489351871047463</v>
       </c>
       <c r="E80">
-        <v>3.5956</v>
+        <v>3.7008</v>
       </c>
       <c r="F80">
-        <v>8.2056</v>
+        <v>8.3108</v>
       </c>
       <c r="G80">
         <v>0.081</v>
@@ -8210,28 +8210,28 @@
         <v>1.2</v>
       </c>
       <c r="M80">
-        <v>0.738504</v>
+        <v>0.747972</v>
       </c>
       <c r="N80">
-        <v>0.4614959999999999</v>
+        <v>0.452028</v>
       </c>
       <c r="O80">
-        <v>0.11075904</v>
+        <v>0.10848672</v>
       </c>
       <c r="P80">
-        <v>0.3507369599999999</v>
+        <v>0.34354128</v>
       </c>
       <c r="Q80">
-        <v>0.8707369599999999</v>
+        <v>0.86354128</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3027140765693375</v>
+        <v>0.314153351632183</v>
       </c>
       <c r="T80">
-        <v>4.331940419273058</v>
+        <v>4.524823030742379</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.624906567872347</v>
+        <v>1.604338130304343</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8256,22 +8256,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1200082038427584</v>
+        <v>0.1200673108402626</v>
       </c>
       <c r="C81">
-        <v>1.259551871047462</v>
+        <v>1.14679959682328</v>
       </c>
       <c r="D81">
-        <v>9.489351871047463</v>
+        <v>9.481799596823281</v>
       </c>
       <c r="E81">
-        <v>3.7008</v>
+        <v>3.806</v>
       </c>
       <c r="F81">
-        <v>8.3108</v>
+        <v>8.416</v>
       </c>
       <c r="G81">
         <v>0.081</v>
@@ -8292,28 +8292,28 @@
         <v>1.2</v>
       </c>
       <c r="M81">
-        <v>0.747972</v>
+        <v>0.75744</v>
       </c>
       <c r="N81">
-        <v>0.452028</v>
+        <v>0.44256</v>
       </c>
       <c r="O81">
-        <v>0.10848672</v>
+        <v>0.1062144</v>
       </c>
       <c r="P81">
-        <v>0.34354128</v>
+        <v>0.3363456</v>
       </c>
       <c r="Q81">
-        <v>0.86354128</v>
+        <v>0.8563456</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.314153351632183</v>
+        <v>0.326736554201313</v>
       </c>
       <c r="T81">
-        <v>4.524823030742379</v>
+        <v>4.736993903358631</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.604338130304343</v>
+        <v>1.584283903675539</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8338,22 +8338,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1200673108402626</v>
+        <v>0.1201264178377668</v>
       </c>
       <c r="C82">
-        <v>1.14679959682328</v>
+        <v>1.0340593342705</v>
       </c>
       <c r="D82">
-        <v>9.481799596823281</v>
+        <v>9.474259334270501</v>
       </c>
       <c r="E82">
-        <v>3.806</v>
+        <v>3.9112</v>
       </c>
       <c r="F82">
-        <v>8.416</v>
+        <v>8.5212</v>
       </c>
       <c r="G82">
         <v>0.081</v>
@@ -8374,28 +8374,28 @@
         <v>1.2</v>
       </c>
       <c r="M82">
-        <v>0.75744</v>
+        <v>0.766908</v>
       </c>
       <c r="N82">
-        <v>0.44256</v>
+        <v>0.4330919999999999</v>
       </c>
       <c r="O82">
-        <v>0.1062144</v>
+        <v>0.10394208</v>
       </c>
       <c r="P82">
-        <v>0.3363456</v>
+        <v>0.3291499199999999</v>
       </c>
       <c r="Q82">
-        <v>0.8563456</v>
+        <v>0.8491499199999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.326736554201313</v>
+        <v>0.3406443044092988</v>
       </c>
       <c r="T82">
-        <v>4.736993903358631</v>
+        <v>4.971498552039751</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.584283903675539</v>
+        <v>1.564724843136334</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8420,22 +8420,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1201264178377668</v>
+        <v>0.1201855248352709</v>
       </c>
       <c r="C83">
-        <v>1.0340593342705</v>
+        <v>0.9213310547555729</v>
       </c>
       <c r="D83">
-        <v>9.474259334270501</v>
+        <v>9.466731054755574</v>
       </c>
       <c r="E83">
-        <v>3.9112</v>
+        <v>4.0164</v>
       </c>
       <c r="F83">
-        <v>8.5212</v>
+        <v>8.6264</v>
       </c>
       <c r="G83">
         <v>0.081</v>
@@ -8456,28 +8456,28 @@
         <v>1.2</v>
       </c>
       <c r="M83">
-        <v>0.766908</v>
+        <v>0.776376</v>
       </c>
       <c r="N83">
-        <v>0.4330919999999999</v>
+        <v>0.423624</v>
       </c>
       <c r="O83">
-        <v>0.10394208</v>
+        <v>0.10166976</v>
       </c>
       <c r="P83">
-        <v>0.3291499199999999</v>
+        <v>0.32195424</v>
       </c>
       <c r="Q83">
-        <v>0.8491499199999999</v>
+        <v>0.84195424</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3406443044092988</v>
+        <v>0.3560973601959497</v>
       </c>
       <c r="T83">
-        <v>4.971498552039751</v>
+        <v>5.232059272796552</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.564724843136334</v>
+        <v>1.545642832854184</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8502,22 +8502,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1201855248352709</v>
+        <v>0.1202446318327751</v>
       </c>
       <c r="C84">
-        <v>0.9213310547555729</v>
+        <v>0.8086147297358828</v>
       </c>
       <c r="D84">
-        <v>9.466731054755574</v>
+        <v>9.459214729735884</v>
       </c>
       <c r="E84">
-        <v>4.0164</v>
+        <v>4.1216</v>
       </c>
       <c r="F84">
-        <v>8.6264</v>
+        <v>8.7316</v>
       </c>
       <c r="G84">
         <v>0.081</v>
@@ -8538,28 +8538,28 @@
         <v>1.2</v>
       </c>
       <c r="M84">
-        <v>0.776376</v>
+        <v>0.785844</v>
       </c>
       <c r="N84">
-        <v>0.423624</v>
+        <v>0.414156</v>
       </c>
       <c r="O84">
-        <v>0.10166976</v>
+        <v>0.09939743999999999</v>
       </c>
       <c r="P84">
-        <v>0.32195424</v>
+        <v>0.31475856</v>
       </c>
       <c r="Q84">
-        <v>0.84195424</v>
+        <v>0.83475856</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3560973601959497</v>
+        <v>0.3733684225457361</v>
       </c>
       <c r="T84">
-        <v>5.232059272796552</v>
+        <v>5.52327419599533</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.545642832854184</v>
+        <v>1.527020630048712</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8584,22 +8584,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1202446318327751</v>
+        <v>0.1203037388302793</v>
       </c>
       <c r="C85">
-        <v>0.8086147297358828</v>
+        <v>0.6959103307594035</v>
       </c>
       <c r="D85">
-        <v>9.459214729735884</v>
+        <v>9.451710330759404</v>
       </c>
       <c r="E85">
-        <v>4.1216</v>
+        <v>4.2268</v>
       </c>
       <c r="F85">
-        <v>8.7316</v>
+        <v>8.8368</v>
       </c>
       <c r="G85">
         <v>0.081</v>
@@ -8620,28 +8620,28 @@
         <v>1.2</v>
       </c>
       <c r="M85">
-        <v>0.785844</v>
+        <v>0.795312</v>
       </c>
       <c r="N85">
-        <v>0.414156</v>
+        <v>0.4046879999999999</v>
       </c>
       <c r="O85">
-        <v>0.09939743999999999</v>
+        <v>0.09712511999999998</v>
       </c>
       <c r="P85">
-        <v>0.31475856</v>
+        <v>0.30756288</v>
       </c>
       <c r="Q85">
-        <v>0.83475856</v>
+        <v>0.82756288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3733684225457361</v>
+        <v>0.3927983676892457</v>
       </c>
       <c r="T85">
-        <v>5.52327419599533</v>
+        <v>5.850890984593955</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8658,7 +8658,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.527020630048712</v>
+        <v>1.508841813024322</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8666,22 +8666,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1203037388302793</v>
+        <v>0.1608441885227698</v>
       </c>
       <c r="C86">
-        <v>0.6959103307594052</v>
+        <v>-2.739980181228566</v>
       </c>
       <c r="D86">
-        <v>9.451710330759404</v>
+        <v>6.121019818771433</v>
       </c>
       <c r="E86">
-        <v>4.226799999999998</v>
+        <v>4.332</v>
       </c>
       <c r="F86">
-        <v>8.836799999999998</v>
+        <v>8.942</v>
       </c>
       <c r="G86">
         <v>0.081</v>
@@ -8702,45 +8702,45 @@
         <v>1.2</v>
       </c>
       <c r="M86">
-        <v>0.7953119999999998</v>
+        <v>1.3126856</v>
       </c>
       <c r="N86">
-        <v>0.4046880000000002</v>
+        <v>-0.1126856000000003</v>
       </c>
       <c r="O86">
-        <v>0.09712512000000004</v>
+        <v>-0.02704454400000007</v>
       </c>
       <c r="P86">
-        <v>0.3075628800000001</v>
+        <v>-0.08564105600000022</v>
       </c>
       <c r="Q86">
-        <v>0.8275628800000001</v>
+        <v>0.4343589439999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3927983676892454</v>
+        <v>0.4229374291885539</v>
       </c>
       <c r="T86">
-        <v>5.85089098459395</v>
+        <v>6.359078859899313</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.24</v>
+        <v>0.2193975465259921</v>
       </c>
       <c r="W86">
-        <v>0.0684</v>
+        <v>0.1145924401699844</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.508841813024323</v>
+        <v>0.9141564438583006</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8748,22 +8748,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1608441885227698</v>
+        <v>0.1618541885227698</v>
       </c>
       <c r="C87">
-        <v>-2.739980181228566</v>
+        <v>-2.898450382809838</v>
       </c>
       <c r="D87">
-        <v>6.121019818771433</v>
+        <v>6.067749617190162</v>
       </c>
       <c r="E87">
-        <v>4.332</v>
+        <v>4.4372</v>
       </c>
       <c r="F87">
-        <v>8.942</v>
+        <v>9.0472</v>
       </c>
       <c r="G87">
         <v>0.081</v>
@@ -8784,37 +8784,37 @@
         <v>1.2</v>
       </c>
       <c r="M87">
-        <v>1.3126856</v>
+        <v>1.32812896</v>
       </c>
       <c r="N87">
-        <v>-0.1126856000000003</v>
+        <v>-0.1281289600000002</v>
       </c>
       <c r="O87">
-        <v>-0.02704454400000007</v>
+        <v>-0.03075095040000004</v>
       </c>
       <c r="P87">
-        <v>-0.08564105600000022</v>
+        <v>-0.09737800960000013</v>
       </c>
       <c r="Q87">
-        <v>0.4343589439999998</v>
+        <v>0.4226219903999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4229374291885539</v>
+        <v>0.4498758169877363</v>
       </c>
       <c r="T87">
-        <v>6.359078859899313</v>
+        <v>6.813298778463548</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2193975465259921</v>
+        <v>0.216846412264062</v>
       </c>
       <c r="W87">
-        <v>0.1145924401699844</v>
+        <v>0.1149669466796357</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9141564438583006</v>
+        <v>0.9035267177669252</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8830,22 +8830,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1618541885227698</v>
+        <v>0.1628641885227698</v>
       </c>
       <c r="C88">
-        <v>-2.898450382809838</v>
+        <v>-3.056001380930582</v>
       </c>
       <c r="D88">
-        <v>6.067749617190162</v>
+        <v>6.015398619069417</v>
       </c>
       <c r="E88">
-        <v>4.4372</v>
+        <v>4.5424</v>
       </c>
       <c r="F88">
-        <v>9.0472</v>
+        <v>9.1524</v>
       </c>
       <c r="G88">
         <v>0.081</v>
@@ -8866,37 +8866,37 @@
         <v>1.2</v>
       </c>
       <c r="M88">
-        <v>1.32812896</v>
+        <v>1.34357232</v>
       </c>
       <c r="N88">
-        <v>-0.1281289600000002</v>
+        <v>-0.1435723200000001</v>
       </c>
       <c r="O88">
-        <v>-0.03075095040000004</v>
+        <v>-0.03445735680000002</v>
       </c>
       <c r="P88">
-        <v>-0.09737800960000013</v>
+        <v>-0.1091149632000001</v>
       </c>
       <c r="Q88">
-        <v>0.4226219903999999</v>
+        <v>0.4108850367999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4498758169877363</v>
+        <v>0.480958572140639</v>
       </c>
       <c r="T88">
-        <v>6.813298778463548</v>
+        <v>7.337398684499206</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.216846412264062</v>
+        <v>0.214353924766774</v>
       </c>
       <c r="W88">
-        <v>0.1149669466796357</v>
+        <v>0.1153328438442376</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9035267177669252</v>
+        <v>0.8931413531948916</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8912,22 +8912,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1628641885227698</v>
+        <v>0.1638741885227698</v>
       </c>
       <c r="C89">
-        <v>-3.056001380930582</v>
+        <v>-3.212656764035661</v>
       </c>
       <c r="D89">
-        <v>6.015398619069417</v>
+        <v>5.963943235964338</v>
       </c>
       <c r="E89">
-        <v>4.5424</v>
+        <v>4.6476</v>
       </c>
       <c r="F89">
-        <v>9.1524</v>
+        <v>9.2576</v>
       </c>
       <c r="G89">
         <v>0.081</v>
@@ -8948,37 +8948,37 @@
         <v>1.2</v>
       </c>
       <c r="M89">
-        <v>1.34357232</v>
+        <v>1.35901568</v>
       </c>
       <c r="N89">
-        <v>-0.1435723200000001</v>
+        <v>-0.1590156800000002</v>
       </c>
       <c r="O89">
-        <v>-0.03445735680000002</v>
+        <v>-0.03816376320000005</v>
       </c>
       <c r="P89">
-        <v>-0.1091149632000001</v>
+        <v>-0.1208519168000002</v>
       </c>
       <c r="Q89">
-        <v>0.4108850367999999</v>
+        <v>0.3991480831999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.480958572140639</v>
+        <v>0.5172217864856924</v>
       </c>
       <c r="T89">
-        <v>7.337398684499206</v>
+        <v>7.948848574874141</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.214353924766774</v>
+        <v>0.2119180847126061</v>
       </c>
       <c r="W89">
-        <v>0.1153328438442376</v>
+        <v>0.1156904251641894</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8931413531948916</v>
+        <v>0.8829920196358587</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8994,22 +8994,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1638741885227698</v>
+        <v>0.1648841885227698</v>
       </c>
       <c r="C90">
-        <v>-3.212656764035661</v>
+        <v>-3.368439320318286</v>
       </c>
       <c r="D90">
-        <v>5.963943235964338</v>
+        <v>5.913360679681714</v>
       </c>
       <c r="E90">
-        <v>4.6476</v>
+        <v>4.7528</v>
       </c>
       <c r="F90">
-        <v>9.2576</v>
+        <v>9.3628</v>
       </c>
       <c r="G90">
         <v>0.081</v>
@@ -9030,37 +9030,37 @@
         <v>1.2</v>
       </c>
       <c r="M90">
-        <v>1.35901568</v>
+        <v>1.37445904</v>
       </c>
       <c r="N90">
-        <v>-0.1590156800000002</v>
+        <v>-0.1744590400000001</v>
       </c>
       <c r="O90">
-        <v>-0.03816376320000005</v>
+        <v>-0.04187016960000003</v>
       </c>
       <c r="P90">
-        <v>-0.1208519168000002</v>
+        <v>-0.1325888704000001</v>
       </c>
       <c r="Q90">
-        <v>0.3991480831999998</v>
+        <v>0.3874111295999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5172217864856924</v>
+        <v>0.5600783125298462</v>
       </c>
       <c r="T90">
-        <v>7.948848574874141</v>
+        <v>8.671471172589973</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2119180847126061</v>
+        <v>0.2095369826371835</v>
       </c>
       <c r="W90">
-        <v>0.1156904251641894</v>
+        <v>0.1160399709488615</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8829920196358587</v>
+        <v>0.8730707609882649</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9076,22 +9076,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1648841885227698</v>
+        <v>0.1658941885227698</v>
       </c>
       <c r="C91">
-        <v>-3.368439320318286</v>
+        <v>-3.523371071370887</v>
       </c>
       <c r="D91">
-        <v>5.913360679681714</v>
+        <v>5.863628928629113</v>
       </c>
       <c r="E91">
-        <v>4.7528</v>
+        <v>4.858</v>
       </c>
       <c r="F91">
-        <v>9.3628</v>
+        <v>9.468</v>
       </c>
       <c r="G91">
         <v>0.081</v>
@@ -9112,37 +9112,37 @@
         <v>1.2</v>
       </c>
       <c r="M91">
-        <v>1.37445904</v>
+        <v>1.3899024</v>
       </c>
       <c r="N91">
-        <v>-0.1744590400000001</v>
+        <v>-0.1899024000000002</v>
       </c>
       <c r="O91">
-        <v>-0.04187016960000003</v>
+        <v>-0.04557657600000006</v>
       </c>
       <c r="P91">
-        <v>-0.1325888704000001</v>
+        <v>-0.1443258240000002</v>
       </c>
       <c r="Q91">
-        <v>0.3874111295999999</v>
+        <v>0.3756741759999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5600783125298462</v>
+        <v>0.6115061437828307</v>
       </c>
       <c r="T91">
-        <v>8.671471172589973</v>
+        <v>9.538618289848969</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2095369826371835</v>
+        <v>0.2072087939412148</v>
       </c>
       <c r="W91">
-        <v>0.1160399709488615</v>
+        <v>0.1163817490494297</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8730707609882649</v>
+        <v>0.8633699747550618</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9158,22 +9158,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1658941885227698</v>
+        <v>0.1669041885227698</v>
       </c>
       <c r="C92">
-        <v>-3.523371071370887</v>
+        <v>-3.677473304152059</v>
       </c>
       <c r="D92">
-        <v>5.863628928629113</v>
+        <v>5.81472669584794</v>
       </c>
       <c r="E92">
-        <v>4.858</v>
+        <v>4.9632</v>
       </c>
       <c r="F92">
-        <v>9.468</v>
+        <v>9.5732</v>
       </c>
       <c r="G92">
         <v>0.081</v>
@@ -9194,37 +9194,37 @@
         <v>1.2</v>
       </c>
       <c r="M92">
-        <v>1.3899024</v>
+        <v>1.40534576</v>
       </c>
       <c r="N92">
-        <v>-0.1899024000000002</v>
+        <v>-0.2053457600000002</v>
       </c>
       <c r="O92">
-        <v>-0.04557657600000006</v>
+        <v>-0.04928298240000004</v>
       </c>
       <c r="P92">
-        <v>-0.1443258240000002</v>
+        <v>-0.1560627776000001</v>
       </c>
       <c r="Q92">
-        <v>0.3756741759999999</v>
+        <v>0.3639372223999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6115061437828307</v>
+        <v>0.6743623819809232</v>
       </c>
       <c r="T92">
-        <v>9.538618289848969</v>
+        <v>10.59846476649886</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2072087939412148</v>
+        <v>0.2049317742275751</v>
       </c>
       <c r="W92">
-        <v>0.1163817490494297</v>
+        <v>0.116716015543392</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8633699747550618</v>
+        <v>0.8538823926148963</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9240,22 +9240,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1669041885227698</v>
+        <v>0.1679141885227698</v>
       </c>
       <c r="C93">
-        <v>-3.677473304152059</v>
+        <v>-3.830766601367161</v>
       </c>
       <c r="D93">
-        <v>5.81472669584794</v>
+        <v>5.766633398632838</v>
       </c>
       <c r="E93">
-        <v>4.9632</v>
+        <v>5.0684</v>
       </c>
       <c r="F93">
-        <v>9.5732</v>
+        <v>9.6784</v>
       </c>
       <c r="G93">
         <v>0.081</v>
@@ -9276,37 +9276,37 @@
         <v>1.2</v>
       </c>
       <c r="M93">
-        <v>1.40534576</v>
+        <v>1.42078912</v>
       </c>
       <c r="N93">
-        <v>-0.2053457600000002</v>
+        <v>-0.2207891200000001</v>
       </c>
       <c r="O93">
-        <v>-0.04928298240000004</v>
+        <v>-0.05298938880000002</v>
       </c>
       <c r="P93">
-        <v>-0.1560627776000001</v>
+        <v>-0.1677997312000001</v>
       </c>
       <c r="Q93">
-        <v>0.3639372223999999</v>
+        <v>0.3522002688</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6743623819809232</v>
+        <v>0.7529326797285388</v>
       </c>
       <c r="T93">
-        <v>10.59846476649886</v>
+        <v>11.92327286231122</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2049317742275751</v>
+        <v>0.2027042549424928</v>
       </c>
       <c r="W93">
-        <v>0.116716015543392</v>
+        <v>0.1170430153744421</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8538823926148963</v>
+        <v>0.8446010622603867</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9322,22 +9322,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1679141885227698</v>
+        <v>0.1689241885227698</v>
       </c>
       <c r="C94">
-        <v>-3.830766601367161</v>
+        <v>-3.983270870353606</v>
       </c>
       <c r="D94">
-        <v>5.766633398632838</v>
+        <v>5.719329129646393</v>
       </c>
       <c r="E94">
-        <v>5.0684</v>
+        <v>5.1736</v>
       </c>
       <c r="F94">
-        <v>9.6784</v>
+        <v>9.7836</v>
       </c>
       <c r="G94">
         <v>0.081</v>
@@ -9358,37 +9358,37 @@
         <v>1.2</v>
       </c>
       <c r="M94">
-        <v>1.42078912</v>
+        <v>1.43623248</v>
       </c>
       <c r="N94">
-        <v>-0.2207891200000001</v>
+        <v>-0.2362324800000002</v>
       </c>
       <c r="O94">
-        <v>-0.05298938880000002</v>
+        <v>-0.05669579520000004</v>
       </c>
       <c r="P94">
-        <v>-0.1677997312000001</v>
+        <v>-0.1795366848000002</v>
       </c>
       <c r="Q94">
-        <v>0.3522002688</v>
+        <v>0.3404633151999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7529326797285388</v>
+        <v>0.853951633975473</v>
       </c>
       <c r="T94">
-        <v>11.92327286231122</v>
+        <v>13.62659755692711</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2027042549424928</v>
+        <v>0.2005246392979498</v>
       </c>
       <c r="W94">
-        <v>0.1170430153744421</v>
+        <v>0.117362982951061</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8446010622603867</v>
+        <v>0.8355193304081243</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9404,22 +9404,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1689241885227698</v>
+        <v>0.1699341885227698</v>
       </c>
       <c r="C95">
-        <v>-3.983270870353606</v>
+        <v>-4.13500537055605</v>
       </c>
       <c r="D95">
-        <v>5.719329129646393</v>
+        <v>5.672794629443949</v>
       </c>
       <c r="E95">
-        <v>5.1736</v>
+        <v>5.278799999999999</v>
       </c>
       <c r="F95">
-        <v>9.7836</v>
+        <v>9.8888</v>
       </c>
       <c r="G95">
         <v>0.081</v>
@@ -9440,37 +9440,37 @@
         <v>1.2</v>
       </c>
       <c r="M95">
-        <v>1.43623248</v>
+        <v>1.45167584</v>
       </c>
       <c r="N95">
-        <v>-0.2362324800000002</v>
+        <v>-0.2516758400000001</v>
       </c>
       <c r="O95">
-        <v>-0.05669579520000004</v>
+        <v>-0.06040220160000002</v>
       </c>
       <c r="P95">
-        <v>-0.1795366848000002</v>
+        <v>-0.1912736384000001</v>
       </c>
       <c r="Q95">
-        <v>0.3404633151999998</v>
+        <v>0.3287263615999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.853951633975473</v>
+        <v>0.9886435729713856</v>
       </c>
       <c r="T95">
-        <v>13.62659755692711</v>
+        <v>15.8976971497483</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2005246392979498</v>
+        <v>0.1983913984543546</v>
       </c>
       <c r="W95">
-        <v>0.117362982951061</v>
+        <v>0.1176761427069008</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8355193304081243</v>
+        <v>0.8266308268931444</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9486,22 +9486,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1699341885227698</v>
+        <v>0.1709441885227698</v>
       </c>
       <c r="C96">
-        <v>-4.13500537055605</v>
+        <v>-4.285988739671077</v>
       </c>
       <c r="D96">
-        <v>5.672794629443949</v>
+        <v>5.627011260328922</v>
       </c>
       <c r="E96">
-        <v>5.278799999999999</v>
+        <v>5.383999999999999</v>
       </c>
       <c r="F96">
-        <v>9.8888</v>
+        <v>9.994</v>
       </c>
       <c r="G96">
         <v>0.081</v>
@@ -9522,37 +9522,37 @@
         <v>1.2</v>
       </c>
       <c r="M96">
-        <v>1.45167584</v>
+        <v>1.4671192</v>
       </c>
       <c r="N96">
-        <v>-0.2516758400000001</v>
+        <v>-0.2671192000000002</v>
       </c>
       <c r="O96">
-        <v>-0.06040220160000002</v>
+        <v>-0.06410860800000005</v>
       </c>
       <c r="P96">
-        <v>-0.1912736384000001</v>
+        <v>-0.2030105920000002</v>
       </c>
       <c r="Q96">
-        <v>0.3287263615999999</v>
+        <v>0.3169894079999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9886435729713856</v>
+        <v>1.177212287565663</v>
       </c>
       <c r="T96">
-        <v>15.8976971497483</v>
+        <v>19.07723657969796</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1983913984543546</v>
+        <v>0.1963030679443088</v>
       </c>
       <c r="W96">
-        <v>0.1176761427069008</v>
+        <v>0.1179827096257755</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8266308268931444</v>
+        <v>0.8179294497679532</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9568,22 +9568,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1709441885227698</v>
+        <v>0.1719541885227698</v>
       </c>
       <c r="C97">
-        <v>-4.285988739671077</v>
+        <v>-4.436239018536026</v>
       </c>
       <c r="D97">
-        <v>5.627011260328922</v>
+        <v>5.581960981463974</v>
       </c>
       <c r="E97">
-        <v>5.383999999999999</v>
+        <v>5.489199999999999</v>
       </c>
       <c r="F97">
-        <v>9.994</v>
+        <v>10.0992</v>
       </c>
       <c r="G97">
         <v>0.081</v>
@@ -9604,37 +9604,37 @@
         <v>1.2</v>
       </c>
       <c r="M97">
-        <v>1.4671192</v>
+        <v>1.48256256</v>
       </c>
       <c r="N97">
-        <v>-0.2671192000000002</v>
+        <v>-0.2825625600000001</v>
       </c>
       <c r="O97">
-        <v>-0.06410860800000005</v>
+        <v>-0.06781501440000003</v>
       </c>
       <c r="P97">
-        <v>-0.2030105920000002</v>
+        <v>-0.2147475456000001</v>
       </c>
       <c r="Q97">
-        <v>0.3169894079999999</v>
+        <v>0.3052524543999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.177212287565663</v>
+        <v>1.46006535945708</v>
       </c>
       <c r="T97">
-        <v>19.07723657969796</v>
+        <v>23.84654572462247</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1963030679443088</v>
+        <v>0.1942582443198889</v>
       </c>
       <c r="W97">
-        <v>0.1179827096257755</v>
+        <v>0.1182828897338403</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8179294497679532</v>
+        <v>0.8094093513328705</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9650,22 +9650,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1719541885227698</v>
+        <v>0.1729641885227698</v>
       </c>
       <c r="C98">
-        <v>-4.436239018536026</v>
+        <v>-4.585773674831725</v>
       </c>
       <c r="D98">
-        <v>5.581960981463974</v>
+        <v>5.537626325168274</v>
       </c>
       <c r="E98">
-        <v>5.489199999999999</v>
+        <v>5.594399999999999</v>
       </c>
       <c r="F98">
-        <v>10.0992</v>
+        <v>10.2044</v>
       </c>
       <c r="G98">
         <v>0.081</v>
@@ -9686,37 +9686,37 @@
         <v>1.2</v>
       </c>
       <c r="M98">
-        <v>1.48256256</v>
+        <v>1.49800592</v>
       </c>
       <c r="N98">
-        <v>-0.2825625600000001</v>
+        <v>-0.29800592</v>
       </c>
       <c r="O98">
-        <v>-0.06781501440000003</v>
+        <v>-0.0715214208</v>
       </c>
       <c r="P98">
-        <v>-0.2147475456000001</v>
+        <v>-0.2264844992</v>
       </c>
       <c r="Q98">
-        <v>0.3052524543999999</v>
+        <v>0.2935155008</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.460065359457076</v>
+        <v>1.931487145942768</v>
       </c>
       <c r="T98">
-        <v>23.8465457246224</v>
+        <v>31.79539429949654</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1942582443198889</v>
+        <v>0.1922555820073127</v>
       </c>
       <c r="W98">
-        <v>0.1182828897338403</v>
+        <v>0.1185768805613265</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8094093513328705</v>
+        <v>0.8010649250304698</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9732,22 +9732,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1729641885227698</v>
+        <v>0.2303816356329733</v>
       </c>
       <c r="C99">
-        <v>-4.585773674831725</v>
+        <v>-6.41355222686955</v>
       </c>
       <c r="D99">
-        <v>5.537626325168274</v>
+        <v>3.81504777313045</v>
       </c>
       <c r="E99">
-        <v>5.594399999999999</v>
+        <v>5.699599999999999</v>
       </c>
       <c r="F99">
-        <v>10.2044</v>
+        <v>10.3096</v>
       </c>
       <c r="G99">
         <v>0.081</v>
@@ -9768,45 +9768,45 @@
         <v>1.2</v>
       </c>
       <c r="M99">
-        <v>1.49800592</v>
+        <v>2.07016768</v>
       </c>
       <c r="N99">
-        <v>-0.29800592</v>
+        <v>-0.87016768</v>
       </c>
       <c r="O99">
-        <v>-0.0715214208</v>
+        <v>-0.2088402432</v>
       </c>
       <c r="P99">
-        <v>-0.2264844992</v>
+        <v>-0.6613274367999999</v>
       </c>
       <c r="Q99">
-        <v>0.2935155008</v>
+        <v>-0.1413274367999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.931487145942768</v>
+        <v>3.04870307442433</v>
       </c>
       <c r="T99">
-        <v>31.79539429949654</v>
+        <v>50.63325987024034</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1922555820073127</v>
+        <v>0.1391191654581333</v>
       </c>
       <c r="W99">
-        <v>0.1185768805613265</v>
+        <v>0.1728648715760068</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8010649250304698</v>
+        <v>0.5796631894088888</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9814,22 +9814,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2303816356329733</v>
+        <v>0.2319316356329733</v>
       </c>
       <c r="C100">
-        <v>-6.41355222686955</v>
+        <v>-6.550521807726897</v>
       </c>
       <c r="D100">
-        <v>3.81504777313045</v>
+        <v>3.783278192273102</v>
       </c>
       <c r="E100">
-        <v>5.699599999999999</v>
+        <v>5.804799999999999</v>
       </c>
       <c r="F100">
-        <v>10.3096</v>
+        <v>10.4148</v>
       </c>
       <c r="G100">
         <v>0.081</v>
@@ -9850,37 +9850,37 @@
         <v>1.2</v>
       </c>
       <c r="M100">
-        <v>2.07016768</v>
+        <v>2.09129184</v>
       </c>
       <c r="N100">
-        <v>-0.87016768</v>
+        <v>-0.8912918399999998</v>
       </c>
       <c r="O100">
-        <v>-0.2088402432</v>
+        <v>-0.2139100416</v>
       </c>
       <c r="P100">
-        <v>-0.6613274367999999</v>
+        <v>-0.6773817983999999</v>
       </c>
       <c r="Q100">
-        <v>-0.1413274367999999</v>
+        <v>-0.1573817983999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.04870307442433</v>
+        <v>6.051606148848659</v>
       </c>
       <c r="T100">
-        <v>50.63325987024034</v>
+        <v>101.2665197404806</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1391191654581333</v>
+        <v>0.1377139213625966</v>
       </c>
       <c r="W100">
-        <v>0.1728648715760068</v>
+        <v>0.1731470445903906</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9888,91 +9888,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5796631894088888</v>
+        <v>0.5738080056774859</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2319316356329733</v>
-      </c>
-      <c r="C101">
-        <v>-6.550521807726897</v>
-      </c>
-      <c r="D101">
-        <v>3.783278192273102</v>
-      </c>
-      <c r="E101">
-        <v>5.804799999999999</v>
-      </c>
-      <c r="F101">
-        <v>10.4148</v>
-      </c>
-      <c r="G101">
-        <v>0.081</v>
-      </c>
-      <c r="H101">
-        <v>5.91</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.72</v>
-      </c>
-      <c r="K101">
-        <v>0.52</v>
-      </c>
-      <c r="L101">
-        <v>1.2</v>
-      </c>
-      <c r="M101">
-        <v>2.09129184</v>
-      </c>
-      <c r="N101">
-        <v>-0.8912918399999998</v>
-      </c>
-      <c r="O101">
-        <v>-0.2139100416</v>
-      </c>
-      <c r="P101">
-        <v>-0.6773817983999999</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1573817983999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.051606148848659</v>
-      </c>
-      <c r="T101">
-        <v>101.2665197404806</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1377139213625966</v>
-      </c>
-      <c r="W101">
-        <v>0.1731470445903906</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5738080056774859</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
